--- a/Images for Markdown files database .xlsx
+++ b/Images for Markdown files database .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trevor\Compac Industries\Compac - General\IT\ChatBot\Markdown-Manuals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2432E8-DF6C-41ED-9952-16F96E098294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA079B67-5E73-4CC6-8AD8-5F1E4BCD2969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7323B22B-375C-41F7-91CD-F86C900FC6DE}"/>
+    <workbookView xWindow="-38520" yWindow="-1320" windowWidth="38640" windowHeight="21120" xr2:uid="{7323B22B-375C-41F7-91CD-F86C900FC6DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="703">
   <si>
     <t xml:space="preserve">PCBs </t>
   </si>
@@ -886,153 +886,39 @@
     <t>11.1.10</t>
   </si>
   <si>
-    <t>11.1.1_CompacOnlineV2_Login.png</t>
-  </si>
-  <si>
-    <t>11.1.2_CompacOnlineV2_Home_Page.png</t>
-  </si>
-  <si>
-    <t>11.1.3_CompacOnlineV2_Sites_Page.png</t>
-  </si>
-  <si>
-    <t>11.1.4_CompacOnlineV2_Sites_Page_1.png</t>
-  </si>
-  <si>
-    <t>11.1.5_CompacOnlineV2_Sites_Page_2.png</t>
-  </si>
-  <si>
-    <t>11.1.6_CompacOnlineV2_Sites_Page_3.png</t>
-  </si>
-  <si>
-    <t>11.1.7_CompacOnlineV2_Sites_Page_4.png</t>
-  </si>
-  <si>
-    <t>11.1.8_CompacOnlineV2_Sites_Page_5.png</t>
-  </si>
-  <si>
-    <t>11.1.9_CompacOnlineV2_Sites_Page_6.png</t>
-  </si>
-  <si>
-    <t>11.1.10_CompacOnlineV2_Sites_Page_7.png</t>
-  </si>
-  <si>
-    <t>11.1.11_CompacOnlineV2_Sites_Page_8.png</t>
-  </si>
-  <si>
     <t>11.1.11</t>
   </si>
   <si>
     <t>11.1.12</t>
   </si>
   <si>
-    <t>11.1.13_CompacOnlineV2_Sites_Page_10.png</t>
-  </si>
-  <si>
-    <t>11.1.12_CompacOnlineV2_Sites_Page_9.png</t>
-  </si>
-  <si>
     <t>11.1.13</t>
   </si>
   <si>
     <t>11.1.14</t>
   </si>
   <si>
-    <t>11.1.14_CompacOnlineV2_Sites_Page_11.png</t>
-  </si>
-  <si>
-    <t>11.1.15_CompacOnlineV2_Sites_Page_12.png</t>
-  </si>
-  <si>
     <t>11.1.15</t>
   </si>
   <si>
-    <t>11.1.16_CompacOnlineV2_Sites_Page_13.png</t>
-  </si>
-  <si>
     <t>11.1.16</t>
   </si>
   <si>
-    <t>11.1.17_CompacOnlineV2_Sites_Page_14.png</t>
-  </si>
-  <si>
     <t>11.1.17</t>
   </si>
   <si>
     <t>11.1.18</t>
   </si>
   <si>
-    <t>11.1.18_CompacOnlineV2_Sites_Page_15.png</t>
-  </si>
-  <si>
-    <t>11.1.19_CompacOnlineV2_Sites_Page_16.png</t>
-  </si>
-  <si>
     <t>11.1.19</t>
   </si>
   <si>
-    <t>Forecourt Controllers</t>
-  </si>
-  <si>
-    <t>Receipt Templates</t>
-  </si>
-  <si>
-    <t>11.1.20_CompacOnlineV2_Sites_Page_17.png</t>
-  </si>
-  <si>
     <t>11.1.20</t>
   </si>
   <si>
-    <t>Sample Receipt</t>
-  </si>
-  <si>
-    <t>11.1.21_CompacOnlineV2_Sites_Page_18.png</t>
-  </si>
-  <si>
     <t>11.1.21</t>
   </si>
   <si>
-    <t>Price sign details</t>
-  </si>
-  <si>
-    <t>Price signs</t>
-  </si>
-  <si>
-    <t>Tanks</t>
-  </si>
-  <si>
-    <t>Pump details</t>
-  </si>
-  <si>
-    <t>Pumps and hoses</t>
-  </si>
-  <si>
-    <t>Other actions</t>
-  </si>
-  <si>
-    <t>Windcave status</t>
-  </si>
-  <si>
-    <t>Terminals</t>
-  </si>
-  <si>
-    <t>Create site</t>
-  </si>
-  <si>
-    <t>Sites</t>
-  </si>
-  <si>
-    <t>icon</t>
-  </si>
-  <si>
-    <t>Home page</t>
-  </si>
-  <si>
-    <t>Site page</t>
-  </si>
-  <si>
-    <t>Login page</t>
-  </si>
-  <si>
     <t>11.2.1</t>
   </si>
   <si>
@@ -1873,30 +1759,6 @@
     <t>Gateway</t>
   </si>
   <si>
-    <t>20.1.1</t>
-  </si>
-  <si>
-    <t>20.1.2</t>
-  </si>
-  <si>
-    <t>20.1.1_GW_image.png</t>
-  </si>
-  <si>
-    <t>20.1.2_GW_LITE_image.png</t>
-  </si>
-  <si>
-    <t>front page image</t>
-  </si>
-  <si>
-    <t>20.1.3</t>
-  </si>
-  <si>
-    <t>20.1.3_GW_arch_image.png</t>
-  </si>
-  <si>
-    <t>architecture image</t>
-  </si>
-  <si>
     <t>Comfill Ex (Volume Register) specific</t>
   </si>
   <si>
@@ -2156,6 +2018,141 @@
   </si>
   <si>
     <t>V2 - Transactions</t>
+  </si>
+  <si>
+    <t>11.1.3_V2_Sites_sites_page.png</t>
+  </si>
+  <si>
+    <t>11.1.4_V2_Sites_status_icon.png</t>
+  </si>
+  <si>
+    <t>11.1.5_V2_Sites_sample_site.png</t>
+  </si>
+  <si>
+    <t>11.1.6_V2_Sites_side_bar_menu.png</t>
+  </si>
+  <si>
+    <t>11.1.7_V2_Sites_create_site.png</t>
+  </si>
+  <si>
+    <t>11.1.8_V2_Sites_terminals_1.png</t>
+  </si>
+  <si>
+    <t>11.1.9_V2_Sites_terminals_2.png</t>
+  </si>
+  <si>
+    <t>11.1.10_V2_Sites_windcave_status.png</t>
+  </si>
+  <si>
+    <t>11.1.11_V2_Sites_operations.png</t>
+  </si>
+  <si>
+    <t>11.1.12_V2_Sites_ops_options.png</t>
+  </si>
+  <si>
+    <t>11.1.13_V2_Sites_pumps_hoses.png</t>
+  </si>
+  <si>
+    <t>11.1.14_V2_Sites_pump_details_1.png</t>
+  </si>
+  <si>
+    <t>11.1.15_V2_Sites_pump_details_2.png</t>
+  </si>
+  <si>
+    <t>11.1.16_V2_Sites_tanks.png</t>
+  </si>
+  <si>
+    <t>11.1.17_V2_Sites_price_sign.png</t>
+  </si>
+  <si>
+    <t>11.1.18_V2_Sites_price_sign_details.png</t>
+  </si>
+  <si>
+    <t>11.1.19_V2_Sites_forecourt_control.png</t>
+  </si>
+  <si>
+    <t>11.1.21_V2_Sites_sample_receipt.png</t>
+  </si>
+  <si>
+    <t>11.1.20_V2_Sites_receipt_template.png</t>
+  </si>
+  <si>
+    <t>11.1.1_V2_login.png</t>
+  </si>
+  <si>
+    <t>11.1.2_V2_home_page.png</t>
+  </si>
+  <si>
+    <t>12.99.2</t>
+  </si>
+  <si>
+    <t>12.99.3</t>
+  </si>
+  <si>
+    <t>12.99.4</t>
+  </si>
+  <si>
+    <t>12.99.5</t>
+  </si>
+  <si>
+    <t>12.99.2_COMFILL_LITE_pass_card.png</t>
+  </si>
+  <si>
+    <t>12.99.3_COMFILL_LITE_pass_hid.png</t>
+  </si>
+  <si>
+    <t>12.99.4_COMFILL_LITE_enter_card.png</t>
+  </si>
+  <si>
+    <t>12.99.6</t>
+  </si>
+  <si>
+    <t>12.99.5_COMFILL_LITE_pump1.png</t>
+  </si>
+  <si>
+    <t>12.99.5_COMFILL_LITE_pump1and 2.png</t>
+  </si>
+  <si>
+    <t>14.1.1</t>
+  </si>
+  <si>
+    <t>14.1.2</t>
+  </si>
+  <si>
+    <t>14.1.1_GW_front_view.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1.2_GW_layout.png </t>
+  </si>
+  <si>
+    <t>14.1.3</t>
+  </si>
+  <si>
+    <t>14.1.3_GW_footprint.png</t>
+  </si>
+  <si>
+    <t>14.1.4</t>
+  </si>
+  <si>
+    <t>14.1.4_GW_perspex_guard.png</t>
+  </si>
+  <si>
+    <t>14.2.1</t>
+  </si>
+  <si>
+    <t>14.2.1_GW_din_rail_terminals.png</t>
+  </si>
+  <si>
+    <t>14.2.2</t>
+  </si>
+  <si>
+    <t>14.2.2_GW_incoming_mains.png</t>
+  </si>
+  <si>
+    <t>14.2.3</t>
+  </si>
+  <si>
+    <t>14.2.3_GW_comms_switches.png</t>
   </si>
 </sst>
 </file>
@@ -2319,7 +2316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2427,8 +2424,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2763,7 +2759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B533B56-556A-40A2-8D3F-E8E5A852019A}">
-  <dimension ref="A1:K408"/>
+  <dimension ref="A1:K419"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="1" customWidth="1"/>
@@ -2771,7 +2767,7 @@
     <col min="3" max="3" width="10.6328125" style="1" customWidth="1"/>
     <col min="4" max="4" width="47.26953125" customWidth="1"/>
     <col min="5" max="5" width="20.81640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7265625" customWidth="1"/>
+    <col min="6" max="6" width="31" customWidth="1"/>
     <col min="7" max="11" width="11.6328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3350,7 +3346,7 @@
         <v>5</v>
       </c>
       <c r="B45" s="29" t="s">
-        <v>606</v>
+        <v>568</v>
       </c>
       <c r="C45" s="28" t="s">
         <v>7</v>
@@ -3914,10 +3910,10 @@
       <c r="A78" s="13"/>
       <c r="B78" s="12"/>
       <c r="C78" s="13" t="s">
-        <v>493</v>
+        <v>455</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>497</v>
+        <v>459</v>
       </c>
       <c r="E78" s="13"/>
       <c r="F78" s="12"/>
@@ -3931,10 +3927,10 @@
       <c r="A79" s="13"/>
       <c r="B79" s="12"/>
       <c r="C79" s="13" t="s">
-        <v>494</v>
+        <v>456</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>498</v>
+        <v>460</v>
       </c>
       <c r="E79" s="13"/>
       <c r="F79" s="12"/>
@@ -3948,10 +3944,10 @@
       <c r="A80" s="13"/>
       <c r="B80" s="12"/>
       <c r="C80" s="13" t="s">
-        <v>495</v>
+        <v>457</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>499</v>
+        <v>461</v>
       </c>
       <c r="E80" s="13"/>
       <c r="F80" s="12"/>
@@ -3965,10 +3961,10 @@
       <c r="A81" s="13"/>
       <c r="B81" s="12"/>
       <c r="C81" s="13" t="s">
-        <v>496</v>
+        <v>458</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>500</v>
+        <v>462</v>
       </c>
       <c r="E81" s="13"/>
       <c r="F81" s="12"/>
@@ -4289,7 +4285,7 @@
     <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" s="35"/>
       <c r="B106" s="36" t="s">
-        <v>607</v>
+        <v>569</v>
       </c>
       <c r="C106" s="35" t="s">
         <v>180</v>
@@ -4394,30 +4390,26 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" s="47" t="s">
-        <v>619</v>
+        <v>573</v>
       </c>
       <c r="B112" s="48" t="s">
-        <v>618</v>
+        <v>572</v>
       </c>
       <c r="C112" s="32" t="s">
         <v>270</v>
       </c>
       <c r="D112" s="33" t="s">
-        <v>280</v>
+        <v>677</v>
       </c>
       <c r="E112" s="34">
         <v>46099</v>
       </c>
-      <c r="F112" s="33" t="s">
-        <v>328</v>
-      </c>
-      <c r="G112" s="33" t="s">
-        <v>324</v>
-      </c>
+      <c r="F112" s="33"/>
+      <c r="G112" s="33"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="13" t="s">
-        <v>620</v>
+        <v>574</v>
       </c>
       <c r="B113" s="19">
         <v>11</v>
@@ -4426,17 +4418,13 @@
         <v>271</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>281</v>
+        <v>678</v>
       </c>
       <c r="E113" s="17">
         <v>46099</v>
       </c>
-      <c r="F113" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="G113" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="F113" s="5"/>
+      <c r="G113" s="5"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4"/>
@@ -4445,17 +4433,15 @@
         <v>272</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>282</v>
+        <v>658</v>
       </c>
       <c r="E114" s="17">
         <v>46099</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="G114" s="5" t="s">
-        <v>324</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="G114" s="5"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4"/>
@@ -4464,17 +4450,15 @@
         <v>273</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>283</v>
+        <v>659</v>
       </c>
       <c r="E115" s="17">
         <v>46099</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>324</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="G115" s="5"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4"/>
@@ -4483,17 +4467,15 @@
         <v>274</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>284</v>
+        <v>660</v>
       </c>
       <c r="E116" s="17">
         <v>46099</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G116" s="5" t="s">
-        <v>324</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="G116" s="5"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4"/>
@@ -4502,17 +4484,15 @@
         <v>275</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>285</v>
+        <v>661</v>
       </c>
       <c r="E117" s="17">
         <v>46099</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>324</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="G117" s="5"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4"/>
@@ -4521,17 +4501,15 @@
         <v>276</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>286</v>
+        <v>662</v>
       </c>
       <c r="E118" s="17">
         <v>46099</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="G118" s="5" t="s">
-        <v>324</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="G118" s="5"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4"/>
@@ -4540,17 +4518,13 @@
         <v>277</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>287</v>
+        <v>663</v>
       </c>
       <c r="E119" s="17">
         <v>46099</v>
       </c>
-      <c r="F119" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="F119" s="5"/>
+      <c r="G119" s="5"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4"/>
@@ -4559,17 +4533,13 @@
         <v>278</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>288</v>
+        <v>664</v>
       </c>
       <c r="E120" s="17">
         <v>46099</v>
       </c>
-      <c r="F120" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="G120" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="F120" s="5"/>
+      <c r="G120" s="5"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4"/>
@@ -4578,226 +4548,178 @@
         <v>279</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>289</v>
+        <v>665</v>
       </c>
       <c r="E121" s="17">
         <v>46099</v>
       </c>
-      <c r="F121" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="G121" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="F121" s="5"/>
+      <c r="G121" s="5"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4"/>
       <c r="B122" s="5"/>
       <c r="C122" s="4" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>290</v>
+        <v>666</v>
       </c>
       <c r="E122" s="17">
         <v>46099</v>
       </c>
-      <c r="F122" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="G122" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="F122" s="5"/>
+      <c r="G122" s="5"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4"/>
       <c r="B123" s="5"/>
       <c r="C123" s="4" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>294</v>
+        <v>667</v>
       </c>
       <c r="E123" s="17">
         <v>46099</v>
       </c>
-      <c r="F123" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="G123" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="F123" s="5"/>
+      <c r="G123" s="5"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4"/>
       <c r="B124" s="5"/>
       <c r="C124" s="4" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>293</v>
+        <v>668</v>
       </c>
       <c r="E124" s="17">
         <v>46099</v>
       </c>
-      <c r="F124" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="G124" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="F124" s="5"/>
+      <c r="G124" s="5"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4"/>
       <c r="B125" s="5"/>
       <c r="C125" s="4" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>297</v>
+        <v>669</v>
       </c>
       <c r="E125" s="17">
         <v>46099</v>
       </c>
-      <c r="F125" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="G125" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="F125" s="5"/>
+      <c r="G125" s="5"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4"/>
       <c r="B126" s="5"/>
       <c r="C126" s="4" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>298</v>
+        <v>670</v>
       </c>
       <c r="E126" s="17">
         <v>46099</v>
       </c>
-      <c r="F126" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="G126" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="F126" s="5"/>
+      <c r="G126" s="5"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4"/>
       <c r="B127" s="5"/>
       <c r="C127" s="4" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>300</v>
+        <v>671</v>
       </c>
       <c r="E127" s="17">
         <v>46099</v>
       </c>
-      <c r="F127" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="G127" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="F127" s="5"/>
+      <c r="G127" s="5"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4"/>
       <c r="B128" s="5"/>
       <c r="C128" s="4" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>302</v>
+        <v>672</v>
       </c>
       <c r="E128" s="17">
         <v>46099</v>
       </c>
-      <c r="F128" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="G128" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="F128" s="5"/>
+      <c r="G128" s="5"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4"/>
       <c r="B129" s="5"/>
       <c r="C129" s="4" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>305</v>
+        <v>673</v>
       </c>
       <c r="E129" s="17">
         <v>46099</v>
       </c>
-      <c r="F129" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="G129" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="F129" s="5"/>
+      <c r="G129" s="5"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4"/>
       <c r="B130" s="5"/>
       <c r="C130" s="4" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>306</v>
+        <v>674</v>
       </c>
       <c r="E130" s="17">
         <v>46099</v>
       </c>
-      <c r="F130" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="G130" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="F130" s="5"/>
+      <c r="G130" s="5"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4"/>
       <c r="B131" s="5"/>
       <c r="C131" s="4" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>310</v>
+        <v>676</v>
       </c>
       <c r="E131" s="17">
         <v>46099</v>
       </c>
-      <c r="F131" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="G131" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="F131" s="5"/>
+      <c r="G131" s="5"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4"/>
       <c r="B132" s="5"/>
       <c r="C132" s="4" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>313</v>
+        <v>675</v>
       </c>
       <c r="E132" s="17">
         <v>46099</v>
       </c>
-      <c r="F132" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="G132" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="F132" s="5"/>
+      <c r="G132" s="5"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4"/>
@@ -4806,7 +4728,7 @@
         <v>11.2</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>703</v>
+        <v>657</v>
       </c>
       <c r="E133" s="46"/>
       <c r="F133" s="12"/>
@@ -4816,10 +4738,10 @@
       <c r="A134" s="4"/>
       <c r="B134" s="5"/>
       <c r="C134" s="4" t="s">
-        <v>329</v>
+        <v>291</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>702</v>
+        <v>656</v>
       </c>
       <c r="E134" s="17">
         <v>46099</v>
@@ -4831,10 +4753,10 @@
       <c r="A135" s="4"/>
       <c r="B135" s="5"/>
       <c r="C135" s="4" t="s">
-        <v>330</v>
+        <v>292</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>701</v>
+        <v>655</v>
       </c>
       <c r="E135" s="17">
         <v>46099</v>
@@ -4846,10 +4768,10 @@
       <c r="A136" s="4"/>
       <c r="B136" s="5"/>
       <c r="C136" s="4" t="s">
-        <v>331</v>
+        <v>293</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>700</v>
+        <v>654</v>
       </c>
       <c r="E136" s="17">
         <v>46099</v>
@@ -4861,10 +4783,10 @@
       <c r="A137" s="4"/>
       <c r="B137" s="5"/>
       <c r="C137" s="4" t="s">
-        <v>332</v>
+        <v>294</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>699</v>
+        <v>653</v>
       </c>
       <c r="E137" s="17">
         <v>46099</v>
@@ -4876,10 +4798,10 @@
       <c r="A138" s="4"/>
       <c r="B138" s="5"/>
       <c r="C138" s="4" t="s">
-        <v>333</v>
+        <v>295</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>698</v>
+        <v>652</v>
       </c>
       <c r="E138" s="17">
         <v>46099</v>
@@ -4895,10 +4817,10 @@
       <c r="A139" s="4"/>
       <c r="B139" s="5"/>
       <c r="C139" s="4" t="s">
-        <v>334</v>
+        <v>296</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>697</v>
+        <v>651</v>
       </c>
       <c r="E139" s="17">
         <v>46099</v>
@@ -4914,10 +4836,10 @@
       <c r="A140" s="4"/>
       <c r="B140" s="5"/>
       <c r="C140" s="4" t="s">
-        <v>335</v>
+        <v>297</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>696</v>
+        <v>650</v>
       </c>
       <c r="E140" s="17">
         <v>46099</v>
@@ -4933,10 +4855,10 @@
       <c r="A141" s="4"/>
       <c r="B141" s="5"/>
       <c r="C141" s="4" t="s">
-        <v>336</v>
+        <v>298</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>695</v>
+        <v>649</v>
       </c>
       <c r="E141" s="17">
         <v>46099</v>
@@ -4952,10 +4874,10 @@
       <c r="A142" s="4"/>
       <c r="B142" s="5"/>
       <c r="C142" s="4" t="s">
-        <v>337</v>
+        <v>299</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>694</v>
+        <v>648</v>
       </c>
       <c r="E142" s="17">
         <v>46099</v>
@@ -4971,10 +4893,10 @@
       <c r="A143" s="4"/>
       <c r="B143" s="5"/>
       <c r="C143" s="4" t="s">
-        <v>338</v>
+        <v>300</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>693</v>
+        <v>647</v>
       </c>
       <c r="E143" s="17">
         <v>46099</v>
@@ -4990,10 +4912,10 @@
       <c r="A144" s="4"/>
       <c r="B144" s="5"/>
       <c r="C144" s="4" t="s">
-        <v>339</v>
+        <v>301</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>692</v>
+        <v>646</v>
       </c>
       <c r="E144" s="17">
         <v>46099</v>
@@ -5009,10 +4931,10 @@
       <c r="A145" s="4"/>
       <c r="B145" s="5"/>
       <c r="C145" s="4" t="s">
-        <v>340</v>
+        <v>302</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>691</v>
+        <v>645</v>
       </c>
       <c r="E145" s="17">
         <v>46099</v>
@@ -5028,10 +4950,10 @@
       <c r="A146" s="4"/>
       <c r="B146" s="5"/>
       <c r="C146" s="4" t="s">
-        <v>341</v>
+        <v>303</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>690</v>
+        <v>644</v>
       </c>
       <c r="E146" s="17">
         <v>46099</v>
@@ -5047,10 +4969,10 @@
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
       <c r="C147" s="4" t="s">
-        <v>342</v>
+        <v>304</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>689</v>
+        <v>643</v>
       </c>
       <c r="E147" s="17">
         <v>46099</v>
@@ -5066,10 +4988,10 @@
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="4" t="s">
-        <v>343</v>
+        <v>305</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>688</v>
+        <v>642</v>
       </c>
       <c r="E148" s="17">
         <v>46099</v>
@@ -5088,7 +5010,7 @@
         <v>11.3</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>687</v>
+        <v>641</v>
       </c>
       <c r="E149" s="46"/>
       <c r="F149" s="12"/>
@@ -5098,10 +5020,10 @@
       <c r="A150" s="4"/>
       <c r="B150" s="5"/>
       <c r="C150" s="4" t="s">
-        <v>344</v>
+        <v>306</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>686</v>
+        <v>640</v>
       </c>
       <c r="E150" s="17">
         <v>46099</v>
@@ -5120,7 +5042,7 @@
         <v>11.4</v>
       </c>
       <c r="D151" s="12" t="s">
-        <v>683</v>
+        <v>637</v>
       </c>
       <c r="E151" s="46"/>
       <c r="F151" s="12"/>
@@ -5130,10 +5052,10 @@
       <c r="A152" s="4"/>
       <c r="B152" s="5"/>
       <c r="C152" s="4" t="s">
-        <v>345</v>
+        <v>307</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>684</v>
+        <v>638</v>
       </c>
       <c r="E152" s="17">
         <v>46099</v>
@@ -5149,10 +5071,10 @@
       <c r="A153" s="4"/>
       <c r="B153" s="5"/>
       <c r="C153" s="4" t="s">
-        <v>346</v>
+        <v>308</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>685</v>
+        <v>639</v>
       </c>
       <c r="E153" s="17">
         <v>46099</v>
@@ -5171,7 +5093,7 @@
         <v>11.5</v>
       </c>
       <c r="D154" s="12" t="s">
-        <v>673</v>
+        <v>627</v>
       </c>
       <c r="E154" s="46"/>
       <c r="F154" s="12"/>
@@ -5181,10 +5103,10 @@
       <c r="A155" s="4"/>
       <c r="B155" s="5"/>
       <c r="C155" s="4" t="s">
-        <v>348</v>
+        <v>310</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>666</v>
+        <v>620</v>
       </c>
       <c r="E155" s="17">
         <v>46099</v>
@@ -5200,10 +5122,10 @@
       <c r="A156" s="4"/>
       <c r="B156" s="5"/>
       <c r="C156" s="4" t="s">
-        <v>347</v>
+        <v>309</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>667</v>
+        <v>621</v>
       </c>
       <c r="E156" s="17">
         <v>46099</v>
@@ -5215,10 +5137,10 @@
       <c r="A157" s="4"/>
       <c r="B157" s="5"/>
       <c r="C157" s="4" t="s">
-        <v>349</v>
+        <v>311</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>668</v>
+        <v>622</v>
       </c>
       <c r="E157" s="17">
         <v>46099</v>
@@ -5230,10 +5152,10 @@
       <c r="A158" s="4"/>
       <c r="B158" s="5"/>
       <c r="C158" s="4" t="s">
-        <v>350</v>
+        <v>312</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>669</v>
+        <v>623</v>
       </c>
       <c r="E158" s="17">
         <v>46099</v>
@@ -5245,10 +5167,10 @@
       <c r="A159" s="4"/>
       <c r="B159" s="5"/>
       <c r="C159" s="4" t="s">
-        <v>351</v>
+        <v>313</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>674</v>
+        <v>628</v>
       </c>
       <c r="E159" s="17">
         <v>46099</v>
@@ -5264,10 +5186,10 @@
       <c r="A160" s="4"/>
       <c r="B160" s="5"/>
       <c r="C160" s="4" t="s">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>670</v>
+        <v>624</v>
       </c>
       <c r="E160" s="17">
         <v>46099</v>
@@ -5279,10 +5201,10 @@
       <c r="A161" s="4"/>
       <c r="B161" s="5"/>
       <c r="C161" s="4" t="s">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>671</v>
+        <v>625</v>
       </c>
       <c r="E161" s="17">
         <v>46099</v>
@@ -5294,10 +5216,10 @@
       <c r="A162" s="4"/>
       <c r="B162" s="5"/>
       <c r="C162" s="4" t="s">
-        <v>354</v>
+        <v>316</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>672</v>
+        <v>626</v>
       </c>
       <c r="E162" s="17">
         <v>46099</v>
@@ -5309,10 +5231,10 @@
       <c r="A163" s="4"/>
       <c r="B163" s="5"/>
       <c r="C163" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="D163" s="50" t="s">
-        <v>676</v>
+        <v>317</v>
+      </c>
+      <c r="D163" s="49" t="s">
+        <v>630</v>
       </c>
       <c r="E163" s="17">
         <v>46099</v>
@@ -5328,10 +5250,10 @@
       <c r="A164" s="4"/>
       <c r="B164" s="5"/>
       <c r="C164" s="4" t="s">
-        <v>356</v>
+        <v>318</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>677</v>
+        <v>631</v>
       </c>
       <c r="E164" s="17">
         <v>46099</v>
@@ -5343,10 +5265,10 @@
       <c r="A165" s="4"/>
       <c r="B165" s="5"/>
       <c r="C165" s="4" t="s">
-        <v>357</v>
+        <v>319</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>678</v>
+        <v>632</v>
       </c>
       <c r="E165" s="17">
         <v>46099</v>
@@ -5358,10 +5280,10 @@
       <c r="A166" s="4"/>
       <c r="B166" s="5"/>
       <c r="C166" s="4" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>679</v>
+        <v>633</v>
       </c>
       <c r="E166" s="17">
         <v>46099</v>
@@ -5373,10 +5295,10 @@
       <c r="A167" s="4"/>
       <c r="B167" s="5"/>
       <c r="C167" s="4" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>680</v>
+        <v>634</v>
       </c>
       <c r="E167" s="17">
         <v>46099</v>
@@ -5388,10 +5310,10 @@
       <c r="A168" s="4"/>
       <c r="B168" s="5"/>
       <c r="C168" s="4" t="s">
-        <v>360</v>
+        <v>322</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>681</v>
+        <v>635</v>
       </c>
       <c r="E168" s="17">
         <v>46099</v>
@@ -5403,10 +5325,10 @@
       <c r="A169" s="4"/>
       <c r="B169" s="5"/>
       <c r="C169" s="4" t="s">
-        <v>675</v>
+        <v>629</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>682</v>
+        <v>636</v>
       </c>
       <c r="E169" s="17">
         <v>46099</v>
@@ -5421,7 +5343,7 @@
         <v>11.6</v>
       </c>
       <c r="D170" s="12" t="s">
-        <v>659</v>
+        <v>613</v>
       </c>
       <c r="E170" s="46"/>
       <c r="F170" s="12"/>
@@ -5431,10 +5353,10 @@
       <c r="A171" s="4"/>
       <c r="B171" s="5"/>
       <c r="C171" s="4" t="s">
-        <v>361</v>
+        <v>323</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>660</v>
+        <v>614</v>
       </c>
       <c r="E171" s="17">
         <v>46099</v>
@@ -5446,10 +5368,10 @@
       <c r="A172" s="4"/>
       <c r="B172" s="5"/>
       <c r="C172" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="D172" s="49" t="s">
-        <v>661</v>
+        <v>324</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>615</v>
       </c>
       <c r="E172" s="17">
         <v>46099</v>
@@ -5461,10 +5383,10 @@
       <c r="A173" s="4"/>
       <c r="B173" s="5"/>
       <c r="C173" s="4" t="s">
-        <v>363</v>
+        <v>325</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>662</v>
+        <v>616</v>
       </c>
       <c r="E173" s="17">
         <v>46099</v>
@@ -5476,10 +5398,10 @@
       <c r="A174" s="4"/>
       <c r="B174" s="5"/>
       <c r="C174" s="4" t="s">
-        <v>364</v>
+        <v>326</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>663</v>
+        <v>617</v>
       </c>
       <c r="E174" s="17">
         <v>46099</v>
@@ -5491,10 +5413,10 @@
       <c r="A175" s="4"/>
       <c r="B175" s="5"/>
       <c r="C175" s="4" t="s">
-        <v>365</v>
+        <v>327</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>664</v>
+        <v>618</v>
       </c>
       <c r="E175" s="17">
         <v>46099</v>
@@ -5506,10 +5428,10 @@
       <c r="A176" s="4"/>
       <c r="B176" s="5"/>
       <c r="C176" s="4" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>665</v>
+        <v>619</v>
       </c>
       <c r="E176" s="17">
         <v>46099</v>
@@ -5524,7 +5446,7 @@
         <v>11.7</v>
       </c>
       <c r="D177" s="12" t="s">
-        <v>657</v>
+        <v>611</v>
       </c>
       <c r="E177" s="46"/>
       <c r="F177" s="12"/>
@@ -5534,10 +5456,10 @@
       <c r="A178" s="4"/>
       <c r="B178" s="5"/>
       <c r="C178" s="4" t="s">
-        <v>367</v>
+        <v>329</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>649</v>
+        <v>603</v>
       </c>
       <c r="E178" s="17">
         <v>46099</v>
@@ -5549,10 +5471,10 @@
       <c r="A179" s="4"/>
       <c r="B179" s="5"/>
       <c r="C179" s="4" t="s">
-        <v>368</v>
+        <v>330</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>650</v>
+        <v>604</v>
       </c>
       <c r="E179" s="17">
         <v>46099</v>
@@ -5564,10 +5486,10 @@
       <c r="A180" s="4"/>
       <c r="B180" s="5"/>
       <c r="C180" s="4" t="s">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>651</v>
+        <v>605</v>
       </c>
       <c r="E180" s="17">
         <v>46099</v>
@@ -5579,10 +5501,10 @@
       <c r="A181" s="4"/>
       <c r="B181" s="5"/>
       <c r="C181" s="4" t="s">
-        <v>370</v>
+        <v>332</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>652</v>
+        <v>606</v>
       </c>
       <c r="E181" s="17">
         <v>46099</v>
@@ -5594,10 +5516,10 @@
       <c r="A182" s="4"/>
       <c r="B182" s="5"/>
       <c r="C182" s="4" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>653</v>
+        <v>607</v>
       </c>
       <c r="E182" s="17">
         <v>46099</v>
@@ -5609,10 +5531,10 @@
       <c r="A183" s="4"/>
       <c r="B183" s="5"/>
       <c r="C183" s="4" t="s">
-        <v>372</v>
+        <v>334</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>654</v>
+        <v>608</v>
       </c>
       <c r="E183" s="17">
         <v>46099</v>
@@ -5624,10 +5546,10 @@
       <c r="A184" s="4"/>
       <c r="B184" s="5"/>
       <c r="C184" s="4" t="s">
-        <v>373</v>
+        <v>335</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>655</v>
+        <v>609</v>
       </c>
       <c r="E184" s="17">
         <v>46099</v>
@@ -5639,10 +5561,10 @@
       <c r="A185" s="4"/>
       <c r="B185" s="5"/>
       <c r="C185" s="4" t="s">
-        <v>374</v>
+        <v>336</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>656</v>
+        <v>610</v>
       </c>
       <c r="E185" s="17">
         <v>46099</v>
@@ -5657,7 +5579,7 @@
         <v>11.8</v>
       </c>
       <c r="D186" s="12" t="s">
-        <v>658</v>
+        <v>612</v>
       </c>
       <c r="E186" s="46"/>
       <c r="F186" s="12"/>
@@ -5667,10 +5589,10 @@
       <c r="A187" s="4"/>
       <c r="B187" s="5"/>
       <c r="C187" s="4" t="s">
-        <v>621</v>
+        <v>575</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>635</v>
+        <v>589</v>
       </c>
       <c r="E187" s="17">
         <v>46275</v>
@@ -5682,10 +5604,10 @@
       <c r="A188" s="4"/>
       <c r="B188" s="5"/>
       <c r="C188" s="4" t="s">
-        <v>622</v>
+        <v>576</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>636</v>
+        <v>590</v>
       </c>
       <c r="E188" s="17">
         <v>46275</v>
@@ -5697,10 +5619,10 @@
       <c r="A189" s="4"/>
       <c r="B189" s="5"/>
       <c r="C189" s="4" t="s">
-        <v>623</v>
+        <v>577</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>637</v>
+        <v>591</v>
       </c>
       <c r="E189" s="17">
         <v>46275</v>
@@ -5712,10 +5634,10 @@
       <c r="A190" s="4"/>
       <c r="B190" s="5"/>
       <c r="C190" s="4" t="s">
-        <v>624</v>
+        <v>578</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>638</v>
+        <v>592</v>
       </c>
       <c r="E190" s="17">
         <v>46275</v>
@@ -5727,10 +5649,10 @@
       <c r="A191" s="4"/>
       <c r="B191" s="5"/>
       <c r="C191" s="4" t="s">
-        <v>625</v>
+        <v>579</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>639</v>
+        <v>593</v>
       </c>
       <c r="E191" s="17">
         <v>46275</v>
@@ -5742,10 +5664,10 @@
       <c r="A192" s="4"/>
       <c r="B192" s="5"/>
       <c r="C192" s="4" t="s">
-        <v>626</v>
+        <v>580</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>640</v>
+        <v>594</v>
       </c>
       <c r="E192" s="17">
         <v>46275</v>
@@ -5757,10 +5679,10 @@
       <c r="A193" s="4"/>
       <c r="B193" s="5"/>
       <c r="C193" s="4" t="s">
-        <v>627</v>
+        <v>581</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>641</v>
+        <v>595</v>
       </c>
       <c r="E193" s="17">
         <v>46275</v>
@@ -5772,10 +5694,10 @@
       <c r="A194" s="4"/>
       <c r="B194" s="5"/>
       <c r="C194" s="4" t="s">
-        <v>628</v>
+        <v>582</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>642</v>
+        <v>596</v>
       </c>
       <c r="E194" s="17">
         <v>46275</v>
@@ -5787,10 +5709,10 @@
       <c r="A195" s="4"/>
       <c r="B195" s="5"/>
       <c r="C195" s="4" t="s">
-        <v>629</v>
+        <v>583</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>643</v>
+        <v>597</v>
       </c>
       <c r="E195" s="17">
         <v>46275</v>
@@ -5802,10 +5724,10 @@
       <c r="A196" s="4"/>
       <c r="B196" s="5"/>
       <c r="C196" s="4" t="s">
-        <v>630</v>
+        <v>584</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>644</v>
+        <v>598</v>
       </c>
       <c r="E196" s="17">
         <v>46275</v>
@@ -5817,10 +5739,10 @@
       <c r="A197" s="4"/>
       <c r="B197" s="5"/>
       <c r="C197" s="4" t="s">
-        <v>631</v>
+        <v>585</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>645</v>
+        <v>599</v>
       </c>
       <c r="E197" s="17">
         <v>46275</v>
@@ -5832,10 +5754,10 @@
       <c r="A198" s="4"/>
       <c r="B198" s="5"/>
       <c r="C198" s="4" t="s">
-        <v>632</v>
+        <v>586</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>646</v>
+        <v>600</v>
       </c>
       <c r="E198" s="17">
         <v>46275</v>
@@ -5847,10 +5769,10 @@
       <c r="A199" s="4"/>
       <c r="B199" s="5"/>
       <c r="C199" s="4" t="s">
-        <v>633</v>
+        <v>587</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>647</v>
+        <v>601</v>
       </c>
       <c r="E199" s="17">
         <v>46275</v>
@@ -5862,10 +5784,10 @@
       <c r="A200" s="4"/>
       <c r="B200" s="5"/>
       <c r="C200" s="4" t="s">
-        <v>634</v>
+        <v>588</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>648</v>
+        <v>602</v>
       </c>
       <c r="E200" s="17">
         <v>46275</v>
@@ -6003,558 +5925,496 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B216" t="s">
-        <v>603</v>
+        <v>565</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>501</v>
+        <v>463</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C217" s="1" t="s">
-        <v>502</v>
+        <v>464</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C218" s="1" t="s">
-        <v>503</v>
+        <v>465</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C219" s="1" t="s">
-        <v>504</v>
+        <v>466</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C220" s="1" t="s">
-        <v>505</v>
+        <v>467</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C221" s="1" t="s">
-        <v>506</v>
+        <v>468</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C222" s="1" t="s">
-        <v>507</v>
+        <v>469</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C223" s="1" t="s">
-        <v>508</v>
+        <v>470</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C224" s="1" t="s">
-        <v>509</v>
+        <v>471</v>
       </c>
     </row>
     <row r="225" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C225" s="1" t="s">
-        <v>510</v>
+        <v>472</v>
       </c>
     </row>
     <row r="226" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C226" s="1" t="s">
-        <v>511</v>
+        <v>473</v>
       </c>
     </row>
     <row r="227" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C227" s="1" t="s">
-        <v>512</v>
+        <v>474</v>
       </c>
     </row>
     <row r="228" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C228" s="1" t="s">
-        <v>513</v>
+        <v>475</v>
       </c>
     </row>
     <row r="229" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C229" s="1" t="s">
-        <v>514</v>
+        <v>476</v>
       </c>
     </row>
     <row r="230" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C230" s="1" t="s">
-        <v>515</v>
+        <v>477</v>
       </c>
     </row>
     <row r="231" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C231" s="1" t="s">
-        <v>516</v>
+        <v>478</v>
       </c>
     </row>
     <row r="232" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C232" s="1" t="s">
-        <v>517</v>
+        <v>479</v>
       </c>
     </row>
     <row r="233" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C233" s="1" t="s">
-        <v>518</v>
+        <v>480</v>
       </c>
     </row>
     <row r="234" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C234" s="1" t="s">
-        <v>519</v>
+        <v>481</v>
       </c>
     </row>
     <row r="235" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C235" s="1" t="s">
-        <v>520</v>
+        <v>482</v>
       </c>
     </row>
     <row r="236" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C236" s="1" t="s">
-        <v>521</v>
+        <v>483</v>
       </c>
     </row>
     <row r="237" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C237" s="1" t="s">
-        <v>522</v>
+        <v>484</v>
       </c>
     </row>
     <row r="238" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C238" s="1" t="s">
-        <v>523</v>
+        <v>485</v>
       </c>
     </row>
     <row r="239" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C239" s="1" t="s">
-        <v>524</v>
+        <v>486</v>
       </c>
     </row>
     <row r="240" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C240" s="1" t="s">
-        <v>525</v>
+        <v>487</v>
       </c>
     </row>
     <row r="241" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C241" s="1" t="s">
-        <v>526</v>
+        <v>488</v>
       </c>
     </row>
     <row r="242" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C242" s="1" t="s">
-        <v>527</v>
+        <v>489</v>
       </c>
     </row>
     <row r="243" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C243" s="1" t="s">
-        <v>528</v>
+        <v>490</v>
       </c>
     </row>
     <row r="244" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C244" s="1" t="s">
-        <v>529</v>
+        <v>491</v>
       </c>
     </row>
     <row r="245" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C245" s="1" t="s">
-        <v>530</v>
+        <v>492</v>
       </c>
     </row>
     <row r="246" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C246" s="1" t="s">
-        <v>531</v>
+        <v>493</v>
       </c>
     </row>
     <row r="247" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C247" s="1" t="s">
-        <v>532</v>
+        <v>494</v>
       </c>
     </row>
     <row r="248" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C248" s="1" t="s">
-        <v>533</v>
+        <v>495</v>
       </c>
     </row>
     <row r="249" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C249" s="1" t="s">
-        <v>534</v>
+        <v>496</v>
       </c>
     </row>
     <row r="250" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C250" s="1" t="s">
-        <v>535</v>
+        <v>497</v>
       </c>
     </row>
     <row r="251" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C251" s="1" t="s">
-        <v>536</v>
+        <v>498</v>
       </c>
     </row>
     <row r="252" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C252" s="1" t="s">
-        <v>537</v>
+        <v>499</v>
       </c>
     </row>
     <row r="253" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C253" s="1" t="s">
-        <v>538</v>
+        <v>500</v>
       </c>
     </row>
     <row r="254" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C254" s="1" t="s">
-        <v>539</v>
+        <v>501</v>
       </c>
     </row>
     <row r="255" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C255" s="1" t="s">
-        <v>540</v>
+        <v>502</v>
       </c>
     </row>
     <row r="256" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C256" s="1" t="s">
-        <v>541</v>
+        <v>503</v>
       </c>
     </row>
     <row r="257" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C257" s="1" t="s">
-        <v>542</v>
+        <v>504</v>
       </c>
     </row>
     <row r="258" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C258" s="1" t="s">
-        <v>543</v>
+        <v>505</v>
       </c>
     </row>
     <row r="259" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C259" s="1" t="s">
-        <v>544</v>
+        <v>506</v>
       </c>
     </row>
     <row r="260" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C260" s="1" t="s">
-        <v>545</v>
+        <v>507</v>
       </c>
     </row>
     <row r="261" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C261" s="1" t="s">
-        <v>546</v>
+        <v>508</v>
       </c>
     </row>
     <row r="262" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C262" s="1" t="s">
-        <v>547</v>
+        <v>509</v>
       </c>
     </row>
     <row r="263" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C263" s="1" t="s">
-        <v>548</v>
+        <v>510</v>
       </c>
     </row>
     <row r="264" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C264" s="1" t="s">
-        <v>549</v>
+        <v>511</v>
       </c>
     </row>
     <row r="265" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C265" s="1" t="s">
-        <v>550</v>
+        <v>512</v>
       </c>
     </row>
     <row r="266" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C266" s="1" t="s">
-        <v>551</v>
+        <v>513</v>
       </c>
     </row>
     <row r="267" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C267" s="1" t="s">
-        <v>552</v>
+        <v>514</v>
       </c>
     </row>
     <row r="268" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C268" s="1" t="s">
-        <v>553</v>
+        <v>515</v>
       </c>
     </row>
     <row r="269" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C269" s="1" t="s">
-        <v>554</v>
+        <v>516</v>
       </c>
     </row>
     <row r="270" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C270" s="1" t="s">
-        <v>555</v>
+        <v>517</v>
       </c>
     </row>
     <row r="271" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C271" s="1" t="s">
-        <v>556</v>
+        <v>518</v>
       </c>
     </row>
     <row r="272" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C272" s="1" t="s">
-        <v>557</v>
+        <v>519</v>
       </c>
     </row>
     <row r="273" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C273" s="1" t="s">
-        <v>558</v>
+        <v>520</v>
       </c>
     </row>
     <row r="274" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C274" s="1" t="s">
-        <v>559</v>
+        <v>521</v>
       </c>
     </row>
     <row r="275" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C275" s="1" t="s">
-        <v>560</v>
+        <v>522</v>
       </c>
     </row>
     <row r="276" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C276" s="1" t="s">
-        <v>561</v>
+        <v>523</v>
       </c>
     </row>
     <row r="277" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C277" s="1" t="s">
-        <v>562</v>
+        <v>524</v>
       </c>
     </row>
     <row r="278" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C278" s="1" t="s">
-        <v>563</v>
+        <v>525</v>
       </c>
     </row>
     <row r="279" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C279" s="1" t="s">
-        <v>564</v>
+        <v>526</v>
       </c>
     </row>
     <row r="280" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C280" s="1" t="s">
-        <v>565</v>
+        <v>527</v>
       </c>
     </row>
     <row r="281" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C281" s="1" t="s">
-        <v>566</v>
+        <v>528</v>
       </c>
     </row>
     <row r="282" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C282" s="1" t="s">
-        <v>567</v>
+        <v>529</v>
       </c>
     </row>
     <row r="283" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C283" s="1" t="s">
-        <v>568</v>
+        <v>530</v>
       </c>
     </row>
     <row r="284" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C284" s="1" t="s">
-        <v>569</v>
+        <v>531</v>
       </c>
     </row>
     <row r="285" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C285" s="1" t="s">
-        <v>570</v>
+        <v>532</v>
       </c>
     </row>
     <row r="286" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C286" s="1" t="s">
-        <v>571</v>
+        <v>533</v>
       </c>
     </row>
     <row r="287" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C287" s="1" t="s">
-        <v>572</v>
+        <v>534</v>
       </c>
     </row>
     <row r="288" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C288" s="1" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.35">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="289" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C289" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.35">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="290" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C290" s="1" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.35">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="291" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C291" s="1" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.35">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="292" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C292" s="1" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.35">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="293" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C293" s="1" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.35">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="295" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B295" t="s">
-        <v>579</v>
+        <v>541</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>580</v>
+        <v>542</v>
       </c>
       <c r="D295" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.35">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="296" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C296" s="1" t="s">
-        <v>582</v>
+        <v>544</v>
       </c>
       <c r="D296" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B298" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A303" s="20"/>
-      <c r="B303" s="21"/>
-      <c r="C303" s="20"/>
-      <c r="D303" s="21"/>
-      <c r="E303" s="20"/>
-      <c r="F303" s="21"/>
-      <c r="G303" s="21"/>
-      <c r="H303" s="21"/>
-      <c r="I303" s="21"/>
-      <c r="J303" s="21"/>
-      <c r="K303" s="21"/>
-    </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A304" s="22">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="297" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C297" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="D297" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="298" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C298" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="D298" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="299" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C299" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="D299" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="300" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C300" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="D300" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="301" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C301" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="D301" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="304" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B304" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A309" s="20"/>
+      <c r="B309" s="21"/>
+      <c r="C309" s="20"/>
+      <c r="D309" s="21"/>
+      <c r="E309" s="20"/>
+      <c r="F309" s="21"/>
+      <c r="G309" s="21"/>
+      <c r="H309" s="21"/>
+      <c r="I309" s="21"/>
+      <c r="J309" s="21"/>
+      <c r="K309" s="21"/>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A310" s="22">
         <v>13</v>
       </c>
-      <c r="B304" s="23" t="s">
-        <v>584</v>
-      </c>
-      <c r="C304" s="22" t="s">
-        <v>585</v>
-      </c>
-      <c r="D304" s="24" t="s">
-        <v>591</v>
-      </c>
-      <c r="E304" s="22" t="s">
-        <v>603</v>
-      </c>
-      <c r="F304" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="G304" s="24" t="s">
-        <v>605</v>
-      </c>
-      <c r="H304" s="24"/>
-      <c r="I304" s="24"/>
-      <c r="J304" s="24"/>
-      <c r="K304" s="24"/>
-    </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A305" s="22"/>
-      <c r="B305" s="24"/>
-      <c r="C305" s="22" t="s">
-        <v>586</v>
-      </c>
-      <c r="D305" s="24" t="s">
-        <v>593</v>
-      </c>
-      <c r="E305" s="22"/>
-      <c r="F305" s="24"/>
-      <c r="G305" s="24"/>
-      <c r="H305" s="24"/>
-      <c r="I305" s="24"/>
-      <c r="J305" s="24"/>
-      <c r="K305" s="24"/>
-    </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A306" s="22"/>
-      <c r="B306" s="24"/>
-      <c r="C306" s="22" t="s">
-        <v>587</v>
-      </c>
-      <c r="D306" s="24" t="s">
-        <v>592</v>
-      </c>
-      <c r="E306" s="22"/>
-      <c r="F306" s="24"/>
-      <c r="G306" s="24"/>
-      <c r="H306" s="24"/>
-      <c r="I306" s="24"/>
-      <c r="J306" s="24"/>
-      <c r="K306" s="24"/>
-    </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A307" s="22"/>
-      <c r="B307" s="24"/>
-      <c r="C307" s="22" t="s">
-        <v>588</v>
-      </c>
-      <c r="D307" s="24" t="s">
-        <v>594</v>
-      </c>
-      <c r="E307" s="22"/>
-      <c r="F307" s="24"/>
-      <c r="G307" s="24"/>
-      <c r="H307" s="24"/>
-      <c r="I307" s="24"/>
-      <c r="J307" s="24"/>
-      <c r="K307" s="24"/>
-    </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A308" s="22"/>
-      <c r="B308" s="24"/>
-      <c r="C308" s="22" t="s">
-        <v>589</v>
-      </c>
-      <c r="D308" s="24" t="s">
-        <v>595</v>
-      </c>
-      <c r="E308" s="22"/>
-      <c r="F308" s="24"/>
-      <c r="G308" s="24"/>
-      <c r="H308" s="24"/>
-      <c r="I308" s="24"/>
-      <c r="J308" s="24"/>
-      <c r="K308" s="24"/>
-    </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A309" s="22"/>
-      <c r="B309" s="24"/>
-      <c r="C309" s="22" t="s">
-        <v>590</v>
-      </c>
-      <c r="D309" s="24" t="s">
-        <v>596</v>
-      </c>
-      <c r="E309" s="22"/>
-      <c r="F309" s="24"/>
-      <c r="G309" s="24"/>
-      <c r="H309" s="24"/>
-      <c r="I309" s="24"/>
-      <c r="J309" s="24"/>
-      <c r="K309" s="24"/>
-    </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A310" s="22"/>
-      <c r="B310" s="24"/>
+      <c r="B310" s="23" t="s">
+        <v>546</v>
+      </c>
       <c r="C310" s="22" t="s">
-        <v>597</v>
+        <v>547</v>
       </c>
       <c r="D310" s="24" t="s">
-        <v>600</v>
-      </c>
-      <c r="E310" s="22"/>
-      <c r="F310" s="24"/>
-      <c r="G310" s="24"/>
+        <v>553</v>
+      </c>
+      <c r="E310" s="22" t="s">
+        <v>565</v>
+      </c>
+      <c r="F310" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="G310" s="24" t="s">
+        <v>567</v>
+      </c>
       <c r="H310" s="24"/>
       <c r="I310" s="24"/>
       <c r="J310" s="24"/>
@@ -6564,10 +6424,10 @@
       <c r="A311" s="22"/>
       <c r="B311" s="24"/>
       <c r="C311" s="22" t="s">
-        <v>598</v>
+        <v>548</v>
       </c>
       <c r="D311" s="24" t="s">
-        <v>601</v>
+        <v>555</v>
       </c>
       <c r="E311" s="22"/>
       <c r="F311" s="24"/>
@@ -6581,10 +6441,10 @@
       <c r="A312" s="22"/>
       <c r="B312" s="24"/>
       <c r="C312" s="22" t="s">
-        <v>599</v>
+        <v>549</v>
       </c>
       <c r="D312" s="24" t="s">
-        <v>602</v>
+        <v>554</v>
       </c>
       <c r="E312" s="22"/>
       <c r="F312" s="24"/>
@@ -6597,8 +6457,12 @@
     <row r="313" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A313" s="22"/>
       <c r="B313" s="24"/>
-      <c r="C313" s="22"/>
-      <c r="D313" s="24"/>
+      <c r="C313" s="22" t="s">
+        <v>550</v>
+      </c>
+      <c r="D313" s="24" t="s">
+        <v>556</v>
+      </c>
       <c r="E313" s="22"/>
       <c r="F313" s="24"/>
       <c r="G313" s="24"/>
@@ -6608,391 +6472,477 @@
       <c r="K313" s="24"/>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A314" s="20"/>
-      <c r="B314" s="21"/>
-      <c r="C314" s="20"/>
-      <c r="D314" s="21"/>
-      <c r="E314" s="20"/>
-      <c r="F314" s="21"/>
-      <c r="G314" s="21"/>
-      <c r="H314" s="21"/>
-      <c r="I314" s="21"/>
-      <c r="J314" s="21"/>
-      <c r="K314" s="21"/>
-    </row>
-    <row r="323" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C323" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="324" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C324" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="D324" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="325" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C325" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="D325" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="326" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C326" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="D326" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="327" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C327" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="D327" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="328" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C328" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="D328" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="329" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C329" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="D329" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="330" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C330" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="D330" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="331" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C331" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D331" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="332" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C332" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D332" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="333" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C333" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="D333" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="334" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="A314" s="22"/>
+      <c r="B314" s="24"/>
+      <c r="C314" s="22" t="s">
+        <v>551</v>
+      </c>
+      <c r="D314" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="E314" s="22"/>
+      <c r="F314" s="24"/>
+      <c r="G314" s="24"/>
+      <c r="H314" s="24"/>
+      <c r="I314" s="24"/>
+      <c r="J314" s="24"/>
+      <c r="K314" s="24"/>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A315" s="22"/>
+      <c r="B315" s="24"/>
+      <c r="C315" s="22" t="s">
+        <v>552</v>
+      </c>
+      <c r="D315" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="E315" s="22"/>
+      <c r="F315" s="24"/>
+      <c r="G315" s="24"/>
+      <c r="H315" s="24"/>
+      <c r="I315" s="24"/>
+      <c r="J315" s="24"/>
+      <c r="K315" s="24"/>
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A316" s="22"/>
+      <c r="B316" s="24"/>
+      <c r="C316" s="22" t="s">
+        <v>559</v>
+      </c>
+      <c r="D316" s="24" t="s">
+        <v>562</v>
+      </c>
+      <c r="E316" s="22"/>
+      <c r="F316" s="24"/>
+      <c r="G316" s="24"/>
+      <c r="H316" s="24"/>
+      <c r="I316" s="24"/>
+      <c r="J316" s="24"/>
+      <c r="K316" s="24"/>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A317" s="22"/>
+      <c r="B317" s="24"/>
+      <c r="C317" s="22" t="s">
+        <v>560</v>
+      </c>
+      <c r="D317" s="24" t="s">
+        <v>563</v>
+      </c>
+      <c r="E317" s="22"/>
+      <c r="F317" s="24"/>
+      <c r="G317" s="24"/>
+      <c r="H317" s="24"/>
+      <c r="I317" s="24"/>
+      <c r="J317" s="24"/>
+      <c r="K317" s="24"/>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A318" s="22"/>
+      <c r="B318" s="24"/>
+      <c r="C318" s="22" t="s">
+        <v>561</v>
+      </c>
+      <c r="D318" s="24" t="s">
+        <v>564</v>
+      </c>
+      <c r="E318" s="22"/>
+      <c r="F318" s="24"/>
+      <c r="G318" s="24"/>
+      <c r="H318" s="24"/>
+      <c r="I318" s="24"/>
+      <c r="J318" s="24"/>
+      <c r="K318" s="24"/>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A319" s="22"/>
+      <c r="B319" s="24"/>
+      <c r="C319" s="22"/>
+      <c r="D319" s="24"/>
+      <c r="E319" s="22"/>
+      <c r="F319" s="24"/>
+      <c r="G319" s="24"/>
+      <c r="H319" s="24"/>
+      <c r="I319" s="24"/>
+      <c r="J319" s="24"/>
+      <c r="K319" s="24"/>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A320" s="20"/>
+      <c r="B320" s="21"/>
+      <c r="C320" s="20"/>
+      <c r="D320" s="21"/>
+      <c r="E320" s="20"/>
+      <c r="F320" s="21"/>
+      <c r="G320" s="21"/>
+      <c r="H320" s="21"/>
+      <c r="I320" s="21"/>
+      <c r="J320" s="21"/>
+      <c r="K320" s="21"/>
+    </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A322" s="4">
+        <v>14</v>
+      </c>
+      <c r="B322" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="C322" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="D322" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="E322" s="4"/>
+      <c r="F322" s="5"/>
+      <c r="G322" s="5"/>
+      <c r="H322" s="5"/>
+      <c r="I322" s="5"/>
+      <c r="J322" s="5"/>
+      <c r="K322" s="5"/>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A323" s="4"/>
+      <c r="B323" s="5"/>
+      <c r="C323" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="D323" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="E323" s="4"/>
+      <c r="F323" s="5"/>
+      <c r="G323" s="5"/>
+      <c r="H323" s="5"/>
+      <c r="I323" s="5"/>
+      <c r="J323" s="5"/>
+      <c r="K323" s="5"/>
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A324" s="4"/>
+      <c r="B324" s="5"/>
+      <c r="C324" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="D324" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="E324" s="4"/>
+      <c r="F324" s="5"/>
+      <c r="G324" s="5"/>
+      <c r="H324" s="5"/>
+      <c r="I324" s="5"/>
+      <c r="J324" s="5"/>
+      <c r="K324" s="5"/>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A325" s="4"/>
+      <c r="B325" s="5"/>
+      <c r="C325" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="D325" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="E325" s="4"/>
+      <c r="F325" s="5"/>
+      <c r="G325" s="5"/>
+      <c r="H325" s="5"/>
+      <c r="I325" s="5"/>
+      <c r="J325" s="5"/>
+      <c r="K325" s="5"/>
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A326" s="4"/>
+      <c r="B326" s="5"/>
+      <c r="C326" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="D326" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="E326" s="4"/>
+      <c r="F326" s="5"/>
+      <c r="G326" s="5"/>
+      <c r="H326" s="5"/>
+      <c r="I326" s="5"/>
+      <c r="J326" s="5"/>
+      <c r="K326" s="5"/>
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A327" s="4"/>
+      <c r="B327" s="5"/>
+      <c r="C327" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="D327" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="E327" s="4"/>
+      <c r="F327" s="5"/>
+      <c r="G327" s="5"/>
+      <c r="H327" s="5"/>
+      <c r="I327" s="5"/>
+      <c r="J327" s="5"/>
+      <c r="K327" s="5"/>
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A328" s="4"/>
+      <c r="B328" s="5"/>
+      <c r="C328" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="D328" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="E328" s="4"/>
+      <c r="F328" s="5"/>
+      <c r="G328" s="5"/>
+      <c r="H328" s="5"/>
+      <c r="I328" s="5"/>
+      <c r="J328" s="5"/>
+      <c r="K328" s="5"/>
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A329" s="4"/>
+      <c r="B329" s="5"/>
+      <c r="C329" s="4"/>
+      <c r="D329" s="5"/>
+      <c r="E329" s="4"/>
+      <c r="F329" s="5"/>
+      <c r="G329" s="5"/>
+      <c r="H329" s="5"/>
+      <c r="I329" s="5"/>
+      <c r="J329" s="5"/>
+      <c r="K329" s="5"/>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A330" s="4"/>
+      <c r="B330" s="5"/>
+      <c r="C330" s="4"/>
+      <c r="D330" s="5"/>
+      <c r="E330" s="4"/>
+      <c r="F330" s="5"/>
+      <c r="G330" s="5"/>
+      <c r="H330" s="5"/>
+      <c r="I330" s="5"/>
+      <c r="J330" s="5"/>
+      <c r="K330" s="5"/>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A331" s="4"/>
+      <c r="B331" s="5"/>
+      <c r="C331" s="4"/>
+      <c r="D331" s="5"/>
+      <c r="E331" s="4"/>
+      <c r="F331" s="5"/>
+      <c r="G331" s="5"/>
+      <c r="H331" s="5"/>
+      <c r="I331" s="5"/>
+      <c r="J331" s="5"/>
+      <c r="K331" s="5"/>
+    </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A332" s="4"/>
+      <c r="B332" s="5"/>
+      <c r="C332" s="4"/>
+      <c r="D332" s="5"/>
+      <c r="E332" s="4"/>
+      <c r="F332" s="5"/>
+      <c r="G332" s="5"/>
+      <c r="H332" s="5"/>
+      <c r="I332" s="5"/>
+      <c r="J332" s="5"/>
+      <c r="K332" s="5"/>
+    </row>
+    <row r="334" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C334" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D334" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="335" spans="3:4" x14ac:dyDescent="0.35">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C335" s="1" t="s">
-        <v>449</v>
+        <v>389</v>
       </c>
       <c r="D335" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="336" spans="3:4" x14ac:dyDescent="0.35">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="336" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C336" s="1" t="s">
-        <v>450</v>
+        <v>391</v>
       </c>
       <c r="D336" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.35">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="337" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C337" s="1" t="s">
-        <v>452</v>
+        <v>393</v>
       </c>
       <c r="D337" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.35">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="338" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C338" s="1" t="s">
-        <v>454</v>
+        <v>395</v>
       </c>
       <c r="D338" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.35">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="339" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C339" s="1" t="s">
-        <v>456</v>
+        <v>397</v>
       </c>
       <c r="D339" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.35">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="340" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C340" s="1" t="s">
-        <v>458</v>
+        <v>399</v>
       </c>
       <c r="D340" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.35">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="341" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C341" s="1" t="s">
-        <v>460</v>
+        <v>401</v>
       </c>
       <c r="D341" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.35">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="342" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C342" s="1" t="s">
+        <v>403</v>
+      </c>
       <c r="D342" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A343" s="26"/>
-      <c r="B343" s="25"/>
-      <c r="C343" s="26"/>
-      <c r="D343" s="25"/>
-      <c r="E343" s="26"/>
-      <c r="F343" s="25"/>
-      <c r="G343" s="25"/>
-      <c r="H343" s="25"/>
-      <c r="I343" s="25"/>
-      <c r="J343" s="25"/>
-      <c r="K343" s="25"/>
-    </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A344" s="39">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="343" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C343" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="D343" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="344" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C344" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D344" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="345" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C345" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D345" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="346" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C346" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D346" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="347" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C347" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D347" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="348" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C348" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D348" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="349" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C349" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D349" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="350" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C350" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D350" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="351" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C351" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D351" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="352" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C352" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D352" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="353" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D353" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="354" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A354" s="26"/>
+      <c r="B354" s="25"/>
+      <c r="C354" s="26"/>
+      <c r="D354" s="25"/>
+      <c r="E354" s="26"/>
+      <c r="F354" s="25"/>
+      <c r="G354" s="25"/>
+      <c r="H354" s="25"/>
+      <c r="I354" s="25"/>
+      <c r="J354" s="25"/>
+      <c r="K354" s="25"/>
+    </row>
+    <row r="355" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A355" s="39">
         <v>16</v>
       </c>
-      <c r="B344" s="40" t="s">
-        <v>423</v>
-      </c>
-      <c r="C344" s="41" t="s">
-        <v>375</v>
-      </c>
-      <c r="D344" s="42" t="s">
-        <v>387</v>
-      </c>
-      <c r="E344" s="39" t="s">
-        <v>603</v>
-      </c>
-      <c r="F344" s="42" t="s">
-        <v>423</v>
-      </c>
-      <c r="G344" s="42"/>
-      <c r="H344" s="42"/>
-      <c r="I344" s="42"/>
-      <c r="J344" s="42"/>
-      <c r="K344" s="42"/>
-    </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A345" s="39"/>
-      <c r="B345" s="42"/>
-      <c r="C345" s="41" t="s">
-        <v>376</v>
-      </c>
-      <c r="D345" s="42" t="s">
-        <v>388</v>
-      </c>
-      <c r="E345" s="39"/>
-      <c r="F345" s="42"/>
-      <c r="G345" s="42"/>
-      <c r="H345" s="42"/>
-      <c r="I345" s="42"/>
-      <c r="J345" s="42"/>
-      <c r="K345" s="42"/>
-    </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A346" s="39"/>
-      <c r="B346" s="42"/>
-      <c r="C346" s="41" t="s">
-        <v>377</v>
-      </c>
-      <c r="D346" s="42" t="s">
-        <v>389</v>
-      </c>
-      <c r="E346" s="39"/>
-      <c r="F346" s="42"/>
-      <c r="G346" s="42"/>
-      <c r="H346" s="42"/>
-      <c r="I346" s="42"/>
-      <c r="J346" s="42"/>
-      <c r="K346" s="42"/>
-    </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A347" s="39"/>
-      <c r="B347" s="42"/>
-      <c r="C347" s="41" t="s">
-        <v>378</v>
-      </c>
-      <c r="D347" s="42" t="s">
-        <v>390</v>
-      </c>
-      <c r="E347" s="39"/>
-      <c r="F347" s="42"/>
-      <c r="G347" s="42"/>
-      <c r="H347" s="42"/>
-      <c r="I347" s="42"/>
-      <c r="J347" s="42"/>
-      <c r="K347" s="42"/>
-    </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A348" s="39"/>
-      <c r="B348" s="42"/>
-      <c r="C348" s="41" t="s">
-        <v>379</v>
-      </c>
-      <c r="D348" s="42" t="s">
-        <v>391</v>
-      </c>
-      <c r="E348" s="39"/>
-      <c r="F348" s="42"/>
-      <c r="G348" s="42"/>
-      <c r="H348" s="42"/>
-      <c r="I348" s="42"/>
-      <c r="J348" s="42"/>
-      <c r="K348" s="42"/>
-    </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A349" s="39"/>
-      <c r="B349" s="42"/>
-      <c r="C349" s="41" t="s">
-        <v>380</v>
-      </c>
-      <c r="D349" s="42" t="s">
-        <v>392</v>
-      </c>
-      <c r="E349" s="39"/>
-      <c r="F349" s="42"/>
-      <c r="G349" s="42"/>
-      <c r="H349" s="42"/>
-      <c r="I349" s="42"/>
-      <c r="J349" s="42"/>
-      <c r="K349" s="42"/>
-    </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A350" s="39"/>
-      <c r="B350" s="42"/>
-      <c r="C350" s="41" t="s">
-        <v>381</v>
-      </c>
-      <c r="D350" s="42" t="s">
-        <v>393</v>
-      </c>
-      <c r="E350" s="39"/>
-      <c r="F350" s="42"/>
-      <c r="G350" s="42"/>
-      <c r="H350" s="42"/>
-      <c r="I350" s="42"/>
-      <c r="J350" s="42"/>
-      <c r="K350" s="42"/>
-    </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A351" s="39"/>
-      <c r="B351" s="42"/>
-      <c r="C351" s="41" t="s">
-        <v>382</v>
-      </c>
-      <c r="D351" s="42" t="s">
-        <v>394</v>
-      </c>
-      <c r="E351" s="39"/>
-      <c r="F351" s="42"/>
-      <c r="G351" s="42"/>
-      <c r="H351" s="42"/>
-      <c r="I351" s="42"/>
-      <c r="J351" s="42"/>
-      <c r="K351" s="42"/>
-    </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A352" s="39"/>
-      <c r="B352" s="42"/>
-      <c r="C352" s="41" t="s">
-        <v>383</v>
-      </c>
-      <c r="D352" s="42" t="s">
-        <v>395</v>
-      </c>
-      <c r="E352" s="39"/>
-      <c r="F352" s="42"/>
-      <c r="G352" s="42"/>
-      <c r="H352" s="42"/>
-      <c r="I352" s="42"/>
-      <c r="J352" s="42"/>
-      <c r="K352" s="42"/>
-    </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A353" s="39"/>
-      <c r="B353" s="42"/>
-      <c r="C353" s="41" t="s">
-        <v>384</v>
-      </c>
-      <c r="D353" s="42" t="s">
-        <v>397</v>
-      </c>
-      <c r="E353" s="39"/>
-      <c r="F353" s="42"/>
-      <c r="G353" s="42"/>
-      <c r="H353" s="42"/>
-      <c r="I353" s="42"/>
-      <c r="J353" s="42"/>
-      <c r="K353" s="42"/>
-    </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A354" s="39"/>
-      <c r="B354" s="42"/>
-      <c r="C354" s="41" t="s">
+      <c r="B355" s="40" t="s">
         <v>385</v>
       </c>
-      <c r="D354" s="42" t="s">
-        <v>396</v>
-      </c>
-      <c r="E354" s="39"/>
-      <c r="F354" s="42"/>
-      <c r="G354" s="42"/>
-      <c r="H354" s="42"/>
-      <c r="I354" s="42"/>
-      <c r="J354" s="42"/>
-      <c r="K354" s="42"/>
-    </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A355" s="39"/>
-      <c r="B355" s="42"/>
       <c r="C355" s="41" t="s">
-        <v>386</v>
+        <v>337</v>
       </c>
       <c r="D355" s="42" t="s">
-        <v>398</v>
-      </c>
-      <c r="E355" s="39"/>
-      <c r="F355" s="42"/>
+        <v>349</v>
+      </c>
+      <c r="E355" s="39" t="s">
+        <v>565</v>
+      </c>
+      <c r="F355" s="42" t="s">
+        <v>385</v>
+      </c>
       <c r="G355" s="42"/>
       <c r="H355" s="42"/>
       <c r="I355" s="42"/>
@@ -7003,10 +6953,10 @@
       <c r="A356" s="39"/>
       <c r="B356" s="42"/>
       <c r="C356" s="41" t="s">
-        <v>410</v>
+        <v>338</v>
       </c>
       <c r="D356" s="42" t="s">
-        <v>399</v>
+        <v>350</v>
       </c>
       <c r="E356" s="39"/>
       <c r="F356" s="42"/>
@@ -7020,10 +6970,10 @@
       <c r="A357" s="39"/>
       <c r="B357" s="42"/>
       <c r="C357" s="41" t="s">
-        <v>411</v>
+        <v>339</v>
       </c>
       <c r="D357" s="42" t="s">
-        <v>400</v>
+        <v>351</v>
       </c>
       <c r="E357" s="39"/>
       <c r="F357" s="42"/>
@@ -7037,10 +6987,10 @@
       <c r="A358" s="39"/>
       <c r="B358" s="42"/>
       <c r="C358" s="41" t="s">
-        <v>412</v>
+        <v>340</v>
       </c>
       <c r="D358" s="42" t="s">
-        <v>401</v>
+        <v>352</v>
       </c>
       <c r="E358" s="39"/>
       <c r="F358" s="42"/>
@@ -7054,10 +7004,10 @@
       <c r="A359" s="39"/>
       <c r="B359" s="42"/>
       <c r="C359" s="41" t="s">
-        <v>413</v>
+        <v>341</v>
       </c>
       <c r="D359" s="42" t="s">
-        <v>402</v>
+        <v>353</v>
       </c>
       <c r="E359" s="39"/>
       <c r="F359" s="42"/>
@@ -7071,10 +7021,10 @@
       <c r="A360" s="39"/>
       <c r="B360" s="42"/>
       <c r="C360" s="41" t="s">
-        <v>414</v>
+        <v>342</v>
       </c>
       <c r="D360" s="42" t="s">
-        <v>403</v>
+        <v>354</v>
       </c>
       <c r="E360" s="39"/>
       <c r="F360" s="42"/>
@@ -7088,10 +7038,10 @@
       <c r="A361" s="39"/>
       <c r="B361" s="42"/>
       <c r="C361" s="41" t="s">
-        <v>415</v>
+        <v>343</v>
       </c>
       <c r="D361" s="42" t="s">
-        <v>404</v>
+        <v>355</v>
       </c>
       <c r="E361" s="39"/>
       <c r="F361" s="42"/>
@@ -7105,10 +7055,10 @@
       <c r="A362" s="39"/>
       <c r="B362" s="42"/>
       <c r="C362" s="41" t="s">
-        <v>416</v>
+        <v>344</v>
       </c>
       <c r="D362" s="42" t="s">
-        <v>405</v>
+        <v>356</v>
       </c>
       <c r="E362" s="39"/>
       <c r="F362" s="42"/>
@@ -7122,10 +7072,10 @@
       <c r="A363" s="39"/>
       <c r="B363" s="42"/>
       <c r="C363" s="41" t="s">
-        <v>417</v>
+        <v>345</v>
       </c>
       <c r="D363" s="42" t="s">
-        <v>406</v>
+        <v>357</v>
       </c>
       <c r="E363" s="39"/>
       <c r="F363" s="42"/>
@@ -7139,10 +7089,10 @@
       <c r="A364" s="39"/>
       <c r="B364" s="42"/>
       <c r="C364" s="41" t="s">
-        <v>418</v>
+        <v>346</v>
       </c>
       <c r="D364" s="42" t="s">
-        <v>407</v>
+        <v>359</v>
       </c>
       <c r="E364" s="39"/>
       <c r="F364" s="42"/>
@@ -7156,10 +7106,10 @@
       <c r="A365" s="39"/>
       <c r="B365" s="42"/>
       <c r="C365" s="41" t="s">
-        <v>419</v>
+        <v>347</v>
       </c>
       <c r="D365" s="42" t="s">
-        <v>408</v>
+        <v>358</v>
       </c>
       <c r="E365" s="39"/>
       <c r="F365" s="42"/>
@@ -7173,10 +7123,10 @@
       <c r="A366" s="39"/>
       <c r="B366" s="42"/>
       <c r="C366" s="41" t="s">
-        <v>420</v>
+        <v>348</v>
       </c>
       <c r="D366" s="42" t="s">
-        <v>409</v>
+        <v>360</v>
       </c>
       <c r="E366" s="39"/>
       <c r="F366" s="42"/>
@@ -7190,10 +7140,10 @@
       <c r="A367" s="39"/>
       <c r="B367" s="42"/>
       <c r="C367" s="41" t="s">
-        <v>421</v>
+        <v>372</v>
       </c>
       <c r="D367" s="42" t="s">
-        <v>422</v>
+        <v>361</v>
       </c>
       <c r="E367" s="39"/>
       <c r="F367" s="42"/>
@@ -7204,443 +7154,465 @@
       <c r="K367" s="42"/>
     </row>
     <row r="368" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A368" s="26"/>
-      <c r="B368" s="25"/>
-      <c r="C368" s="26"/>
-      <c r="D368" s="25"/>
-      <c r="E368" s="26"/>
-      <c r="F368" s="25"/>
-      <c r="G368" s="25"/>
-      <c r="H368" s="25"/>
-      <c r="I368" s="25"/>
-      <c r="J368" s="25"/>
-      <c r="K368" s="25"/>
-    </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A369" s="32"/>
-      <c r="B369" s="33" t="s">
-        <v>462</v>
-      </c>
-      <c r="C369" s="32" t="s">
-        <v>463</v>
-      </c>
-      <c r="D369" s="38" t="s">
-        <v>464</v>
-      </c>
-      <c r="E369" s="32"/>
-      <c r="F369" s="33"/>
-      <c r="G369" s="33"/>
-    </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A370" s="4"/>
-      <c r="B370" s="5"/>
-      <c r="C370" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="D370" s="18" t="s">
-        <v>466</v>
-      </c>
-      <c r="E370" s="4"/>
-      <c r="F370" s="5"/>
-      <c r="G370" s="5"/>
-    </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A372" s="4"/>
-      <c r="B372" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="C372" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="D372" s="16" t="s">
-        <v>467</v>
-      </c>
-      <c r="E372" s="4"/>
-      <c r="F372" s="5"/>
-      <c r="G372" s="5"/>
-    </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A373" s="4"/>
-      <c r="B373" s="5"/>
-      <c r="C373" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="D373" s="16" t="s">
-        <v>468</v>
-      </c>
-      <c r="E373" s="4"/>
-      <c r="F373" s="5"/>
-      <c r="G373" s="5"/>
-    </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A374" s="4"/>
-      <c r="B374" s="5"/>
-      <c r="C374" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="D374" s="16" t="s">
-        <v>469</v>
-      </c>
-      <c r="E374" s="4"/>
-      <c r="F374" s="5"/>
-      <c r="G374" s="5"/>
-    </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A375" s="4"/>
-      <c r="B375" s="5"/>
-      <c r="C375" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="D375" s="16" t="s">
-        <v>470</v>
-      </c>
-      <c r="E375" s="4"/>
-      <c r="F375" s="5"/>
-      <c r="G375" s="5"/>
-    </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A376" s="4"/>
-      <c r="B376" s="5"/>
-      <c r="C376" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="D376" s="16" t="s">
-        <v>471</v>
-      </c>
-      <c r="E376" s="4"/>
-      <c r="F376" s="5"/>
-      <c r="G376" s="5"/>
-    </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A377" s="4"/>
-      <c r="B377" s="5"/>
-      <c r="C377" s="4"/>
-      <c r="D377" s="5"/>
-      <c r="E377" s="4"/>
-      <c r="F377" s="5"/>
-      <c r="G377" s="5"/>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A378" s="4"/>
-      <c r="B378" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="C378" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="D378" s="16" t="s">
-        <v>488</v>
-      </c>
-      <c r="E378" s="4"/>
-      <c r="F378" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="G378" s="5"/>
-    </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A379" s="4"/>
-      <c r="B379" s="5"/>
-      <c r="C379" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="D379" s="16" t="s">
-        <v>489</v>
-      </c>
-      <c r="E379" s="4"/>
-      <c r="F379" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="G379" s="5"/>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A380" s="4"/>
-      <c r="B380" s="5"/>
-      <c r="C380" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="D380" s="16" t="s">
-        <v>490</v>
-      </c>
-      <c r="E380" s="4"/>
-      <c r="F380" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="G380" s="5"/>
-    </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A368" s="39"/>
+      <c r="B368" s="42"/>
+      <c r="C368" s="41" t="s">
+        <v>373</v>
+      </c>
+      <c r="D368" s="42" t="s">
+        <v>362</v>
+      </c>
+      <c r="E368" s="39"/>
+      <c r="F368" s="42"/>
+      <c r="G368" s="42"/>
+      <c r="H368" s="42"/>
+      <c r="I368" s="42"/>
+      <c r="J368" s="42"/>
+      <c r="K368" s="42"/>
+    </row>
+    <row r="369" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A369" s="39"/>
+      <c r="B369" s="42"/>
+      <c r="C369" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="D369" s="42" t="s">
+        <v>363</v>
+      </c>
+      <c r="E369" s="39"/>
+      <c r="F369" s="42"/>
+      <c r="G369" s="42"/>
+      <c r="H369" s="42"/>
+      <c r="I369" s="42"/>
+      <c r="J369" s="42"/>
+      <c r="K369" s="42"/>
+    </row>
+    <row r="370" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A370" s="39"/>
+      <c r="B370" s="42"/>
+      <c r="C370" s="41" t="s">
+        <v>375</v>
+      </c>
+      <c r="D370" s="42" t="s">
+        <v>364</v>
+      </c>
+      <c r="E370" s="39"/>
+      <c r="F370" s="42"/>
+      <c r="G370" s="42"/>
+      <c r="H370" s="42"/>
+      <c r="I370" s="42"/>
+      <c r="J370" s="42"/>
+      <c r="K370" s="42"/>
+    </row>
+    <row r="371" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A371" s="39"/>
+      <c r="B371" s="42"/>
+      <c r="C371" s="41" t="s">
+        <v>376</v>
+      </c>
+      <c r="D371" s="42" t="s">
+        <v>365</v>
+      </c>
+      <c r="E371" s="39"/>
+      <c r="F371" s="42"/>
+      <c r="G371" s="42"/>
+      <c r="H371" s="42"/>
+      <c r="I371" s="42"/>
+      <c r="J371" s="42"/>
+      <c r="K371" s="42"/>
+    </row>
+    <row r="372" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A372" s="39"/>
+      <c r="B372" s="42"/>
+      <c r="C372" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="D372" s="42" t="s">
+        <v>366</v>
+      </c>
+      <c r="E372" s="39"/>
+      <c r="F372" s="42"/>
+      <c r="G372" s="42"/>
+      <c r="H372" s="42"/>
+      <c r="I372" s="42"/>
+      <c r="J372" s="42"/>
+      <c r="K372" s="42"/>
+    </row>
+    <row r="373" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A373" s="39"/>
+      <c r="B373" s="42"/>
+      <c r="C373" s="41" t="s">
+        <v>378</v>
+      </c>
+      <c r="D373" s="42" t="s">
+        <v>367</v>
+      </c>
+      <c r="E373" s="39"/>
+      <c r="F373" s="42"/>
+      <c r="G373" s="42"/>
+      <c r="H373" s="42"/>
+      <c r="I373" s="42"/>
+      <c r="J373" s="42"/>
+      <c r="K373" s="42"/>
+    </row>
+    <row r="374" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A374" s="39"/>
+      <c r="B374" s="42"/>
+      <c r="C374" s="41" t="s">
+        <v>379</v>
+      </c>
+      <c r="D374" s="42" t="s">
+        <v>368</v>
+      </c>
+      <c r="E374" s="39"/>
+      <c r="F374" s="42"/>
+      <c r="G374" s="42"/>
+      <c r="H374" s="42"/>
+      <c r="I374" s="42"/>
+      <c r="J374" s="42"/>
+      <c r="K374" s="42"/>
+    </row>
+    <row r="375" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A375" s="39"/>
+      <c r="B375" s="42"/>
+      <c r="C375" s="41" t="s">
+        <v>380</v>
+      </c>
+      <c r="D375" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="E375" s="39"/>
+      <c r="F375" s="42"/>
+      <c r="G375" s="42"/>
+      <c r="H375" s="42"/>
+      <c r="I375" s="42"/>
+      <c r="J375" s="42"/>
+      <c r="K375" s="42"/>
+    </row>
+    <row r="376" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A376" s="39"/>
+      <c r="B376" s="42"/>
+      <c r="C376" s="41" t="s">
+        <v>381</v>
+      </c>
+      <c r="D376" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="E376" s="39"/>
+      <c r="F376" s="42"/>
+      <c r="G376" s="42"/>
+      <c r="H376" s="42"/>
+      <c r="I376" s="42"/>
+      <c r="J376" s="42"/>
+      <c r="K376" s="42"/>
+    </row>
+    <row r="377" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A377" s="39"/>
+      <c r="B377" s="42"/>
+      <c r="C377" s="41" t="s">
+        <v>382</v>
+      </c>
+      <c r="D377" s="42" t="s">
+        <v>371</v>
+      </c>
+      <c r="E377" s="39"/>
+      <c r="F377" s="42"/>
+      <c r="G377" s="42"/>
+      <c r="H377" s="42"/>
+      <c r="I377" s="42"/>
+      <c r="J377" s="42"/>
+      <c r="K377" s="42"/>
+    </row>
+    <row r="378" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A378" s="39"/>
+      <c r="B378" s="42"/>
+      <c r="C378" s="41" t="s">
+        <v>383</v>
+      </c>
+      <c r="D378" s="42" t="s">
+        <v>384</v>
+      </c>
+      <c r="E378" s="39"/>
+      <c r="F378" s="42"/>
+      <c r="G378" s="42"/>
+      <c r="H378" s="42"/>
+      <c r="I378" s="42"/>
+      <c r="J378" s="42"/>
+      <c r="K378" s="42"/>
+    </row>
+    <row r="379" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A379" s="26"/>
+      <c r="B379" s="25"/>
+      <c r="C379" s="26"/>
+      <c r="D379" s="25"/>
+      <c r="E379" s="26"/>
+      <c r="F379" s="25"/>
+      <c r="G379" s="25"/>
+      <c r="H379" s="25"/>
+      <c r="I379" s="25"/>
+      <c r="J379" s="25"/>
+      <c r="K379" s="25"/>
+    </row>
+    <row r="380" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A380" s="32"/>
+      <c r="B380" s="33" t="s">
+        <v>424</v>
+      </c>
+      <c r="C380" s="32" t="s">
+        <v>425</v>
+      </c>
+      <c r="D380" s="38" t="s">
+        <v>426</v>
+      </c>
+      <c r="E380" s="32"/>
+      <c r="F380" s="33"/>
+      <c r="G380" s="33"/>
+    </row>
+    <row r="381" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A381" s="4"/>
       <c r="B381" s="5"/>
       <c r="C381" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="D381" s="16" t="s">
-        <v>492</v>
+        <v>427</v>
+      </c>
+      <c r="D381" s="18" t="s">
+        <v>428</v>
       </c>
       <c r="E381" s="4"/>
-      <c r="F381" s="5" t="s">
-        <v>491</v>
-      </c>
+      <c r="F381" s="5"/>
       <c r="G381" s="5"/>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A382" s="4"/>
-      <c r="B382" s="5"/>
-      <c r="C382" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="D382" s="16" t="s">
-        <v>478</v>
-      </c>
-      <c r="E382" s="4"/>
-      <c r="F382" s="5"/>
-      <c r="G382" s="5"/>
-    </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A383" s="4"/>
-      <c r="B383" s="5"/>
-      <c r="C383" s="4"/>
-      <c r="D383" s="5"/>
+      <c r="B383" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="C383" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D383" s="16" t="s">
+        <v>429</v>
+      </c>
       <c r="E383" s="4"/>
       <c r="F383" s="5"/>
       <c r="G383" s="5"/>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A384" s="4"/>
-      <c r="B384" s="5" t="s">
-        <v>479</v>
-      </c>
+      <c r="B384" s="5"/>
       <c r="C384" s="4" t="s">
-        <v>480</v>
+        <v>430</v>
       </c>
       <c r="D384" s="16" t="s">
-        <v>480</v>
+        <v>430</v>
       </c>
       <c r="E384" s="4"/>
       <c r="F384" s="5"/>
       <c r="G384" s="5"/>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A385" s="4"/>
       <c r="B385" s="5"/>
       <c r="C385" s="4" t="s">
-        <v>481</v>
+        <v>431</v>
       </c>
       <c r="D385" s="16" t="s">
-        <v>481</v>
+        <v>431</v>
       </c>
       <c r="E385" s="4"/>
       <c r="F385" s="5"/>
       <c r="G385" s="5"/>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A386" s="4"/>
       <c r="B386" s="5"/>
       <c r="C386" s="4" t="s">
-        <v>482</v>
+        <v>432</v>
       </c>
       <c r="D386" s="16" t="s">
-        <v>482</v>
+        <v>432</v>
       </c>
       <c r="E386" s="4"/>
       <c r="F386" s="5"/>
       <c r="G386" s="5"/>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A387" s="4"/>
       <c r="B387" s="5"/>
       <c r="C387" s="4" t="s">
-        <v>483</v>
+        <v>433</v>
       </c>
       <c r="D387" s="16" t="s">
-        <v>483</v>
+        <v>433</v>
       </c>
       <c r="E387" s="4"/>
       <c r="F387" s="5"/>
       <c r="G387" s="5"/>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A388" s="4"/>
       <c r="B388" s="5"/>
-      <c r="C388" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="D388" s="16" t="s">
-        <v>484</v>
-      </c>
+      <c r="C388" s="4"/>
+      <c r="D388" s="5"/>
       <c r="E388" s="4"/>
       <c r="F388" s="5"/>
       <c r="G388" s="5"/>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A391" s="43">
-        <v>20</v>
-      </c>
-      <c r="B391" s="44" t="s">
-        <v>608</v>
-      </c>
-      <c r="C391" s="43" t="s">
-        <v>609</v>
-      </c>
-      <c r="D391" s="45" t="s">
-        <v>611</v>
-      </c>
-      <c r="E391" s="43" t="s">
-        <v>613</v>
-      </c>
-      <c r="F391" s="44"/>
-      <c r="G391" s="44"/>
-      <c r="H391" s="44"/>
-      <c r="I391" s="44"/>
-      <c r="J391" s="44"/>
-      <c r="K391" s="44"/>
-    </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A392" s="43"/>
-      <c r="B392" s="44"/>
-      <c r="C392" s="43" t="s">
-        <v>610</v>
-      </c>
-      <c r="D392" s="45" t="s">
-        <v>612</v>
-      </c>
-      <c r="E392" s="43" t="s">
-        <v>613</v>
-      </c>
-      <c r="F392" s="44"/>
-      <c r="G392" s="44"/>
-      <c r="H392" s="44"/>
-      <c r="I392" s="44"/>
-      <c r="J392" s="44"/>
-      <c r="K392" s="44"/>
-    </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A393" s="43"/>
-      <c r="B393" s="44"/>
-      <c r="C393" s="43" t="s">
-        <v>614</v>
-      </c>
-      <c r="D393" s="44" t="s">
-        <v>615</v>
-      </c>
-      <c r="E393" s="43" t="s">
-        <v>616</v>
-      </c>
-      <c r="F393" s="44"/>
-      <c r="G393" s="44"/>
-      <c r="H393" s="44"/>
-      <c r="I393" s="44"/>
-      <c r="J393" s="44"/>
-      <c r="K393" s="44"/>
-    </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A394" s="43"/>
-      <c r="B394" s="44"/>
-      <c r="C394" s="43"/>
-      <c r="D394" s="44"/>
-      <c r="E394" s="43"/>
-      <c r="F394" s="44"/>
-      <c r="G394" s="44"/>
-      <c r="H394" s="44"/>
-      <c r="I394" s="44"/>
-      <c r="J394" s="44"/>
-      <c r="K394" s="44"/>
-    </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A395" s="43"/>
-      <c r="B395" s="44"/>
-      <c r="C395" s="43"/>
-      <c r="D395" s="44"/>
-      <c r="E395" s="43"/>
-      <c r="F395" s="44"/>
-      <c r="G395" s="44"/>
-      <c r="H395" s="44"/>
-      <c r="I395" s="44"/>
-      <c r="J395" s="44"/>
-      <c r="K395" s="44"/>
-    </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A396" s="43"/>
-      <c r="B396" s="44"/>
-      <c r="C396" s="43"/>
-      <c r="D396" s="44"/>
-      <c r="E396" s="43"/>
-      <c r="F396" s="44"/>
-      <c r="G396" s="44"/>
-      <c r="H396" s="44"/>
-      <c r="I396" s="44"/>
-      <c r="J396" s="44"/>
-      <c r="K396" s="44"/>
-    </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A397" s="43"/>
-      <c r="B397" s="44"/>
-      <c r="C397" s="43"/>
-      <c r="D397" s="44"/>
-      <c r="E397" s="43"/>
-      <c r="F397" s="44"/>
-      <c r="G397" s="44"/>
-      <c r="H397" s="44"/>
-      <c r="I397" s="44"/>
-      <c r="J397" s="44"/>
-      <c r="K397" s="44"/>
-    </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A398" s="43"/>
-      <c r="B398" s="44"/>
-      <c r="C398" s="43"/>
-      <c r="D398" s="44"/>
-      <c r="E398" s="43"/>
-      <c r="F398" s="44"/>
-      <c r="G398" s="44"/>
-      <c r="H398" s="44"/>
-      <c r="I398" s="44"/>
-      <c r="J398" s="44"/>
-      <c r="K398" s="44"/>
-    </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A399" s="43"/>
-      <c r="B399" s="44"/>
-      <c r="C399" s="43"/>
-      <c r="D399" s="44"/>
-      <c r="E399" s="43"/>
-      <c r="F399" s="44"/>
-      <c r="G399" s="44"/>
-      <c r="H399" s="44"/>
-      <c r="I399" s="44"/>
-      <c r="J399" s="44"/>
-      <c r="K399" s="44"/>
-    </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A400" s="43"/>
-      <c r="B400" s="44"/>
-      <c r="C400" s="43"/>
-      <c r="D400" s="44"/>
-      <c r="E400" s="43"/>
-      <c r="F400" s="44"/>
-      <c r="G400" s="44"/>
-      <c r="H400" s="44"/>
-      <c r="I400" s="44"/>
-      <c r="J400" s="44"/>
-      <c r="K400" s="44"/>
-    </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A401" s="43"/>
-      <c r="B401" s="44"/>
-      <c r="C401" s="43"/>
-      <c r="D401" s="44"/>
-      <c r="E401" s="43"/>
-      <c r="F401" s="44"/>
-      <c r="G401" s="44"/>
-      <c r="H401" s="44"/>
-      <c r="I401" s="44"/>
-      <c r="J401" s="44"/>
-      <c r="K401" s="44"/>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A389" s="4"/>
+      <c r="B389" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C389" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="D389" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="E389" s="4"/>
+      <c r="F389" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="G389" s="5"/>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A390" s="4"/>
+      <c r="B390" s="5"/>
+      <c r="C390" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="D390" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="E390" s="4"/>
+      <c r="F390" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="G390" s="5"/>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A391" s="4"/>
+      <c r="B391" s="5"/>
+      <c r="C391" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D391" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="E391" s="4"/>
+      <c r="F391" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="G391" s="5"/>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A392" s="4"/>
+      <c r="B392" s="5"/>
+      <c r="C392" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D392" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="E392" s="4"/>
+      <c r="F392" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="G392" s="5"/>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A393" s="4"/>
+      <c r="B393" s="5"/>
+      <c r="C393" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="D393" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="E393" s="4"/>
+      <c r="F393" s="5"/>
+      <c r="G393" s="5"/>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A394" s="4"/>
+      <c r="B394" s="5"/>
+      <c r="C394" s="4"/>
+      <c r="D394" s="5"/>
+      <c r="E394" s="4"/>
+      <c r="F394" s="5"/>
+      <c r="G394" s="5"/>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A395" s="4"/>
+      <c r="B395" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="C395" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="D395" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="E395" s="4"/>
+      <c r="F395" s="5"/>
+      <c r="G395" s="5"/>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A396" s="4"/>
+      <c r="B396" s="5"/>
+      <c r="C396" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="D396" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="E396" s="4"/>
+      <c r="F396" s="5"/>
+      <c r="G396" s="5"/>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A397" s="4"/>
+      <c r="B397" s="5"/>
+      <c r="C397" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="D397" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="E397" s="4"/>
+      <c r="F397" s="5"/>
+      <c r="G397" s="5"/>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A398" s="4"/>
+      <c r="B398" s="5"/>
+      <c r="C398" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="D398" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="E398" s="4"/>
+      <c r="F398" s="5"/>
+      <c r="G398" s="5"/>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A399" s="4"/>
+      <c r="B399" s="5"/>
+      <c r="C399" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D399" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="E399" s="4"/>
+      <c r="F399" s="5"/>
+      <c r="G399" s="5"/>
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A402" s="43"/>
       <c r="B402" s="44"/>
       <c r="C402" s="43"/>
-      <c r="D402" s="44"/>
+      <c r="D402" s="45"/>
       <c r="E402" s="43"/>
       <c r="F402" s="44"/>
       <c r="G402" s="44"/>
@@ -7653,7 +7625,7 @@
       <c r="A403" s="43"/>
       <c r="B403" s="44"/>
       <c r="C403" s="43"/>
-      <c r="D403" s="44"/>
+      <c r="D403" s="45"/>
       <c r="E403" s="43"/>
       <c r="F403" s="44"/>
       <c r="G403" s="44"/>
@@ -7726,6 +7698,149 @@
       <c r="I408" s="44"/>
       <c r="J408" s="44"/>
       <c r="K408" s="44"/>
+    </row>
+    <row r="409" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A409" s="43"/>
+      <c r="B409" s="44"/>
+      <c r="C409" s="43"/>
+      <c r="D409" s="44"/>
+      <c r="E409" s="43"/>
+      <c r="F409" s="44"/>
+      <c r="G409" s="44"/>
+      <c r="H409" s="44"/>
+      <c r="I409" s="44"/>
+      <c r="J409" s="44"/>
+      <c r="K409" s="44"/>
+    </row>
+    <row r="410" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A410" s="43"/>
+      <c r="B410" s="44"/>
+      <c r="C410" s="43"/>
+      <c r="D410" s="44"/>
+      <c r="E410" s="43"/>
+      <c r="F410" s="44"/>
+      <c r="G410" s="44"/>
+      <c r="H410" s="44"/>
+      <c r="I410" s="44"/>
+      <c r="J410" s="44"/>
+      <c r="K410" s="44"/>
+    </row>
+    <row r="411" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A411" s="43"/>
+      <c r="B411" s="44"/>
+      <c r="C411" s="43"/>
+      <c r="D411" s="44"/>
+      <c r="E411" s="43"/>
+      <c r="F411" s="44"/>
+      <c r="G411" s="44"/>
+      <c r="H411" s="44"/>
+      <c r="I411" s="44"/>
+      <c r="J411" s="44"/>
+      <c r="K411" s="44"/>
+    </row>
+    <row r="412" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A412" s="43"/>
+      <c r="B412" s="44"/>
+      <c r="C412" s="43"/>
+      <c r="D412" s="44"/>
+      <c r="E412" s="43"/>
+      <c r="F412" s="44"/>
+      <c r="G412" s="44"/>
+      <c r="H412" s="44"/>
+      <c r="I412" s="44"/>
+      <c r="J412" s="44"/>
+      <c r="K412" s="44"/>
+    </row>
+    <row r="413" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A413" s="43"/>
+      <c r="B413" s="44"/>
+      <c r="C413" s="43"/>
+      <c r="D413" s="44"/>
+      <c r="E413" s="43"/>
+      <c r="F413" s="44"/>
+      <c r="G413" s="44"/>
+      <c r="H413" s="44"/>
+      <c r="I413" s="44"/>
+      <c r="J413" s="44"/>
+      <c r="K413" s="44"/>
+    </row>
+    <row r="414" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A414" s="43"/>
+      <c r="B414" s="44"/>
+      <c r="C414" s="43"/>
+      <c r="D414" s="44"/>
+      <c r="E414" s="43"/>
+      <c r="F414" s="44"/>
+      <c r="G414" s="44"/>
+      <c r="H414" s="44"/>
+      <c r="I414" s="44"/>
+      <c r="J414" s="44"/>
+      <c r="K414" s="44"/>
+    </row>
+    <row r="415" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A415" s="43"/>
+      <c r="B415" s="44"/>
+      <c r="C415" s="43"/>
+      <c r="D415" s="44"/>
+      <c r="E415" s="43"/>
+      <c r="F415" s="44"/>
+      <c r="G415" s="44"/>
+      <c r="H415" s="44"/>
+      <c r="I415" s="44"/>
+      <c r="J415" s="44"/>
+      <c r="K415" s="44"/>
+    </row>
+    <row r="416" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A416" s="43"/>
+      <c r="B416" s="44"/>
+      <c r="C416" s="43"/>
+      <c r="D416" s="44"/>
+      <c r="E416" s="43"/>
+      <c r="F416" s="44"/>
+      <c r="G416" s="44"/>
+      <c r="H416" s="44"/>
+      <c r="I416" s="44"/>
+      <c r="J416" s="44"/>
+      <c r="K416" s="44"/>
+    </row>
+    <row r="417" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A417" s="43"/>
+      <c r="B417" s="44"/>
+      <c r="C417" s="43"/>
+      <c r="D417" s="44"/>
+      <c r="E417" s="43"/>
+      <c r="F417" s="44"/>
+      <c r="G417" s="44"/>
+      <c r="H417" s="44"/>
+      <c r="I417" s="44"/>
+      <c r="J417" s="44"/>
+      <c r="K417" s="44"/>
+    </row>
+    <row r="418" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A418" s="43"/>
+      <c r="B418" s="44"/>
+      <c r="C418" s="43"/>
+      <c r="D418" s="44"/>
+      <c r="E418" s="43"/>
+      <c r="F418" s="44"/>
+      <c r="G418" s="44"/>
+      <c r="H418" s="44"/>
+      <c r="I418" s="44"/>
+      <c r="J418" s="44"/>
+      <c r="K418" s="44"/>
+    </row>
+    <row r="419" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A419" s="43"/>
+      <c r="B419" s="44"/>
+      <c r="C419" s="43"/>
+      <c r="D419" s="44"/>
+      <c r="E419" s="43"/>
+      <c r="F419" s="44"/>
+      <c r="G419" s="44"/>
+      <c r="H419" s="44"/>
+      <c r="I419" s="44"/>
+      <c r="J419" s="44"/>
+      <c r="K419" s="44"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Images for Markdown files database .xlsx
+++ b/Images for Markdown files database .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trevor\Compac Industries\Compac - General\IT\ChatBot\Markdown-Manuals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA079B67-5E73-4CC6-8AD8-5F1E4BCD2969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1058868D-79DF-42E3-961D-C53D82C68E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-1320" windowWidth="38640" windowHeight="21120" xr2:uid="{7323B22B-375C-41F7-91CD-F86C900FC6DE}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="716">
   <si>
     <t xml:space="preserve">PCBs </t>
   </si>
@@ -2153,6 +2153,45 @@
   </si>
   <si>
     <t>14.2.3_GW_comms_switches.png</t>
+  </si>
+  <si>
+    <t>12.88.1</t>
+  </si>
+  <si>
+    <t>12.88.2</t>
+  </si>
+  <si>
+    <t>12.88.3</t>
+  </si>
+  <si>
+    <t>12.88.4</t>
+  </si>
+  <si>
+    <t>12.88.5</t>
+  </si>
+  <si>
+    <t>12.88.6</t>
+  </si>
+  <si>
+    <t>12.88.7</t>
+  </si>
+  <si>
+    <t>12.88.8</t>
+  </si>
+  <si>
+    <t>12.88.0</t>
+  </si>
+  <si>
+    <t>12.88.0_COMFILL_Ex_footprint.png</t>
+  </si>
+  <si>
+    <t>12.88.1_COMFILL_Ex_layout.png</t>
+  </si>
+  <si>
+    <t>6.1.5</t>
+  </si>
+  <si>
+    <t>6.1.5_GPIO_VeederRoot_EMR4_Pulser.png</t>
   </si>
 </sst>
 </file>
@@ -2759,7 +2798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B533B56-556A-40A2-8D3F-E8E5A852019A}">
-  <dimension ref="A1:K419"/>
+  <dimension ref="A1:K432"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="1" customWidth="1"/>
@@ -3842,10 +3881,10 @@
       <c r="A74" s="13"/>
       <c r="B74" s="12"/>
       <c r="C74" s="13" t="s">
-        <v>82</v>
+        <v>714</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>81</v>
+        <v>715</v>
       </c>
       <c r="E74" s="13"/>
       <c r="F74" s="12"/>
@@ -3859,10 +3898,10 @@
       <c r="A75" s="13"/>
       <c r="B75" s="12"/>
       <c r="C75" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E75" s="13"/>
       <c r="F75" s="12"/>
@@ -3876,10 +3915,10 @@
       <c r="A76" s="13"/>
       <c r="B76" s="12"/>
       <c r="C76" s="13" t="s">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="E76" s="13"/>
       <c r="F76" s="12"/>
@@ -3893,10 +3932,10 @@
       <c r="A77" s="13"/>
       <c r="B77" s="12"/>
       <c r="C77" s="13" t="s">
-        <v>86</v>
+        <v>169</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>85</v>
+        <v>168</v>
       </c>
       <c r="E77" s="13"/>
       <c r="F77" s="12"/>
@@ -3910,10 +3949,10 @@
       <c r="A78" s="13"/>
       <c r="B78" s="12"/>
       <c r="C78" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="D78" s="19" t="s">
-        <v>459</v>
+        <v>86</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="E78" s="13"/>
       <c r="F78" s="12"/>
@@ -3927,10 +3966,10 @@
       <c r="A79" s="13"/>
       <c r="B79" s="12"/>
       <c r="C79" s="13" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E79" s="13"/>
       <c r="F79" s="12"/>
@@ -3944,10 +3983,10 @@
       <c r="A80" s="13"/>
       <c r="B80" s="12"/>
       <c r="C80" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E80" s="13"/>
       <c r="F80" s="12"/>
@@ -3961,10 +4000,10 @@
       <c r="A81" s="13"/>
       <c r="B81" s="12"/>
       <c r="C81" s="13" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E81" s="13"/>
       <c r="F81" s="12"/>
@@ -3975,108 +4014,112 @@
       <c r="K81" s="12"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A82" s="26"/>
-      <c r="B82" s="25"/>
-      <c r="C82" s="26"/>
-      <c r="D82" s="25"/>
-      <c r="E82" s="26"/>
-      <c r="F82" s="25"/>
-      <c r="G82" s="25"/>
-      <c r="H82" s="25"/>
-      <c r="I82" s="25"/>
-      <c r="J82" s="25"/>
-      <c r="K82" s="25"/>
+      <c r="A82" s="13"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="D82" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="E82" s="13"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
+      <c r="H82" s="12"/>
+      <c r="I82" s="12"/>
+      <c r="J82" s="12"/>
+      <c r="K82" s="12"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A83" s="4">
+      <c r="A83" s="13"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="19"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
+      <c r="H83" s="12"/>
+      <c r="I83" s="12"/>
+      <c r="J83" s="12"/>
+      <c r="K83" s="12"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A84" s="26"/>
+      <c r="B84" s="25"/>
+      <c r="C84" s="26"/>
+      <c r="D84" s="25"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="25"/>
+      <c r="H84" s="25"/>
+      <c r="I84" s="25"/>
+      <c r="J84" s="25"/>
+      <c r="K84" s="25"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A85" s="4">
         <v>7</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="B85" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C85" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D83" s="5" t="s">
+      <c r="D85" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="E83" s="4"/>
-      <c r="F83" s="5"/>
-      <c r="G83" s="5"/>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A84" s="4"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E84" s="4"/>
-      <c r="F84" s="5"/>
-      <c r="G84" s="5"/>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A85" s="4"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A86" s="6"/>
-      <c r="B86" s="7"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="6"/>
+      <c r="A86" s="4"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E86" s="4"/>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A87" s="4">
-        <v>8</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>63</v>
-      </c>
+      <c r="A87" s="4"/>
+      <c r="B87" s="5"/>
       <c r="C87" s="4" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A88" s="4"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E88" s="4"/>
+      <c r="A88" s="6"/>
+      <c r="B88" s="7"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="6"/>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A89" s="4"/>
-      <c r="B89" s="5"/>
+      <c r="A89" s="4">
+        <v>8</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="C89" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E89" s="4"/>
       <c r="F89" s="5"/>
@@ -4086,10 +4129,10 @@
       <c r="A90" s="4"/>
       <c r="B90" s="5"/>
       <c r="C90" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E90" s="4"/>
       <c r="F90" s="5"/>
@@ -4099,64 +4142,62 @@
       <c r="A91" s="4"/>
       <c r="B91" s="5"/>
       <c r="C91" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E91" s="4"/>
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A92" s="6"/>
-      <c r="B92" s="7"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="6"/>
+      <c r="A92" s="4"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E92" s="4"/>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A93" s="4">
-        <v>9</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>265</v>
-      </c>
+      <c r="A93" s="4"/>
+      <c r="B93" s="5"/>
       <c r="C93" s="4" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>149</v>
+        <v>62</v>
       </c>
       <c r="E93" s="4"/>
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A94" s="4"/>
-      <c r="B94" s="5"/>
-      <c r="C94" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E94" s="17">
-        <v>46098</v>
-      </c>
+      <c r="A94" s="6"/>
+      <c r="B94" s="7"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="7"/>
+      <c r="E94" s="6"/>
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A95" s="4"/>
-      <c r="B95" s="5"/>
+      <c r="A95" s="4">
+        <v>9</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>265</v>
+      </c>
       <c r="C95" s="4" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="E95" s="4"/>
       <c r="F95" s="5"/>
@@ -4166,12 +4207,14 @@
       <c r="A96" s="4"/>
       <c r="B96" s="5"/>
       <c r="C96" s="4" t="s">
-        <v>158</v>
+        <v>263</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="E96" s="4"/>
+        <v>264</v>
+      </c>
+      <c r="E96" s="17">
+        <v>46098</v>
+      </c>
       <c r="F96" s="5"/>
       <c r="G96" s="5"/>
     </row>
@@ -4179,10 +4222,10 @@
       <c r="A97" s="4"/>
       <c r="B97" s="5"/>
       <c r="C97" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="5"/>
@@ -4192,10 +4235,10 @@
       <c r="A98" s="4"/>
       <c r="B98" s="5"/>
       <c r="C98" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="5"/>
@@ -4205,10 +4248,10 @@
       <c r="A99" s="4"/>
       <c r="B99" s="5"/>
       <c r="C99" s="4" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E99" s="4"/>
       <c r="F99" s="5"/>
@@ -4218,10 +4261,10 @@
       <c r="A100" s="4"/>
       <c r="B100" s="5"/>
       <c r="C100" s="4" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="5"/>
@@ -4231,10 +4274,10 @@
       <c r="A101" s="4"/>
       <c r="B101" s="5"/>
       <c r="C101" s="4" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E101" s="4"/>
       <c r="F101" s="5"/>
@@ -4243,8 +4286,12 @@
     <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="4"/>
       <c r="B102" s="5"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="5"/>
+      <c r="C102" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>176</v>
+      </c>
       <c r="E102" s="4"/>
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
@@ -4252,84 +4299,68 @@
     <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="4"/>
       <c r="B103" s="5"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="5"/>
+      <c r="C103" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>174</v>
+      </c>
       <c r="E103" s="4"/>
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A104" s="30"/>
-      <c r="B104" s="31"/>
-      <c r="C104" s="30"/>
-      <c r="D104" s="31"/>
-      <c r="E104" s="30"/>
-      <c r="F104" s="31"/>
-      <c r="G104" s="31"/>
+      <c r="A104" s="4"/>
+      <c r="B104" s="5"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A105" s="26"/>
-      <c r="B105" s="25"/>
-      <c r="C105" s="26"/>
-      <c r="D105" s="25" t="s">
+      <c r="A105" s="4"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="5"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="5"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A106" s="30"/>
+      <c r="B106" s="31"/>
+      <c r="C106" s="30"/>
+      <c r="D106" s="31"/>
+      <c r="E106" s="30"/>
+      <c r="F106" s="31"/>
+      <c r="G106" s="31"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A107" s="26"/>
+      <c r="B107" s="25"/>
+      <c r="C107" s="26"/>
+      <c r="D107" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="E105" s="26"/>
-      <c r="F105" s="25"/>
-      <c r="G105" s="25"/>
-      <c r="H105" s="25"/>
-      <c r="I105" s="25"/>
-      <c r="J105" s="25"/>
-      <c r="K105" s="25"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A106" s="35"/>
-      <c r="B106" s="36" t="s">
-        <v>569</v>
-      </c>
-      <c r="C106" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="D106" s="36" t="s">
-        <v>266</v>
-      </c>
-      <c r="E106" s="37">
-        <v>46098</v>
-      </c>
-      <c r="F106" s="36"/>
-      <c r="G106" s="36"/>
-      <c r="H106" s="36"/>
-      <c r="I106" s="36"/>
-      <c r="J106" s="36"/>
-      <c r="K106" s="36"/>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A107" s="35"/>
-      <c r="B107" s="36"/>
-      <c r="C107" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="D107" s="36" t="s">
-        <v>267</v>
-      </c>
-      <c r="E107" s="37">
-        <v>46098</v>
-      </c>
-      <c r="F107" s="36"/>
-      <c r="G107" s="36"/>
-      <c r="H107" s="36"/>
-      <c r="I107" s="36"/>
-      <c r="J107" s="36"/>
-      <c r="K107" s="36"/>
+      <c r="E107" s="26"/>
+      <c r="F107" s="25"/>
+      <c r="G107" s="25"/>
+      <c r="H107" s="25"/>
+      <c r="I107" s="25"/>
+      <c r="J107" s="25"/>
+      <c r="K107" s="25"/>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" s="35"/>
-      <c r="B108" s="36"/>
+      <c r="B108" s="36" t="s">
+        <v>569</v>
+      </c>
       <c r="C108" s="35" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D108" s="36" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E108" s="37">
         <v>46098</v>
@@ -4345,10 +4376,10 @@
       <c r="A109" s="35"/>
       <c r="B109" s="36"/>
       <c r="C109" s="35" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D109" s="36" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E109" s="37">
         <v>46098</v>
@@ -4363,9 +4394,15 @@
     <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" s="35"/>
       <c r="B110" s="36"/>
-      <c r="C110" s="35"/>
-      <c r="D110" s="36"/>
-      <c r="E110" s="35"/>
+      <c r="C110" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="D110" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="E110" s="37">
+        <v>46098</v>
+      </c>
       <c r="F110" s="36"/>
       <c r="G110" s="36"/>
       <c r="H110" s="36"/>
@@ -4374,100 +4411,98 @@
       <c r="K110" s="36"/>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A111" s="26"/>
-      <c r="B111" s="25"/>
-      <c r="C111" s="26"/>
-      <c r="D111" s="25" t="s">
+      <c r="A111" s="35"/>
+      <c r="B111" s="36"/>
+      <c r="C111" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="D111" s="36" t="s">
+        <v>269</v>
+      </c>
+      <c r="E111" s="37">
+        <v>46098</v>
+      </c>
+      <c r="F111" s="36"/>
+      <c r="G111" s="36"/>
+      <c r="H111" s="36"/>
+      <c r="I111" s="36"/>
+      <c r="J111" s="36"/>
+      <c r="K111" s="36"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A112" s="35"/>
+      <c r="B112" s="36"/>
+      <c r="C112" s="35"/>
+      <c r="D112" s="36"/>
+      <c r="E112" s="35"/>
+      <c r="F112" s="36"/>
+      <c r="G112" s="36"/>
+      <c r="H112" s="36"/>
+      <c r="I112" s="36"/>
+      <c r="J112" s="36"/>
+      <c r="K112" s="36"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A113" s="26"/>
+      <c r="B113" s="25"/>
+      <c r="C113" s="26"/>
+      <c r="D113" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="E111" s="26"/>
-      <c r="F111" s="25"/>
-      <c r="G111" s="25"/>
-      <c r="H111" s="25"/>
-      <c r="I111" s="25"/>
-      <c r="J111" s="25"/>
-      <c r="K111" s="25"/>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A112" s="47" t="s">
+      <c r="E113" s="26"/>
+      <c r="F113" s="25"/>
+      <c r="G113" s="25"/>
+      <c r="H113" s="25"/>
+      <c r="I113" s="25"/>
+      <c r="J113" s="25"/>
+      <c r="K113" s="25"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A114" s="47" t="s">
         <v>573</v>
       </c>
-      <c r="B112" s="48" t="s">
+      <c r="B114" s="48" t="s">
         <v>572</v>
       </c>
-      <c r="C112" s="32" t="s">
+      <c r="C114" s="32" t="s">
         <v>270</v>
       </c>
-      <c r="D112" s="33" t="s">
+      <c r="D114" s="33" t="s">
         <v>677</v>
       </c>
-      <c r="E112" s="34">
+      <c r="E114" s="34">
         <v>46099</v>
       </c>
-      <c r="F112" s="33"/>
-      <c r="G112" s="33"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A113" s="13" t="s">
+      <c r="F114" s="33"/>
+      <c r="G114" s="33"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A115" s="13" t="s">
         <v>574</v>
       </c>
-      <c r="B113" s="19">
+      <c r="B115" s="19">
         <v>11</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C115" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="D113" s="5" t="s">
+      <c r="D115" s="5" t="s">
         <v>678</v>
-      </c>
-      <c r="E113" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F113" s="5"/>
-      <c r="G113" s="5"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A114" s="4"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>658</v>
-      </c>
-      <c r="E114" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G114" s="5"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A115" s="4"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>659</v>
       </c>
       <c r="E115" s="17">
         <v>46099</v>
       </c>
-      <c r="F115" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="F115" s="5"/>
       <c r="G115" s="5"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116" s="4"/>
       <c r="B116" s="5"/>
       <c r="C116" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E116" s="17">
         <v>46099</v>
@@ -4477,14 +4512,14 @@
       </c>
       <c r="G116" s="5"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117" s="4"/>
       <c r="B117" s="5"/>
       <c r="C117" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E117" s="17">
         <v>46099</v>
@@ -4494,14 +4529,14 @@
       </c>
       <c r="G117" s="5"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118" s="4"/>
       <c r="B118" s="5"/>
       <c r="C118" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E118" s="17">
         <v>46099</v>
@@ -4511,44 +4546,48 @@
       </c>
       <c r="G118" s="5"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119" s="4"/>
       <c r="B119" s="5"/>
       <c r="C119" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E119" s="17">
         <v>46099</v>
       </c>
-      <c r="F119" s="5"/>
+      <c r="F119" s="5" t="s">
+        <v>172</v>
+      </c>
       <c r="G119" s="5"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120" s="4"/>
       <c r="B120" s="5"/>
       <c r="C120" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E120" s="17">
         <v>46099</v>
       </c>
-      <c r="F120" s="5"/>
+      <c r="F120" s="5" t="s">
+        <v>172</v>
+      </c>
       <c r="G120" s="5"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" s="4"/>
       <c r="B121" s="5"/>
       <c r="C121" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E121" s="17">
         <v>46099</v>
@@ -4556,14 +4595,14 @@
       <c r="F121" s="5"/>
       <c r="G121" s="5"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122" s="4"/>
       <c r="B122" s="5"/>
       <c r="C122" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E122" s="17">
         <v>46099</v>
@@ -4571,14 +4610,14 @@
       <c r="F122" s="5"/>
       <c r="G122" s="5"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123" s="4"/>
       <c r="B123" s="5"/>
       <c r="C123" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E123" s="17">
         <v>46099</v>
@@ -4586,14 +4625,14 @@
       <c r="F123" s="5"/>
       <c r="G123" s="5"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" s="4"/>
       <c r="B124" s="5"/>
       <c r="C124" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E124" s="17">
         <v>46099</v>
@@ -4601,14 +4640,14 @@
       <c r="F124" s="5"/>
       <c r="G124" s="5"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" s="4"/>
       <c r="B125" s="5"/>
       <c r="C125" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E125" s="17">
         <v>46099</v>
@@ -4616,14 +4655,14 @@
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" s="4"/>
       <c r="B126" s="5"/>
       <c r="C126" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E126" s="17">
         <v>46099</v>
@@ -4631,14 +4670,14 @@
       <c r="F126" s="5"/>
       <c r="G126" s="5"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" s="4"/>
       <c r="B127" s="5"/>
       <c r="C127" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E127" s="17">
         <v>46099</v>
@@ -4646,14 +4685,14 @@
       <c r="F127" s="5"/>
       <c r="G127" s="5"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" s="4"/>
       <c r="B128" s="5"/>
       <c r="C128" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E128" s="17">
         <v>46099</v>
@@ -4665,10 +4704,10 @@
       <c r="A129" s="4"/>
       <c r="B129" s="5"/>
       <c r="C129" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E129" s="17">
         <v>46099</v>
@@ -4680,10 +4719,10 @@
       <c r="A130" s="4"/>
       <c r="B130" s="5"/>
       <c r="C130" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E130" s="17">
         <v>46099</v>
@@ -4695,10 +4734,10 @@
       <c r="A131" s="4"/>
       <c r="B131" s="5"/>
       <c r="C131" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="E131" s="17">
         <v>46099</v>
@@ -4710,10 +4749,10 @@
       <c r="A132" s="4"/>
       <c r="B132" s="5"/>
       <c r="C132" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E132" s="17">
         <v>46099</v>
@@ -4724,24 +4763,26 @@
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4"/>
       <c r="B133" s="5"/>
-      <c r="C133" s="13">
-        <v>11.2</v>
-      </c>
-      <c r="D133" s="12" t="s">
-        <v>657</v>
-      </c>
-      <c r="E133" s="46"/>
-      <c r="F133" s="12"/>
-      <c r="G133" s="12"/>
+      <c r="C133" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="E133" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F133" s="5"/>
+      <c r="G133" s="5"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4"/>
       <c r="B134" s="5"/>
       <c r="C134" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>656</v>
+        <v>675</v>
       </c>
       <c r="E134" s="17">
         <v>46099</v>
@@ -4752,26 +4793,24 @@
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4"/>
       <c r="B135" s="5"/>
-      <c r="C135" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="D135" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="E135" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F135" s="5"/>
-      <c r="G135" s="5"/>
+      <c r="C135" s="13">
+        <v>11.2</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>657</v>
+      </c>
+      <c r="E135" s="46"/>
+      <c r="F135" s="12"/>
+      <c r="G135" s="12"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4"/>
       <c r="B136" s="5"/>
       <c r="C136" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E136" s="17">
         <v>46099</v>
@@ -4783,10 +4822,10 @@
       <c r="A137" s="4"/>
       <c r="B137" s="5"/>
       <c r="C137" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E137" s="17">
         <v>46099</v>
@@ -4798,48 +4837,40 @@
       <c r="A138" s="4"/>
       <c r="B138" s="5"/>
       <c r="C138" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E138" s="17">
         <v>46099</v>
       </c>
-      <c r="F138" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G138" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="F138" s="5"/>
+      <c r="G138" s="5"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4"/>
       <c r="B139" s="5"/>
       <c r="C139" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E139" s="17">
         <v>46099</v>
       </c>
-      <c r="F139" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G139" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="F139" s="5"/>
+      <c r="G139" s="5"/>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4"/>
       <c r="B140" s="5"/>
       <c r="C140" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E140" s="17">
         <v>46099</v>
@@ -4855,10 +4886,10 @@
       <c r="A141" s="4"/>
       <c r="B141" s="5"/>
       <c r="C141" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E141" s="17">
         <v>46099</v>
@@ -4874,10 +4905,10 @@
       <c r="A142" s="4"/>
       <c r="B142" s="5"/>
       <c r="C142" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E142" s="17">
         <v>46099</v>
@@ -4893,10 +4924,10 @@
       <c r="A143" s="4"/>
       <c r="B143" s="5"/>
       <c r="C143" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E143" s="17">
         <v>46099</v>
@@ -4912,10 +4943,10 @@
       <c r="A144" s="4"/>
       <c r="B144" s="5"/>
       <c r="C144" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E144" s="17">
         <v>46099</v>
@@ -4931,10 +4962,10 @@
       <c r="A145" s="4"/>
       <c r="B145" s="5"/>
       <c r="C145" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E145" s="17">
         <v>46099</v>
@@ -4950,10 +4981,10 @@
       <c r="A146" s="4"/>
       <c r="B146" s="5"/>
       <c r="C146" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E146" s="17">
         <v>46099</v>
@@ -4969,10 +5000,10 @@
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
       <c r="C147" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E147" s="17">
         <v>46099</v>
@@ -4988,10 +5019,10 @@
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E148" s="17">
         <v>46099</v>
@@ -5006,24 +5037,30 @@
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4"/>
       <c r="B149" s="5"/>
-      <c r="C149" s="13">
-        <v>11.3</v>
-      </c>
-      <c r="D149" s="12" t="s">
-        <v>641</v>
-      </c>
-      <c r="E149" s="46"/>
-      <c r="F149" s="12"/>
-      <c r="G149" s="12"/>
+      <c r="C149" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="E149" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4"/>
       <c r="B150" s="5"/>
       <c r="C150" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E150" s="17">
         <v>46099</v>
@@ -5039,10 +5076,10 @@
       <c r="A151" s="4"/>
       <c r="B151" s="5"/>
       <c r="C151" s="13">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="D151" s="12" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E151" s="46"/>
       <c r="F151" s="12"/>
@@ -5052,10 +5089,10 @@
       <c r="A152" s="4"/>
       <c r="B152" s="5"/>
       <c r="C152" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E152" s="17">
         <v>46099</v>
@@ -5070,43 +5107,43 @@
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4"/>
       <c r="B153" s="5"/>
-      <c r="C153" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="D153" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="E153" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F153" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G153" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="C153" s="13">
+        <v>11.4</v>
+      </c>
+      <c r="D153" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="E153" s="46"/>
+      <c r="F153" s="12"/>
+      <c r="G153" s="12"/>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
-      <c r="C154" s="13">
-        <v>11.5</v>
-      </c>
-      <c r="D154" s="12" t="s">
-        <v>627</v>
-      </c>
-      <c r="E154" s="46"/>
-      <c r="F154" s="12"/>
-      <c r="G154" s="12"/>
+      <c r="C154" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="E154" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4"/>
       <c r="B155" s="5"/>
       <c r="C155" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>620</v>
+        <v>639</v>
       </c>
       <c r="E155" s="17">
         <v>46099</v>
@@ -5121,41 +5158,43 @@
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4"/>
       <c r="B156" s="5"/>
-      <c r="C156" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="D156" s="5" t="s">
-        <v>621</v>
-      </c>
-      <c r="E156" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F156" s="5"/>
-      <c r="G156" s="5"/>
+      <c r="C156" s="13">
+        <v>11.5</v>
+      </c>
+      <c r="D156" s="12" t="s">
+        <v>627</v>
+      </c>
+      <c r="E156" s="46"/>
+      <c r="F156" s="12"/>
+      <c r="G156" s="12"/>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4"/>
       <c r="B157" s="5"/>
       <c r="C157" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E157" s="17">
         <v>46099</v>
       </c>
-      <c r="F157" s="5"/>
-      <c r="G157" s="5"/>
+      <c r="F157" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4"/>
       <c r="B158" s="5"/>
       <c r="C158" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E158" s="17">
         <v>46099</v>
@@ -5167,29 +5206,25 @@
       <c r="A159" s="4"/>
       <c r="B159" s="5"/>
       <c r="C159" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="E159" s="17">
         <v>46099</v>
       </c>
-      <c r="F159" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G159" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="F159" s="5"/>
+      <c r="G159" s="5"/>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4"/>
       <c r="B160" s="5"/>
       <c r="C160" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E160" s="17">
         <v>46099</v>
@@ -5201,25 +5236,29 @@
       <c r="A161" s="4"/>
       <c r="B161" s="5"/>
       <c r="C161" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E161" s="17">
         <v>46099</v>
       </c>
-      <c r="F161" s="5"/>
-      <c r="G161" s="5"/>
+      <c r="F161" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4"/>
       <c r="B162" s="5"/>
       <c r="C162" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E162" s="17">
         <v>46099</v>
@@ -5231,29 +5270,25 @@
       <c r="A163" s="4"/>
       <c r="B163" s="5"/>
       <c r="C163" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="D163" s="49" t="s">
-        <v>630</v>
+        <v>315</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>625</v>
       </c>
       <c r="E163" s="17">
         <v>46099</v>
       </c>
-      <c r="F163" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G163" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="F163" s="5"/>
+      <c r="G163" s="5"/>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4"/>
       <c r="B164" s="5"/>
       <c r="C164" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="E164" s="17">
         <v>46099</v>
@@ -5265,25 +5300,29 @@
       <c r="A165" s="4"/>
       <c r="B165" s="5"/>
       <c r="C165" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D165" s="5" t="s">
-        <v>632</v>
+        <v>317</v>
+      </c>
+      <c r="D165" s="49" t="s">
+        <v>630</v>
       </c>
       <c r="E165" s="17">
         <v>46099</v>
       </c>
-      <c r="F165" s="5"/>
-      <c r="G165" s="5"/>
+      <c r="F165" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4"/>
       <c r="B166" s="5"/>
       <c r="C166" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E166" s="17">
         <v>46099</v>
@@ -5295,10 +5334,10 @@
       <c r="A167" s="4"/>
       <c r="B167" s="5"/>
       <c r="C167" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E167" s="17">
         <v>46099</v>
@@ -5310,10 +5349,10 @@
       <c r="A168" s="4"/>
       <c r="B168" s="5"/>
       <c r="C168" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E168" s="17">
         <v>46099</v>
@@ -5325,10 +5364,10 @@
       <c r="A169" s="4"/>
       <c r="B169" s="5"/>
       <c r="C169" s="4" t="s">
-        <v>629</v>
+        <v>321</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E169" s="17">
         <v>46099</v>
@@ -5339,24 +5378,26 @@
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4"/>
       <c r="B170" s="5"/>
-      <c r="C170" s="13">
-        <v>11.6</v>
-      </c>
-      <c r="D170" s="12" t="s">
-        <v>613</v>
-      </c>
-      <c r="E170" s="46"/>
-      <c r="F170" s="12"/>
-      <c r="G170" s="12"/>
+      <c r="C170" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="E170" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F170" s="5"/>
+      <c r="G170" s="5"/>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4"/>
       <c r="B171" s="5"/>
       <c r="C171" s="4" t="s">
-        <v>323</v>
+        <v>629</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>614</v>
+        <v>636</v>
       </c>
       <c r="E171" s="17">
         <v>46099</v>
@@ -5367,26 +5408,24 @@
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4"/>
       <c r="B172" s="5"/>
-      <c r="C172" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="D172" s="5" t="s">
-        <v>615</v>
-      </c>
-      <c r="E172" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F172" s="5"/>
-      <c r="G172" s="5"/>
+      <c r="C172" s="13">
+        <v>11.6</v>
+      </c>
+      <c r="D172" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="E172" s="46"/>
+      <c r="F172" s="12"/>
+      <c r="G172" s="12"/>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4"/>
       <c r="B173" s="5"/>
       <c r="C173" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E173" s="17">
         <v>46099</v>
@@ -5398,10 +5437,10 @@
       <c r="A174" s="4"/>
       <c r="B174" s="5"/>
       <c r="C174" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E174" s="17">
         <v>46099</v>
@@ -5413,10 +5452,10 @@
       <c r="A175" s="4"/>
       <c r="B175" s="5"/>
       <c r="C175" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E175" s="17">
         <v>46099</v>
@@ -5428,10 +5467,10 @@
       <c r="A176" s="4"/>
       <c r="B176" s="5"/>
       <c r="C176" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E176" s="17">
         <v>46099</v>
@@ -5442,24 +5481,26 @@
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4"/>
       <c r="B177" s="5"/>
-      <c r="C177" s="13">
-        <v>11.7</v>
-      </c>
-      <c r="D177" s="12" t="s">
-        <v>611</v>
-      </c>
-      <c r="E177" s="46"/>
-      <c r="F177" s="12"/>
-      <c r="G177" s="12"/>
+      <c r="C177" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="E177" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F177" s="5"/>
+      <c r="G177" s="5"/>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4"/>
       <c r="B178" s="5"/>
       <c r="C178" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="E178" s="17">
         <v>46099</v>
@@ -5470,26 +5511,24 @@
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4"/>
       <c r="B179" s="5"/>
-      <c r="C179" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="D179" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="E179" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F179" s="5"/>
-      <c r="G179" s="5"/>
+      <c r="C179" s="13">
+        <v>11.7</v>
+      </c>
+      <c r="D179" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="E179" s="46"/>
+      <c r="F179" s="12"/>
+      <c r="G179" s="12"/>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4"/>
       <c r="B180" s="5"/>
       <c r="C180" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E180" s="17">
         <v>46099</v>
@@ -5501,10 +5540,10 @@
       <c r="A181" s="4"/>
       <c r="B181" s="5"/>
       <c r="C181" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E181" s="17">
         <v>46099</v>
@@ -5516,10 +5555,10 @@
       <c r="A182" s="4"/>
       <c r="B182" s="5"/>
       <c r="C182" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E182" s="17">
         <v>46099</v>
@@ -5531,10 +5570,10 @@
       <c r="A183" s="4"/>
       <c r="B183" s="5"/>
       <c r="C183" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E183" s="17">
         <v>46099</v>
@@ -5546,10 +5585,10 @@
       <c r="A184" s="4"/>
       <c r="B184" s="5"/>
       <c r="C184" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E184" s="17">
         <v>46099</v>
@@ -5561,10 +5600,10 @@
       <c r="A185" s="4"/>
       <c r="B185" s="5"/>
       <c r="C185" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E185" s="17">
         <v>46099</v>
@@ -5575,27 +5614,29 @@
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4"/>
       <c r="B186" s="5"/>
-      <c r="C186" s="13">
-        <v>11.8</v>
-      </c>
-      <c r="D186" s="12" t="s">
-        <v>612</v>
-      </c>
-      <c r="E186" s="46"/>
-      <c r="F186" s="12"/>
-      <c r="G186" s="12"/>
+      <c r="C186" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D186" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="E186" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F186" s="5"/>
+      <c r="G186" s="5"/>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4"/>
       <c r="B187" s="5"/>
       <c r="C187" s="4" t="s">
-        <v>575</v>
+        <v>336</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>589</v>
+        <v>610</v>
       </c>
       <c r="E187" s="17">
-        <v>46275</v>
+        <v>46099</v>
       </c>
       <c r="F187" s="5"/>
       <c r="G187" s="5"/>
@@ -5603,26 +5644,24 @@
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4"/>
       <c r="B188" s="5"/>
-      <c r="C188" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="D188" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="E188" s="17">
-        <v>46275</v>
-      </c>
-      <c r="F188" s="5"/>
-      <c r="G188" s="5"/>
+      <c r="C188" s="13">
+        <v>11.8</v>
+      </c>
+      <c r="D188" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="E188" s="46"/>
+      <c r="F188" s="12"/>
+      <c r="G188" s="12"/>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="4"/>
       <c r="B189" s="5"/>
       <c r="C189" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E189" s="17">
         <v>46275</v>
@@ -5634,10 +5673,10 @@
       <c r="A190" s="4"/>
       <c r="B190" s="5"/>
       <c r="C190" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E190" s="17">
         <v>46275</v>
@@ -5649,10 +5688,10 @@
       <c r="A191" s="4"/>
       <c r="B191" s="5"/>
       <c r="C191" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E191" s="17">
         <v>46275</v>
@@ -5664,10 +5703,10 @@
       <c r="A192" s="4"/>
       <c r="B192" s="5"/>
       <c r="C192" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E192" s="17">
         <v>46275</v>
@@ -5679,10 +5718,10 @@
       <c r="A193" s="4"/>
       <c r="B193" s="5"/>
       <c r="C193" s="4" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E193" s="17">
         <v>46275</v>
@@ -5694,10 +5733,10 @@
       <c r="A194" s="4"/>
       <c r="B194" s="5"/>
       <c r="C194" s="4" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E194" s="17">
         <v>46275</v>
@@ -5709,10 +5748,10 @@
       <c r="A195" s="4"/>
       <c r="B195" s="5"/>
       <c r="C195" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E195" s="17">
         <v>46275</v>
@@ -5724,10 +5763,10 @@
       <c r="A196" s="4"/>
       <c r="B196" s="5"/>
       <c r="C196" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E196" s="17">
         <v>46275</v>
@@ -5739,10 +5778,10 @@
       <c r="A197" s="4"/>
       <c r="B197" s="5"/>
       <c r="C197" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E197" s="17">
         <v>46275</v>
@@ -5754,10 +5793,10 @@
       <c r="A198" s="4"/>
       <c r="B198" s="5"/>
       <c r="C198" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E198" s="17">
         <v>46275</v>
@@ -5769,10 +5808,10 @@
       <c r="A199" s="4"/>
       <c r="B199" s="5"/>
       <c r="C199" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E199" s="17">
         <v>46275</v>
@@ -5784,10 +5823,10 @@
       <c r="A200" s="4"/>
       <c r="B200" s="5"/>
       <c r="C200" s="4" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E200" s="17">
         <v>46275</v>
@@ -5798,31 +5837,43 @@
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="4"/>
       <c r="B201" s="5"/>
-      <c r="C201" s="13">
-        <v>11.9</v>
-      </c>
-      <c r="D201" s="12"/>
-      <c r="E201" s="46"/>
-      <c r="F201" s="12"/>
-      <c r="G201" s="12"/>
+      <c r="C201" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="E201" s="17">
+        <v>46275</v>
+      </c>
+      <c r="F201" s="5"/>
+      <c r="G201" s="5"/>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="4"/>
       <c r="B202" s="5"/>
-      <c r="C202" s="4"/>
-      <c r="D202" s="5"/>
-      <c r="E202" s="17"/>
+      <c r="C202" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="D202" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="E202" s="17">
+        <v>46275</v>
+      </c>
       <c r="F202" s="5"/>
       <c r="G202" s="5"/>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="4"/>
       <c r="B203" s="5"/>
-      <c r="C203" s="4"/>
-      <c r="D203" s="5"/>
-      <c r="E203" s="17"/>
-      <c r="F203" s="5"/>
-      <c r="G203" s="5"/>
+      <c r="C203" s="13">
+        <v>11.9</v>
+      </c>
+      <c r="D203" s="12"/>
+      <c r="E203" s="46"/>
+      <c r="F203" s="12"/>
+      <c r="G203" s="12"/>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="4"/>
@@ -5919,1251 +5970,1097 @@
       <c r="B214" s="5"/>
       <c r="C214" s="4"/>
       <c r="D214" s="5"/>
-      <c r="E214" s="4"/>
+      <c r="E214" s="17"/>
       <c r="F214" s="5"/>
       <c r="G214" s="5"/>
     </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A215" s="4"/>
+      <c r="B215" s="5"/>
+      <c r="C215" s="4"/>
+      <c r="D215" s="5"/>
+      <c r="E215" s="17"/>
+      <c r="F215" s="5"/>
+      <c r="G215" s="5"/>
+    </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B216" t="s">
+      <c r="A216" s="4"/>
+      <c r="B216" s="5"/>
+      <c r="C216" s="4"/>
+      <c r="D216" s="5"/>
+      <c r="E216" s="4"/>
+      <c r="F216" s="5"/>
+      <c r="G216" s="5"/>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B218" t="s">
         <v>565</v>
       </c>
-      <c r="C216" s="1" t="s">
+      <c r="C218" s="1" t="s">
         <v>463</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C217" s="1" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C218" s="1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C219" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C220" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C221" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C222" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C223" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C224" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="225" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C225" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="226" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C226" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="227" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C227" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="228" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C228" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="229" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C229" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="230" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C230" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="231" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C231" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="232" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C232" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="233" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C233" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="234" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C234" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="235" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C235" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="236" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C236" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="237" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C237" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="238" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C238" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="239" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C239" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="240" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C240" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="241" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C241" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="242" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C242" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="243" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C243" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="244" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C244" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="245" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C245" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="246" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C246" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="247" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C247" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="248" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C248" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="249" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C249" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="250" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C250" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="251" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C251" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="252" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C252" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="253" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C253" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="254" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C254" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="255" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C255" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="256" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C256" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="257" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C257" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="258" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C258" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="259" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C259" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="260" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C260" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="261" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C261" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="262" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C262" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="263" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C263" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="264" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C264" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="265" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C265" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="266" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C266" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="267" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C267" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="268" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C268" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="269" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C269" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="270" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C270" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="271" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C271" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="272" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C272" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="273" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C273" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="274" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C274" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="275" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C275" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="276" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C276" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="277" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C277" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="278" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C278" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="279" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C279" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="280" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C280" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="281" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C281" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="282" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C282" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="283" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C283" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="284" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C284" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="285" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C285" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="286" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C286" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="287" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C287" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="288" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C288" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="289" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C289" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="290" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C290" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="291" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C291" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="292" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C292" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="293" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C293" s="1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="294" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C294" s="1" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="295" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C295" s="1" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="295" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B295" t="s">
-        <v>541</v>
-      </c>
-      <c r="C295" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="D295" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="296" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="C296" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="D296" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="297" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="C297" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="D297" t="s">
-        <v>683</v>
-      </c>
-    </row>
     <row r="298" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B298" t="s">
+        <v>571</v>
+      </c>
       <c r="C298" s="1" t="s">
-        <v>680</v>
+        <v>711</v>
       </c>
       <c r="D298" t="s">
-        <v>684</v>
+        <v>712</v>
       </c>
     </row>
     <row r="299" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C299" s="1" t="s">
-        <v>681</v>
+        <v>703</v>
       </c>
       <c r="D299" t="s">
-        <v>685</v>
+        <v>713</v>
       </c>
     </row>
     <row r="300" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C300" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="D300" t="s">
-        <v>687</v>
+        <v>704</v>
       </c>
     </row>
     <row r="301" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C301" s="1" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="302" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C302" s="1" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="303" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C303" s="1" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="304" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C304" s="1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="305" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C305" s="1" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="306" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C306" s="1" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="308" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B308" t="s">
+        <v>541</v>
+      </c>
+      <c r="C308" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D308" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="309" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C309" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="D309" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="310" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C310" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="D310" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="311" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C311" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="D311" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="312" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C312" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="D312" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="313" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C313" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="D313" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="314" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C314" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="D301" t="s">
+      <c r="D314" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="304" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B304" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A309" s="20"/>
-      <c r="B309" s="21"/>
-      <c r="C309" s="20"/>
-      <c r="D309" s="21"/>
-      <c r="E309" s="20"/>
-      <c r="F309" s="21"/>
-      <c r="G309" s="21"/>
-      <c r="H309" s="21"/>
-      <c r="I309" s="21"/>
-      <c r="J309" s="21"/>
-      <c r="K309" s="21"/>
-    </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A310" s="22">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A322" s="20"/>
+      <c r="B322" s="21"/>
+      <c r="C322" s="20"/>
+      <c r="D322" s="21"/>
+      <c r="E322" s="20"/>
+      <c r="F322" s="21"/>
+      <c r="G322" s="21"/>
+      <c r="H322" s="21"/>
+      <c r="I322" s="21"/>
+      <c r="J322" s="21"/>
+      <c r="K322" s="21"/>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A323" s="22">
         <v>13</v>
       </c>
-      <c r="B310" s="23" t="s">
+      <c r="B323" s="23" t="s">
         <v>546</v>
       </c>
-      <c r="C310" s="22" t="s">
+      <c r="C323" s="22" t="s">
         <v>547</v>
       </c>
-      <c r="D310" s="24" t="s">
+      <c r="D323" s="24" t="s">
         <v>553</v>
       </c>
-      <c r="E310" s="22" t="s">
+      <c r="E323" s="22" t="s">
         <v>565</v>
       </c>
-      <c r="F310" s="22" t="s">
+      <c r="F323" s="22" t="s">
         <v>566</v>
       </c>
-      <c r="G310" s="24" t="s">
+      <c r="G323" s="24" t="s">
         <v>567</v>
       </c>
-      <c r="H310" s="24"/>
-      <c r="I310" s="24"/>
-      <c r="J310" s="24"/>
-      <c r="K310" s="24"/>
-    </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A311" s="22"/>
-      <c r="B311" s="24"/>
-      <c r="C311" s="22" t="s">
+      <c r="H323" s="24"/>
+      <c r="I323" s="24"/>
+      <c r="J323" s="24"/>
+      <c r="K323" s="24"/>
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A324" s="22"/>
+      <c r="B324" s="24"/>
+      <c r="C324" s="22" t="s">
         <v>548</v>
       </c>
-      <c r="D311" s="24" t="s">
+      <c r="D324" s="24" t="s">
         <v>555</v>
       </c>
-      <c r="E311" s="22"/>
-      <c r="F311" s="24"/>
-      <c r="G311" s="24"/>
-      <c r="H311" s="24"/>
-      <c r="I311" s="24"/>
-      <c r="J311" s="24"/>
-      <c r="K311" s="24"/>
-    </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A312" s="22"/>
-      <c r="B312" s="24"/>
-      <c r="C312" s="22" t="s">
+      <c r="E324" s="22"/>
+      <c r="F324" s="24"/>
+      <c r="G324" s="24"/>
+      <c r="H324" s="24"/>
+      <c r="I324" s="24"/>
+      <c r="J324" s="24"/>
+      <c r="K324" s="24"/>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A325" s="22"/>
+      <c r="B325" s="24"/>
+      <c r="C325" s="22" t="s">
         <v>549</v>
       </c>
-      <c r="D312" s="24" t="s">
+      <c r="D325" s="24" t="s">
         <v>554</v>
       </c>
-      <c r="E312" s="22"/>
-      <c r="F312" s="24"/>
-      <c r="G312" s="24"/>
-      <c r="H312" s="24"/>
-      <c r="I312" s="24"/>
-      <c r="J312" s="24"/>
-      <c r="K312" s="24"/>
-    </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A313" s="22"/>
-      <c r="B313" s="24"/>
-      <c r="C313" s="22" t="s">
+      <c r="E325" s="22"/>
+      <c r="F325" s="24"/>
+      <c r="G325" s="24"/>
+      <c r="H325" s="24"/>
+      <c r="I325" s="24"/>
+      <c r="J325" s="24"/>
+      <c r="K325" s="24"/>
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A326" s="22"/>
+      <c r="B326" s="24"/>
+      <c r="C326" s="22" t="s">
         <v>550</v>
       </c>
-      <c r="D313" s="24" t="s">
+      <c r="D326" s="24" t="s">
         <v>556</v>
       </c>
-      <c r="E313" s="22"/>
-      <c r="F313" s="24"/>
-      <c r="G313" s="24"/>
-      <c r="H313" s="24"/>
-      <c r="I313" s="24"/>
-      <c r="J313" s="24"/>
-      <c r="K313" s="24"/>
-    </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A314" s="22"/>
-      <c r="B314" s="24"/>
-      <c r="C314" s="22" t="s">
+      <c r="E326" s="22"/>
+      <c r="F326" s="24"/>
+      <c r="G326" s="24"/>
+      <c r="H326" s="24"/>
+      <c r="I326" s="24"/>
+      <c r="J326" s="24"/>
+      <c r="K326" s="24"/>
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A327" s="22"/>
+      <c r="B327" s="24"/>
+      <c r="C327" s="22" t="s">
         <v>551</v>
       </c>
-      <c r="D314" s="24" t="s">
+      <c r="D327" s="24" t="s">
         <v>557</v>
       </c>
-      <c r="E314" s="22"/>
-      <c r="F314" s="24"/>
-      <c r="G314" s="24"/>
-      <c r="H314" s="24"/>
-      <c r="I314" s="24"/>
-      <c r="J314" s="24"/>
-      <c r="K314" s="24"/>
-    </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A315" s="22"/>
-      <c r="B315" s="24"/>
-      <c r="C315" s="22" t="s">
+      <c r="E327" s="22"/>
+      <c r="F327" s="24"/>
+      <c r="G327" s="24"/>
+      <c r="H327" s="24"/>
+      <c r="I327" s="24"/>
+      <c r="J327" s="24"/>
+      <c r="K327" s="24"/>
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A328" s="22"/>
+      <c r="B328" s="24"/>
+      <c r="C328" s="22" t="s">
         <v>552</v>
       </c>
-      <c r="D315" s="24" t="s">
+      <c r="D328" s="24" t="s">
         <v>558</v>
       </c>
-      <c r="E315" s="22"/>
-      <c r="F315" s="24"/>
-      <c r="G315" s="24"/>
-      <c r="H315" s="24"/>
-      <c r="I315" s="24"/>
-      <c r="J315" s="24"/>
-      <c r="K315" s="24"/>
-    </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A316" s="22"/>
-      <c r="B316" s="24"/>
-      <c r="C316" s="22" t="s">
+      <c r="E328" s="22"/>
+      <c r="F328" s="24"/>
+      <c r="G328" s="24"/>
+      <c r="H328" s="24"/>
+      <c r="I328" s="24"/>
+      <c r="J328" s="24"/>
+      <c r="K328" s="24"/>
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A329" s="22"/>
+      <c r="B329" s="24"/>
+      <c r="C329" s="22" t="s">
         <v>559</v>
       </c>
-      <c r="D316" s="24" t="s">
+      <c r="D329" s="24" t="s">
         <v>562</v>
       </c>
-      <c r="E316" s="22"/>
-      <c r="F316" s="24"/>
-      <c r="G316" s="24"/>
-      <c r="H316" s="24"/>
-      <c r="I316" s="24"/>
-      <c r="J316" s="24"/>
-      <c r="K316" s="24"/>
-    </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A317" s="22"/>
-      <c r="B317" s="24"/>
-      <c r="C317" s="22" t="s">
+      <c r="E329" s="22"/>
+      <c r="F329" s="24"/>
+      <c r="G329" s="24"/>
+      <c r="H329" s="24"/>
+      <c r="I329" s="24"/>
+      <c r="J329" s="24"/>
+      <c r="K329" s="24"/>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A330" s="22"/>
+      <c r="B330" s="24"/>
+      <c r="C330" s="22" t="s">
         <v>560</v>
       </c>
-      <c r="D317" s="24" t="s">
+      <c r="D330" s="24" t="s">
         <v>563</v>
       </c>
-      <c r="E317" s="22"/>
-      <c r="F317" s="24"/>
-      <c r="G317" s="24"/>
-      <c r="H317" s="24"/>
-      <c r="I317" s="24"/>
-      <c r="J317" s="24"/>
-      <c r="K317" s="24"/>
-    </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A318" s="22"/>
-      <c r="B318" s="24"/>
-      <c r="C318" s="22" t="s">
+      <c r="E330" s="22"/>
+      <c r="F330" s="24"/>
+      <c r="G330" s="24"/>
+      <c r="H330" s="24"/>
+      <c r="I330" s="24"/>
+      <c r="J330" s="24"/>
+      <c r="K330" s="24"/>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A331" s="22"/>
+      <c r="B331" s="24"/>
+      <c r="C331" s="22" t="s">
         <v>561</v>
       </c>
-      <c r="D318" s="24" t="s">
+      <c r="D331" s="24" t="s">
         <v>564</v>
       </c>
-      <c r="E318" s="22"/>
-      <c r="F318" s="24"/>
-      <c r="G318" s="24"/>
-      <c r="H318" s="24"/>
-      <c r="I318" s="24"/>
-      <c r="J318" s="24"/>
-      <c r="K318" s="24"/>
-    </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A319" s="22"/>
-      <c r="B319" s="24"/>
-      <c r="C319" s="22"/>
-      <c r="D319" s="24"/>
-      <c r="E319" s="22"/>
-      <c r="F319" s="24"/>
-      <c r="G319" s="24"/>
-      <c r="H319" s="24"/>
-      <c r="I319" s="24"/>
-      <c r="J319" s="24"/>
-      <c r="K319" s="24"/>
-    </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A320" s="20"/>
-      <c r="B320" s="21"/>
-      <c r="C320" s="20"/>
-      <c r="D320" s="21"/>
-      <c r="E320" s="20"/>
-      <c r="F320" s="21"/>
-      <c r="G320" s="21"/>
-      <c r="H320" s="21"/>
-      <c r="I320" s="21"/>
-      <c r="J320" s="21"/>
-      <c r="K320" s="21"/>
-    </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A322" s="4">
+      <c r="E331" s="22"/>
+      <c r="F331" s="24"/>
+      <c r="G331" s="24"/>
+      <c r="H331" s="24"/>
+      <c r="I331" s="24"/>
+      <c r="J331" s="24"/>
+      <c r="K331" s="24"/>
+    </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A332" s="22"/>
+      <c r="B332" s="24"/>
+      <c r="C332" s="22"/>
+      <c r="D332" s="24"/>
+      <c r="E332" s="22"/>
+      <c r="F332" s="24"/>
+      <c r="G332" s="24"/>
+      <c r="H332" s="24"/>
+      <c r="I332" s="24"/>
+      <c r="J332" s="24"/>
+      <c r="K332" s="24"/>
+    </row>
+    <row r="333" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A333" s="20"/>
+      <c r="B333" s="21"/>
+      <c r="C333" s="20"/>
+      <c r="D333" s="21"/>
+      <c r="E333" s="20"/>
+      <c r="F333" s="21"/>
+      <c r="G333" s="21"/>
+      <c r="H333" s="21"/>
+      <c r="I333" s="21"/>
+      <c r="J333" s="21"/>
+      <c r="K333" s="21"/>
+    </row>
+    <row r="335" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A335" s="4">
         <v>14</v>
       </c>
-      <c r="B322" s="3" t="s">
+      <c r="B335" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="C322" s="4" t="s">
+      <c r="C335" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="D322" s="5" t="s">
+      <c r="D335" s="5" t="s">
         <v>691</v>
       </c>
-      <c r="E322" s="4"/>
-      <c r="F322" s="5"/>
-      <c r="G322" s="5"/>
-      <c r="H322" s="5"/>
-      <c r="I322" s="5"/>
-      <c r="J322" s="5"/>
-      <c r="K322" s="5"/>
-    </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A323" s="4"/>
-      <c r="B323" s="5"/>
-      <c r="C323" s="4" t="s">
+      <c r="E335" s="4"/>
+      <c r="F335" s="5"/>
+      <c r="G335" s="5"/>
+      <c r="H335" s="5"/>
+      <c r="I335" s="5"/>
+      <c r="J335" s="5"/>
+      <c r="K335" s="5"/>
+    </row>
+    <row r="336" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A336" s="4"/>
+      <c r="B336" s="5"/>
+      <c r="C336" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="D323" s="5" t="s">
+      <c r="D336" s="5" t="s">
         <v>692</v>
       </c>
-      <c r="E323" s="4"/>
-      <c r="F323" s="5"/>
-      <c r="G323" s="5"/>
-      <c r="H323" s="5"/>
-      <c r="I323" s="5"/>
-      <c r="J323" s="5"/>
-      <c r="K323" s="5"/>
-    </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A324" s="4"/>
-      <c r="B324" s="5"/>
-      <c r="C324" s="4" t="s">
+      <c r="E336" s="4"/>
+      <c r="F336" s="5"/>
+      <c r="G336" s="5"/>
+      <c r="H336" s="5"/>
+      <c r="I336" s="5"/>
+      <c r="J336" s="5"/>
+      <c r="K336" s="5"/>
+    </row>
+    <row r="337" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A337" s="4"/>
+      <c r="B337" s="5"/>
+      <c r="C337" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="D324" s="5" t="s">
+      <c r="D337" s="5" t="s">
         <v>694</v>
       </c>
-      <c r="E324" s="4"/>
-      <c r="F324" s="5"/>
-      <c r="G324" s="5"/>
-      <c r="H324" s="5"/>
-      <c r="I324" s="5"/>
-      <c r="J324" s="5"/>
-      <c r="K324" s="5"/>
-    </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A325" s="4"/>
-      <c r="B325" s="5"/>
-      <c r="C325" s="4" t="s">
+      <c r="E337" s="4"/>
+      <c r="F337" s="5"/>
+      <c r="G337" s="5"/>
+      <c r="H337" s="5"/>
+      <c r="I337" s="5"/>
+      <c r="J337" s="5"/>
+      <c r="K337" s="5"/>
+    </row>
+    <row r="338" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A338" s="4"/>
+      <c r="B338" s="5"/>
+      <c r="C338" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="D325" s="5" t="s">
+      <c r="D338" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="E325" s="4"/>
-      <c r="F325" s="5"/>
-      <c r="G325" s="5"/>
-      <c r="H325" s="5"/>
-      <c r="I325" s="5"/>
-      <c r="J325" s="5"/>
-      <c r="K325" s="5"/>
-    </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A326" s="4"/>
-      <c r="B326" s="5"/>
-      <c r="C326" s="4" t="s">
+      <c r="E338" s="4"/>
+      <c r="F338" s="5"/>
+      <c r="G338" s="5"/>
+      <c r="H338" s="5"/>
+      <c r="I338" s="5"/>
+      <c r="J338" s="5"/>
+      <c r="K338" s="5"/>
+    </row>
+    <row r="339" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A339" s="4"/>
+      <c r="B339" s="5"/>
+      <c r="C339" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="D326" s="5" t="s">
+      <c r="D339" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="E326" s="4"/>
-      <c r="F326" s="5"/>
-      <c r="G326" s="5"/>
-      <c r="H326" s="5"/>
-      <c r="I326" s="5"/>
-      <c r="J326" s="5"/>
-      <c r="K326" s="5"/>
-    </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A327" s="4"/>
-      <c r="B327" s="5"/>
-      <c r="C327" s="4" t="s">
+      <c r="E339" s="4"/>
+      <c r="F339" s="5"/>
+      <c r="G339" s="5"/>
+      <c r="H339" s="5"/>
+      <c r="I339" s="5"/>
+      <c r="J339" s="5"/>
+      <c r="K339" s="5"/>
+    </row>
+    <row r="340" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A340" s="4"/>
+      <c r="B340" s="5"/>
+      <c r="C340" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="D327" s="5" t="s">
+      <c r="D340" s="5" t="s">
         <v>700</v>
       </c>
-      <c r="E327" s="4"/>
-      <c r="F327" s="5"/>
-      <c r="G327" s="5"/>
-      <c r="H327" s="5"/>
-      <c r="I327" s="5"/>
-      <c r="J327" s="5"/>
-      <c r="K327" s="5"/>
-    </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A328" s="4"/>
-      <c r="B328" s="5"/>
-      <c r="C328" s="4" t="s">
+      <c r="E340" s="4"/>
+      <c r="F340" s="5"/>
+      <c r="G340" s="5"/>
+      <c r="H340" s="5"/>
+      <c r="I340" s="5"/>
+      <c r="J340" s="5"/>
+      <c r="K340" s="5"/>
+    </row>
+    <row r="341" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A341" s="4"/>
+      <c r="B341" s="5"/>
+      <c r="C341" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="D328" s="5" t="s">
+      <c r="D341" s="5" t="s">
         <v>702</v>
       </c>
-      <c r="E328" s="4"/>
-      <c r="F328" s="5"/>
-      <c r="G328" s="5"/>
-      <c r="H328" s="5"/>
-      <c r="I328" s="5"/>
-      <c r="J328" s="5"/>
-      <c r="K328" s="5"/>
-    </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A329" s="4"/>
-      <c r="B329" s="5"/>
-      <c r="C329" s="4"/>
-      <c r="D329" s="5"/>
-      <c r="E329" s="4"/>
-      <c r="F329" s="5"/>
-      <c r="G329" s="5"/>
-      <c r="H329" s="5"/>
-      <c r="I329" s="5"/>
-      <c r="J329" s="5"/>
-      <c r="K329" s="5"/>
-    </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A330" s="4"/>
-      <c r="B330" s="5"/>
-      <c r="C330" s="4"/>
-      <c r="D330" s="5"/>
-      <c r="E330" s="4"/>
-      <c r="F330" s="5"/>
-      <c r="G330" s="5"/>
-      <c r="H330" s="5"/>
-      <c r="I330" s="5"/>
-      <c r="J330" s="5"/>
-      <c r="K330" s="5"/>
-    </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A331" s="4"/>
-      <c r="B331" s="5"/>
-      <c r="C331" s="4"/>
-      <c r="D331" s="5"/>
-      <c r="E331" s="4"/>
-      <c r="F331" s="5"/>
-      <c r="G331" s="5"/>
-      <c r="H331" s="5"/>
-      <c r="I331" s="5"/>
-      <c r="J331" s="5"/>
-      <c r="K331" s="5"/>
-    </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A332" s="4"/>
-      <c r="B332" s="5"/>
-      <c r="C332" s="4"/>
-      <c r="D332" s="5"/>
-      <c r="E332" s="4"/>
-      <c r="F332" s="5"/>
-      <c r="G332" s="5"/>
-      <c r="H332" s="5"/>
-      <c r="I332" s="5"/>
-      <c r="J332" s="5"/>
-      <c r="K332" s="5"/>
-    </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C334" s="1" t="s">
+      <c r="E341" s="4"/>
+      <c r="F341" s="5"/>
+      <c r="G341" s="5"/>
+      <c r="H341" s="5"/>
+      <c r="I341" s="5"/>
+      <c r="J341" s="5"/>
+      <c r="K341" s="5"/>
+    </row>
+    <row r="342" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A342" s="4"/>
+      <c r="B342" s="5"/>
+      <c r="C342" s="4"/>
+      <c r="D342" s="5"/>
+      <c r="E342" s="4"/>
+      <c r="F342" s="5"/>
+      <c r="G342" s="5"/>
+      <c r="H342" s="5"/>
+      <c r="I342" s="5"/>
+      <c r="J342" s="5"/>
+      <c r="K342" s="5"/>
+    </row>
+    <row r="343" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A343" s="4"/>
+      <c r="B343" s="5"/>
+      <c r="C343" s="4"/>
+      <c r="D343" s="5"/>
+      <c r="E343" s="4"/>
+      <c r="F343" s="5"/>
+      <c r="G343" s="5"/>
+      <c r="H343" s="5"/>
+      <c r="I343" s="5"/>
+      <c r="J343" s="5"/>
+      <c r="K343" s="5"/>
+    </row>
+    <row r="344" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A344" s="4"/>
+      <c r="B344" s="5"/>
+      <c r="C344" s="4"/>
+      <c r="D344" s="5"/>
+      <c r="E344" s="4"/>
+      <c r="F344" s="5"/>
+      <c r="G344" s="5"/>
+      <c r="H344" s="5"/>
+      <c r="I344" s="5"/>
+      <c r="J344" s="5"/>
+      <c r="K344" s="5"/>
+    </row>
+    <row r="345" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A345" s="4"/>
+      <c r="B345" s="5"/>
+      <c r="C345" s="4"/>
+      <c r="D345" s="5"/>
+      <c r="E345" s="4"/>
+      <c r="F345" s="5"/>
+      <c r="G345" s="5"/>
+      <c r="H345" s="5"/>
+      <c r="I345" s="5"/>
+      <c r="J345" s="5"/>
+      <c r="K345" s="5"/>
+    </row>
+    <row r="347" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C347" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C335" s="1" t="s">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C348" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D335" t="s">
+      <c r="D348" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C336" s="1" t="s">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C349" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="D336" t="s">
+      <c r="D349" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="337" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C337" s="1" t="s">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C350" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D337" t="s">
+      <c r="D350" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="338" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C338" s="1" t="s">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C351" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D338" t="s">
+      <c r="D351" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="339" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C339" s="1" t="s">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C352" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D339" t="s">
+      <c r="D352" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="340" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C340" s="1" t="s">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C353" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="D340" t="s">
+      <c r="D353" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="341" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C341" s="1" t="s">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C354" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="D341" t="s">
+      <c r="D354" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="342" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C342" s="1" t="s">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C355" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="D342" t="s">
+      <c r="D355" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="343" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C343" s="1" t="s">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C356" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="D343" t="s">
+      <c r="D356" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="344" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C344" s="1" t="s">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C357" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D344" t="s">
+      <c r="D357" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="345" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C345" s="1" t="s">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C358" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="D345" t="s">
+      <c r="D358" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="346" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C346" s="1" t="s">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C359" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="D346" t="s">
+      <c r="D359" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="347" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C347" s="1" t="s">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C360" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D347" t="s">
+      <c r="D360" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="348" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C348" s="1" t="s">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C361" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="D348" t="s">
+      <c r="D361" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="349" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C349" s="1" t="s">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C362" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D349" t="s">
+      <c r="D362" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="350" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C350" s="1" t="s">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C363" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="D350" t="s">
+      <c r="D363" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="351" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C351" s="1" t="s">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C364" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="D351" t="s">
+      <c r="D364" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="352" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C352" s="1" t="s">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C365" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="D352" t="s">
+      <c r="D365" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="D353" t="s">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D366" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A354" s="26"/>
-      <c r="B354" s="25"/>
-      <c r="C354" s="26"/>
-      <c r="D354" s="25"/>
-      <c r="E354" s="26"/>
-      <c r="F354" s="25"/>
-      <c r="G354" s="25"/>
-      <c r="H354" s="25"/>
-      <c r="I354" s="25"/>
-      <c r="J354" s="25"/>
-      <c r="K354" s="25"/>
-    </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A355" s="39">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A367" s="26"/>
+      <c r="B367" s="25"/>
+      <c r="C367" s="26"/>
+      <c r="D367" s="25"/>
+      <c r="E367" s="26"/>
+      <c r="F367" s="25"/>
+      <c r="G367" s="25"/>
+      <c r="H367" s="25"/>
+      <c r="I367" s="25"/>
+      <c r="J367" s="25"/>
+      <c r="K367" s="25"/>
+    </row>
+    <row r="368" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A368" s="39">
         <v>16</v>
       </c>
-      <c r="B355" s="40" t="s">
+      <c r="B368" s="40" t="s">
         <v>385</v>
       </c>
-      <c r="C355" s="41" t="s">
+      <c r="C368" s="41" t="s">
         <v>337</v>
       </c>
-      <c r="D355" s="42" t="s">
+      <c r="D368" s="42" t="s">
         <v>349</v>
       </c>
-      <c r="E355" s="39" t="s">
+      <c r="E368" s="39" t="s">
         <v>565</v>
       </c>
-      <c r="F355" s="42" t="s">
+      <c r="F368" s="42" t="s">
         <v>385</v>
       </c>
-      <c r="G355" s="42"/>
-      <c r="H355" s="42"/>
-      <c r="I355" s="42"/>
-      <c r="J355" s="42"/>
-      <c r="K355" s="42"/>
-    </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A356" s="39"/>
-      <c r="B356" s="42"/>
-      <c r="C356" s="41" t="s">
-        <v>338</v>
-      </c>
-      <c r="D356" s="42" t="s">
-        <v>350</v>
-      </c>
-      <c r="E356" s="39"/>
-      <c r="F356" s="42"/>
-      <c r="G356" s="42"/>
-      <c r="H356" s="42"/>
-      <c r="I356" s="42"/>
-      <c r="J356" s="42"/>
-      <c r="K356" s="42"/>
-    </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A357" s="39"/>
-      <c r="B357" s="42"/>
-      <c r="C357" s="41" t="s">
-        <v>339</v>
-      </c>
-      <c r="D357" s="42" t="s">
-        <v>351</v>
-      </c>
-      <c r="E357" s="39"/>
-      <c r="F357" s="42"/>
-      <c r="G357" s="42"/>
-      <c r="H357" s="42"/>
-      <c r="I357" s="42"/>
-      <c r="J357" s="42"/>
-      <c r="K357" s="42"/>
-    </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A358" s="39"/>
-      <c r="B358" s="42"/>
-      <c r="C358" s="41" t="s">
-        <v>340</v>
-      </c>
-      <c r="D358" s="42" t="s">
-        <v>352</v>
-      </c>
-      <c r="E358" s="39"/>
-      <c r="F358" s="42"/>
-      <c r="G358" s="42"/>
-      <c r="H358" s="42"/>
-      <c r="I358" s="42"/>
-      <c r="J358" s="42"/>
-      <c r="K358" s="42"/>
-    </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A359" s="39"/>
-      <c r="B359" s="42"/>
-      <c r="C359" s="41" t="s">
-        <v>341</v>
-      </c>
-      <c r="D359" s="42" t="s">
-        <v>353</v>
-      </c>
-      <c r="E359" s="39"/>
-      <c r="F359" s="42"/>
-      <c r="G359" s="42"/>
-      <c r="H359" s="42"/>
-      <c r="I359" s="42"/>
-      <c r="J359" s="42"/>
-      <c r="K359" s="42"/>
-    </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A360" s="39"/>
-      <c r="B360" s="42"/>
-      <c r="C360" s="41" t="s">
-        <v>342</v>
-      </c>
-      <c r="D360" s="42" t="s">
-        <v>354</v>
-      </c>
-      <c r="E360" s="39"/>
-      <c r="F360" s="42"/>
-      <c r="G360" s="42"/>
-      <c r="H360" s="42"/>
-      <c r="I360" s="42"/>
-      <c r="J360" s="42"/>
-      <c r="K360" s="42"/>
-    </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A361" s="39"/>
-      <c r="B361" s="42"/>
-      <c r="C361" s="41" t="s">
-        <v>343</v>
-      </c>
-      <c r="D361" s="42" t="s">
-        <v>355</v>
-      </c>
-      <c r="E361" s="39"/>
-      <c r="F361" s="42"/>
-      <c r="G361" s="42"/>
-      <c r="H361" s="42"/>
-      <c r="I361" s="42"/>
-      <c r="J361" s="42"/>
-      <c r="K361" s="42"/>
-    </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A362" s="39"/>
-      <c r="B362" s="42"/>
-      <c r="C362" s="41" t="s">
-        <v>344</v>
-      </c>
-      <c r="D362" s="42" t="s">
-        <v>356</v>
-      </c>
-      <c r="E362" s="39"/>
-      <c r="F362" s="42"/>
-      <c r="G362" s="42"/>
-      <c r="H362" s="42"/>
-      <c r="I362" s="42"/>
-      <c r="J362" s="42"/>
-      <c r="K362" s="42"/>
-    </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A363" s="39"/>
-      <c r="B363" s="42"/>
-      <c r="C363" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="D363" s="42" t="s">
-        <v>357</v>
-      </c>
-      <c r="E363" s="39"/>
-      <c r="F363" s="42"/>
-      <c r="G363" s="42"/>
-      <c r="H363" s="42"/>
-      <c r="I363" s="42"/>
-      <c r="J363" s="42"/>
-      <c r="K363" s="42"/>
-    </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A364" s="39"/>
-      <c r="B364" s="42"/>
-      <c r="C364" s="41" t="s">
-        <v>346</v>
-      </c>
-      <c r="D364" s="42" t="s">
-        <v>359</v>
-      </c>
-      <c r="E364" s="39"/>
-      <c r="F364" s="42"/>
-      <c r="G364" s="42"/>
-      <c r="H364" s="42"/>
-      <c r="I364" s="42"/>
-      <c r="J364" s="42"/>
-      <c r="K364" s="42"/>
-    </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A365" s="39"/>
-      <c r="B365" s="42"/>
-      <c r="C365" s="41" t="s">
-        <v>347</v>
-      </c>
-      <c r="D365" s="42" t="s">
-        <v>358</v>
-      </c>
-      <c r="E365" s="39"/>
-      <c r="F365" s="42"/>
-      <c r="G365" s="42"/>
-      <c r="H365" s="42"/>
-      <c r="I365" s="42"/>
-      <c r="J365" s="42"/>
-      <c r="K365" s="42"/>
-    </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A366" s="39"/>
-      <c r="B366" s="42"/>
-      <c r="C366" s="41" t="s">
-        <v>348</v>
-      </c>
-      <c r="D366" s="42" t="s">
-        <v>360</v>
-      </c>
-      <c r="E366" s="39"/>
-      <c r="F366" s="42"/>
-      <c r="G366" s="42"/>
-      <c r="H366" s="42"/>
-      <c r="I366" s="42"/>
-      <c r="J366" s="42"/>
-      <c r="K366" s="42"/>
-    </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A367" s="39"/>
-      <c r="B367" s="42"/>
-      <c r="C367" s="41" t="s">
-        <v>372</v>
-      </c>
-      <c r="D367" s="42" t="s">
-        <v>361</v>
-      </c>
-      <c r="E367" s="39"/>
-      <c r="F367" s="42"/>
-      <c r="G367" s="42"/>
-      <c r="H367" s="42"/>
-      <c r="I367" s="42"/>
-      <c r="J367" s="42"/>
-      <c r="K367" s="42"/>
-    </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A368" s="39"/>
-      <c r="B368" s="42"/>
-      <c r="C368" s="41" t="s">
-        <v>373</v>
-      </c>
-      <c r="D368" s="42" t="s">
-        <v>362</v>
-      </c>
-      <c r="E368" s="39"/>
-      <c r="F368" s="42"/>
       <c r="G368" s="42"/>
       <c r="H368" s="42"/>
       <c r="I368" s="42"/>
@@ -7174,10 +7071,10 @@
       <c r="A369" s="39"/>
       <c r="B369" s="42"/>
       <c r="C369" s="41" t="s">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="D369" s="42" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="E369" s="39"/>
       <c r="F369" s="42"/>
@@ -7191,10 +7088,10 @@
       <c r="A370" s="39"/>
       <c r="B370" s="42"/>
       <c r="C370" s="41" t="s">
-        <v>375</v>
+        <v>339</v>
       </c>
       <c r="D370" s="42" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="E370" s="39"/>
       <c r="F370" s="42"/>
@@ -7208,10 +7105,10 @@
       <c r="A371" s="39"/>
       <c r="B371" s="42"/>
       <c r="C371" s="41" t="s">
-        <v>376</v>
+        <v>340</v>
       </c>
       <c r="D371" s="42" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="E371" s="39"/>
       <c r="F371" s="42"/>
@@ -7225,10 +7122,10 @@
       <c r="A372" s="39"/>
       <c r="B372" s="42"/>
       <c r="C372" s="41" t="s">
-        <v>377</v>
+        <v>341</v>
       </c>
       <c r="D372" s="42" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="E372" s="39"/>
       <c r="F372" s="42"/>
@@ -7242,10 +7139,10 @@
       <c r="A373" s="39"/>
       <c r="B373" s="42"/>
       <c r="C373" s="41" t="s">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="D373" s="42" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="E373" s="39"/>
       <c r="F373" s="42"/>
@@ -7259,10 +7156,10 @@
       <c r="A374" s="39"/>
       <c r="B374" s="42"/>
       <c r="C374" s="41" t="s">
-        <v>379</v>
+        <v>343</v>
       </c>
       <c r="D374" s="42" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="E374" s="39"/>
       <c r="F374" s="42"/>
@@ -7276,10 +7173,10 @@
       <c r="A375" s="39"/>
       <c r="B375" s="42"/>
       <c r="C375" s="41" t="s">
-        <v>380</v>
+        <v>344</v>
       </c>
       <c r="D375" s="42" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="E375" s="39"/>
       <c r="F375" s="42"/>
@@ -7293,10 +7190,10 @@
       <c r="A376" s="39"/>
       <c r="B376" s="42"/>
       <c r="C376" s="41" t="s">
-        <v>381</v>
+        <v>345</v>
       </c>
       <c r="D376" s="42" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="E376" s="39"/>
       <c r="F376" s="42"/>
@@ -7310,10 +7207,10 @@
       <c r="A377" s="39"/>
       <c r="B377" s="42"/>
       <c r="C377" s="41" t="s">
-        <v>382</v>
+        <v>346</v>
       </c>
       <c r="D377" s="42" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="E377" s="39"/>
       <c r="F377" s="42"/>
@@ -7327,10 +7224,10 @@
       <c r="A378" s="39"/>
       <c r="B378" s="42"/>
       <c r="C378" s="41" t="s">
-        <v>383</v>
+        <v>347</v>
       </c>
       <c r="D378" s="42" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="E378" s="39"/>
       <c r="F378" s="42"/>
@@ -7341,447 +7238,499 @@
       <c r="K378" s="42"/>
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A379" s="26"/>
-      <c r="B379" s="25"/>
-      <c r="C379" s="26"/>
-      <c r="D379" s="25"/>
-      <c r="E379" s="26"/>
-      <c r="F379" s="25"/>
-      <c r="G379" s="25"/>
-      <c r="H379" s="25"/>
-      <c r="I379" s="25"/>
-      <c r="J379" s="25"/>
-      <c r="K379" s="25"/>
+      <c r="A379" s="39"/>
+      <c r="B379" s="42"/>
+      <c r="C379" s="41" t="s">
+        <v>348</v>
+      </c>
+      <c r="D379" s="42" t="s">
+        <v>360</v>
+      </c>
+      <c r="E379" s="39"/>
+      <c r="F379" s="42"/>
+      <c r="G379" s="42"/>
+      <c r="H379" s="42"/>
+      <c r="I379" s="42"/>
+      <c r="J379" s="42"/>
+      <c r="K379" s="42"/>
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A380" s="32"/>
-      <c r="B380" s="33" t="s">
+      <c r="A380" s="39"/>
+      <c r="B380" s="42"/>
+      <c r="C380" s="41" t="s">
+        <v>372</v>
+      </c>
+      <c r="D380" s="42" t="s">
+        <v>361</v>
+      </c>
+      <c r="E380" s="39"/>
+      <c r="F380" s="42"/>
+      <c r="G380" s="42"/>
+      <c r="H380" s="42"/>
+      <c r="I380" s="42"/>
+      <c r="J380" s="42"/>
+      <c r="K380" s="42"/>
+    </row>
+    <row r="381" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A381" s="39"/>
+      <c r="B381" s="42"/>
+      <c r="C381" s="41" t="s">
+        <v>373</v>
+      </c>
+      <c r="D381" s="42" t="s">
+        <v>362</v>
+      </c>
+      <c r="E381" s="39"/>
+      <c r="F381" s="42"/>
+      <c r="G381" s="42"/>
+      <c r="H381" s="42"/>
+      <c r="I381" s="42"/>
+      <c r="J381" s="42"/>
+      <c r="K381" s="42"/>
+    </row>
+    <row r="382" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A382" s="39"/>
+      <c r="B382" s="42"/>
+      <c r="C382" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="D382" s="42" t="s">
+        <v>363</v>
+      </c>
+      <c r="E382" s="39"/>
+      <c r="F382" s="42"/>
+      <c r="G382" s="42"/>
+      <c r="H382" s="42"/>
+      <c r="I382" s="42"/>
+      <c r="J382" s="42"/>
+      <c r="K382" s="42"/>
+    </row>
+    <row r="383" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A383" s="39"/>
+      <c r="B383" s="42"/>
+      <c r="C383" s="41" t="s">
+        <v>375</v>
+      </c>
+      <c r="D383" s="42" t="s">
+        <v>364</v>
+      </c>
+      <c r="E383" s="39"/>
+      <c r="F383" s="42"/>
+      <c r="G383" s="42"/>
+      <c r="H383" s="42"/>
+      <c r="I383" s="42"/>
+      <c r="J383" s="42"/>
+      <c r="K383" s="42"/>
+    </row>
+    <row r="384" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A384" s="39"/>
+      <c r="B384" s="42"/>
+      <c r="C384" s="41" t="s">
+        <v>376</v>
+      </c>
+      <c r="D384" s="42" t="s">
+        <v>365</v>
+      </c>
+      <c r="E384" s="39"/>
+      <c r="F384" s="42"/>
+      <c r="G384" s="42"/>
+      <c r="H384" s="42"/>
+      <c r="I384" s="42"/>
+      <c r="J384" s="42"/>
+      <c r="K384" s="42"/>
+    </row>
+    <row r="385" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A385" s="39"/>
+      <c r="B385" s="42"/>
+      <c r="C385" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="D385" s="42" t="s">
+        <v>366</v>
+      </c>
+      <c r="E385" s="39"/>
+      <c r="F385" s="42"/>
+      <c r="G385" s="42"/>
+      <c r="H385" s="42"/>
+      <c r="I385" s="42"/>
+      <c r="J385" s="42"/>
+      <c r="K385" s="42"/>
+    </row>
+    <row r="386" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A386" s="39"/>
+      <c r="B386" s="42"/>
+      <c r="C386" s="41" t="s">
+        <v>378</v>
+      </c>
+      <c r="D386" s="42" t="s">
+        <v>367</v>
+      </c>
+      <c r="E386" s="39"/>
+      <c r="F386" s="42"/>
+      <c r="G386" s="42"/>
+      <c r="H386" s="42"/>
+      <c r="I386" s="42"/>
+      <c r="J386" s="42"/>
+      <c r="K386" s="42"/>
+    </row>
+    <row r="387" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A387" s="39"/>
+      <c r="B387" s="42"/>
+      <c r="C387" s="41" t="s">
+        <v>379</v>
+      </c>
+      <c r="D387" s="42" t="s">
+        <v>368</v>
+      </c>
+      <c r="E387" s="39"/>
+      <c r="F387" s="42"/>
+      <c r="G387" s="42"/>
+      <c r="H387" s="42"/>
+      <c r="I387" s="42"/>
+      <c r="J387" s="42"/>
+      <c r="K387" s="42"/>
+    </row>
+    <row r="388" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A388" s="39"/>
+      <c r="B388" s="42"/>
+      <c r="C388" s="41" t="s">
+        <v>380</v>
+      </c>
+      <c r="D388" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="E388" s="39"/>
+      <c r="F388" s="42"/>
+      <c r="G388" s="42"/>
+      <c r="H388" s="42"/>
+      <c r="I388" s="42"/>
+      <c r="J388" s="42"/>
+      <c r="K388" s="42"/>
+    </row>
+    <row r="389" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A389" s="39"/>
+      <c r="B389" s="42"/>
+      <c r="C389" s="41" t="s">
+        <v>381</v>
+      </c>
+      <c r="D389" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="E389" s="39"/>
+      <c r="F389" s="42"/>
+      <c r="G389" s="42"/>
+      <c r="H389" s="42"/>
+      <c r="I389" s="42"/>
+      <c r="J389" s="42"/>
+      <c r="K389" s="42"/>
+    </row>
+    <row r="390" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A390" s="39"/>
+      <c r="B390" s="42"/>
+      <c r="C390" s="41" t="s">
+        <v>382</v>
+      </c>
+      <c r="D390" s="42" t="s">
+        <v>371</v>
+      </c>
+      <c r="E390" s="39"/>
+      <c r="F390" s="42"/>
+      <c r="G390" s="42"/>
+      <c r="H390" s="42"/>
+      <c r="I390" s="42"/>
+      <c r="J390" s="42"/>
+      <c r="K390" s="42"/>
+    </row>
+    <row r="391" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A391" s="39"/>
+      <c r="B391" s="42"/>
+      <c r="C391" s="41" t="s">
+        <v>383</v>
+      </c>
+      <c r="D391" s="42" t="s">
+        <v>384</v>
+      </c>
+      <c r="E391" s="39"/>
+      <c r="F391" s="42"/>
+      <c r="G391" s="42"/>
+      <c r="H391" s="42"/>
+      <c r="I391" s="42"/>
+      <c r="J391" s="42"/>
+      <c r="K391" s="42"/>
+    </row>
+    <row r="392" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A392" s="26"/>
+      <c r="B392" s="25"/>
+      <c r="C392" s="26"/>
+      <c r="D392" s="25"/>
+      <c r="E392" s="26"/>
+      <c r="F392" s="25"/>
+      <c r="G392" s="25"/>
+      <c r="H392" s="25"/>
+      <c r="I392" s="25"/>
+      <c r="J392" s="25"/>
+      <c r="K392" s="25"/>
+    </row>
+    <row r="393" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A393" s="32"/>
+      <c r="B393" s="33" t="s">
         <v>424</v>
       </c>
-      <c r="C380" s="32" t="s">
+      <c r="C393" s="32" t="s">
         <v>425</v>
       </c>
-      <c r="D380" s="38" t="s">
+      <c r="D393" s="38" t="s">
         <v>426</v>
       </c>
-      <c r="E380" s="32"/>
-      <c r="F380" s="33"/>
-      <c r="G380" s="33"/>
-    </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A381" s="4"/>
-      <c r="B381" s="5"/>
-      <c r="C381" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="D381" s="18" t="s">
-        <v>428</v>
-      </c>
-      <c r="E381" s="4"/>
-      <c r="F381" s="5"/>
-      <c r="G381" s="5"/>
-    </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A383" s="4"/>
-      <c r="B383" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="C383" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="D383" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="E383" s="4"/>
-      <c r="F383" s="5"/>
-      <c r="G383" s="5"/>
-    </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A384" s="4"/>
-      <c r="B384" s="5"/>
-      <c r="C384" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="D384" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="E384" s="4"/>
-      <c r="F384" s="5"/>
-      <c r="G384" s="5"/>
-    </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A385" s="4"/>
-      <c r="B385" s="5"/>
-      <c r="C385" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="D385" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="E385" s="4"/>
-      <c r="F385" s="5"/>
-      <c r="G385" s="5"/>
-    </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A386" s="4"/>
-      <c r="B386" s="5"/>
-      <c r="C386" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="D386" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="E386" s="4"/>
-      <c r="F386" s="5"/>
-      <c r="G386" s="5"/>
-    </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A387" s="4"/>
-      <c r="B387" s="5"/>
-      <c r="C387" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="D387" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="E387" s="4"/>
-      <c r="F387" s="5"/>
-      <c r="G387" s="5"/>
-    </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A388" s="4"/>
-      <c r="B388" s="5"/>
-      <c r="C388" s="4"/>
-      <c r="D388" s="5"/>
-      <c r="E388" s="4"/>
-      <c r="F388" s="5"/>
-      <c r="G388" s="5"/>
-    </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A389" s="4"/>
-      <c r="B389" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="C389" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="D389" s="16" t="s">
-        <v>450</v>
-      </c>
-      <c r="E389" s="4"/>
-      <c r="F389" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="G389" s="5"/>
-    </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A390" s="4"/>
-      <c r="B390" s="5"/>
-      <c r="C390" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="D390" s="16" t="s">
-        <v>451</v>
-      </c>
-      <c r="E390" s="4"/>
-      <c r="F390" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="G390" s="5"/>
-    </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A391" s="4"/>
-      <c r="B391" s="5"/>
-      <c r="C391" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="D391" s="16" t="s">
-        <v>452</v>
-      </c>
-      <c r="E391" s="4"/>
-      <c r="F391" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="G391" s="5"/>
-    </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A392" s="4"/>
-      <c r="B392" s="5"/>
-      <c r="C392" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D392" s="16" t="s">
-        <v>454</v>
-      </c>
-      <c r="E392" s="4"/>
-      <c r="F392" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="G392" s="5"/>
-    </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A393" s="4"/>
-      <c r="B393" s="5"/>
-      <c r="C393" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="D393" s="16" t="s">
-        <v>440</v>
-      </c>
-      <c r="E393" s="4"/>
-      <c r="F393" s="5"/>
-      <c r="G393" s="5"/>
-    </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E393" s="32"/>
+      <c r="F393" s="33"/>
+      <c r="G393" s="33"/>
+    </row>
+    <row r="394" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A394" s="4"/>
       <c r="B394" s="5"/>
-      <c r="C394" s="4"/>
-      <c r="D394" s="5"/>
+      <c r="C394" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="D394" s="18" t="s">
+        <v>428</v>
+      </c>
       <c r="E394" s="4"/>
       <c r="F394" s="5"/>
       <c r="G394" s="5"/>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A395" s="4"/>
-      <c r="B395" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="C395" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="D395" s="16" t="s">
-        <v>442</v>
-      </c>
-      <c r="E395" s="4"/>
-      <c r="F395" s="5"/>
-      <c r="G395" s="5"/>
-    </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A396" s="4"/>
-      <c r="B396" s="5"/>
+      <c r="B396" s="5" t="s">
+        <v>435</v>
+      </c>
       <c r="C396" s="4" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="D396" s="16" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="E396" s="4"/>
       <c r="F396" s="5"/>
       <c r="G396" s="5"/>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A397" s="4"/>
       <c r="B397" s="5"/>
       <c r="C397" s="4" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="D397" s="16" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="E397" s="4"/>
       <c r="F397" s="5"/>
       <c r="G397" s="5"/>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A398" s="4"/>
       <c r="B398" s="5"/>
       <c r="C398" s="4" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="D398" s="16" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="E398" s="4"/>
       <c r="F398" s="5"/>
       <c r="G398" s="5"/>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A399" s="4"/>
       <c r="B399" s="5"/>
       <c r="C399" s="4" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="D399" s="16" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="E399" s="4"/>
       <c r="F399" s="5"/>
       <c r="G399" s="5"/>
     </row>
+    <row r="400" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A400" s="4"/>
+      <c r="B400" s="5"/>
+      <c r="C400" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="D400" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="E400" s="4"/>
+      <c r="F400" s="5"/>
+      <c r="G400" s="5"/>
+    </row>
+    <row r="401" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A401" s="4"/>
+      <c r="B401" s="5"/>
+      <c r="C401" s="4"/>
+      <c r="D401" s="5"/>
+      <c r="E401" s="4"/>
+      <c r="F401" s="5"/>
+      <c r="G401" s="5"/>
+    </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A402" s="43"/>
-      <c r="B402" s="44"/>
-      <c r="C402" s="43"/>
-      <c r="D402" s="45"/>
-      <c r="E402" s="43"/>
-      <c r="F402" s="44"/>
-      <c r="G402" s="44"/>
-      <c r="H402" s="44"/>
-      <c r="I402" s="44"/>
-      <c r="J402" s="44"/>
-      <c r="K402" s="44"/>
+      <c r="A402" s="4"/>
+      <c r="B402" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C402" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="D402" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="E402" s="4"/>
+      <c r="F402" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="G402" s="5"/>
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A403" s="43"/>
-      <c r="B403" s="44"/>
-      <c r="C403" s="43"/>
-      <c r="D403" s="45"/>
-      <c r="E403" s="43"/>
-      <c r="F403" s="44"/>
-      <c r="G403" s="44"/>
-      <c r="H403" s="44"/>
-      <c r="I403" s="44"/>
-      <c r="J403" s="44"/>
-      <c r="K403" s="44"/>
+      <c r="A403" s="4"/>
+      <c r="B403" s="5"/>
+      <c r="C403" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="D403" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="E403" s="4"/>
+      <c r="F403" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="G403" s="5"/>
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A404" s="43"/>
-      <c r="B404" s="44"/>
-      <c r="C404" s="43"/>
-      <c r="D404" s="44"/>
-      <c r="E404" s="43"/>
-      <c r="F404" s="44"/>
-      <c r="G404" s="44"/>
-      <c r="H404" s="44"/>
-      <c r="I404" s="44"/>
-      <c r="J404" s="44"/>
-      <c r="K404" s="44"/>
+      <c r="A404" s="4"/>
+      <c r="B404" s="5"/>
+      <c r="C404" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D404" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="E404" s="4"/>
+      <c r="F404" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="G404" s="5"/>
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A405" s="43"/>
-      <c r="B405" s="44"/>
-      <c r="C405" s="43"/>
-      <c r="D405" s="44"/>
-      <c r="E405" s="43"/>
-      <c r="F405" s="44"/>
-      <c r="G405" s="44"/>
-      <c r="H405" s="44"/>
-      <c r="I405" s="44"/>
-      <c r="J405" s="44"/>
-      <c r="K405" s="44"/>
+      <c r="A405" s="4"/>
+      <c r="B405" s="5"/>
+      <c r="C405" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D405" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="E405" s="4"/>
+      <c r="F405" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="G405" s="5"/>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A406" s="43"/>
-      <c r="B406" s="44"/>
-      <c r="C406" s="43"/>
-      <c r="D406" s="44"/>
-      <c r="E406" s="43"/>
-      <c r="F406" s="44"/>
-      <c r="G406" s="44"/>
-      <c r="H406" s="44"/>
-      <c r="I406" s="44"/>
-      <c r="J406" s="44"/>
-      <c r="K406" s="44"/>
+      <c r="A406" s="4"/>
+      <c r="B406" s="5"/>
+      <c r="C406" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="D406" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="E406" s="4"/>
+      <c r="F406" s="5"/>
+      <c r="G406" s="5"/>
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A407" s="43"/>
-      <c r="B407" s="44"/>
-      <c r="C407" s="43"/>
-      <c r="D407" s="44"/>
-      <c r="E407" s="43"/>
-      <c r="F407" s="44"/>
-      <c r="G407" s="44"/>
-      <c r="H407" s="44"/>
-      <c r="I407" s="44"/>
-      <c r="J407" s="44"/>
-      <c r="K407" s="44"/>
+      <c r="A407" s="4"/>
+      <c r="B407" s="5"/>
+      <c r="C407" s="4"/>
+      <c r="D407" s="5"/>
+      <c r="E407" s="4"/>
+      <c r="F407" s="5"/>
+      <c r="G407" s="5"/>
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A408" s="43"/>
-      <c r="B408" s="44"/>
-      <c r="C408" s="43"/>
-      <c r="D408" s="44"/>
-      <c r="E408" s="43"/>
-      <c r="F408" s="44"/>
-      <c r="G408" s="44"/>
-      <c r="H408" s="44"/>
-      <c r="I408" s="44"/>
-      <c r="J408" s="44"/>
-      <c r="K408" s="44"/>
+      <c r="A408" s="4"/>
+      <c r="B408" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="C408" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="D408" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="E408" s="4"/>
+      <c r="F408" s="5"/>
+      <c r="G408" s="5"/>
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A409" s="43"/>
-      <c r="B409" s="44"/>
-      <c r="C409" s="43"/>
-      <c r="D409" s="44"/>
-      <c r="E409" s="43"/>
-      <c r="F409" s="44"/>
-      <c r="G409" s="44"/>
-      <c r="H409" s="44"/>
-      <c r="I409" s="44"/>
-      <c r="J409" s="44"/>
-      <c r="K409" s="44"/>
+      <c r="A409" s="4"/>
+      <c r="B409" s="5"/>
+      <c r="C409" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="D409" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="E409" s="4"/>
+      <c r="F409" s="5"/>
+      <c r="G409" s="5"/>
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A410" s="43"/>
-      <c r="B410" s="44"/>
-      <c r="C410" s="43"/>
-      <c r="D410" s="44"/>
-      <c r="E410" s="43"/>
-      <c r="F410" s="44"/>
-      <c r="G410" s="44"/>
-      <c r="H410" s="44"/>
-      <c r="I410" s="44"/>
-      <c r="J410" s="44"/>
-      <c r="K410" s="44"/>
+      <c r="A410" s="4"/>
+      <c r="B410" s="5"/>
+      <c r="C410" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="D410" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="E410" s="4"/>
+      <c r="F410" s="5"/>
+      <c r="G410" s="5"/>
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A411" s="43"/>
-      <c r="B411" s="44"/>
-      <c r="C411" s="43"/>
-      <c r="D411" s="44"/>
-      <c r="E411" s="43"/>
-      <c r="F411" s="44"/>
-      <c r="G411" s="44"/>
-      <c r="H411" s="44"/>
-      <c r="I411" s="44"/>
-      <c r="J411" s="44"/>
-      <c r="K411" s="44"/>
+      <c r="A411" s="4"/>
+      <c r="B411" s="5"/>
+      <c r="C411" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="D411" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="E411" s="4"/>
+      <c r="F411" s="5"/>
+      <c r="G411" s="5"/>
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A412" s="43"/>
-      <c r="B412" s="44"/>
-      <c r="C412" s="43"/>
-      <c r="D412" s="44"/>
-      <c r="E412" s="43"/>
-      <c r="F412" s="44"/>
-      <c r="G412" s="44"/>
-      <c r="H412" s="44"/>
-      <c r="I412" s="44"/>
-      <c r="J412" s="44"/>
-      <c r="K412" s="44"/>
-    </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A413" s="43"/>
-      <c r="B413" s="44"/>
-      <c r="C413" s="43"/>
-      <c r="D413" s="44"/>
-      <c r="E413" s="43"/>
-      <c r="F413" s="44"/>
-      <c r="G413" s="44"/>
-      <c r="H413" s="44"/>
-      <c r="I413" s="44"/>
-      <c r="J413" s="44"/>
-      <c r="K413" s="44"/>
-    </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A414" s="43"/>
-      <c r="B414" s="44"/>
-      <c r="C414" s="43"/>
-      <c r="D414" s="44"/>
-      <c r="E414" s="43"/>
-      <c r="F414" s="44"/>
-      <c r="G414" s="44"/>
-      <c r="H414" s="44"/>
-      <c r="I414" s="44"/>
-      <c r="J414" s="44"/>
-      <c r="K414" s="44"/>
+      <c r="A412" s="4"/>
+      <c r="B412" s="5"/>
+      <c r="C412" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D412" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="E412" s="4"/>
+      <c r="F412" s="5"/>
+      <c r="G412" s="5"/>
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A415" s="43"/>
       <c r="B415" s="44"/>
       <c r="C415" s="43"/>
-      <c r="D415" s="44"/>
+      <c r="D415" s="45"/>
       <c r="E415" s="43"/>
       <c r="F415" s="44"/>
       <c r="G415" s="44"/>
@@ -7794,7 +7743,7 @@
       <c r="A416" s="43"/>
       <c r="B416" s="44"/>
       <c r="C416" s="43"/>
-      <c r="D416" s="44"/>
+      <c r="D416" s="45"/>
       <c r="E416" s="43"/>
       <c r="F416" s="44"/>
       <c r="G416" s="44"/>
@@ -7841,6 +7790,175 @@
       <c r="I419" s="44"/>
       <c r="J419" s="44"/>
       <c r="K419" s="44"/>
+    </row>
+    <row r="420" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A420" s="43"/>
+      <c r="B420" s="44"/>
+      <c r="C420" s="43"/>
+      <c r="D420" s="44"/>
+      <c r="E420" s="43"/>
+      <c r="F420" s="44"/>
+      <c r="G420" s="44"/>
+      <c r="H420" s="44"/>
+      <c r="I420" s="44"/>
+      <c r="J420" s="44"/>
+      <c r="K420" s="44"/>
+    </row>
+    <row r="421" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A421" s="43"/>
+      <c r="B421" s="44"/>
+      <c r="C421" s="43"/>
+      <c r="D421" s="44"/>
+      <c r="E421" s="43"/>
+      <c r="F421" s="44"/>
+      <c r="G421" s="44"/>
+      <c r="H421" s="44"/>
+      <c r="I421" s="44"/>
+      <c r="J421" s="44"/>
+      <c r="K421" s="44"/>
+    </row>
+    <row r="422" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A422" s="43"/>
+      <c r="B422" s="44"/>
+      <c r="C422" s="43"/>
+      <c r="D422" s="44"/>
+      <c r="E422" s="43"/>
+      <c r="F422" s="44"/>
+      <c r="G422" s="44"/>
+      <c r="H422" s="44"/>
+      <c r="I422" s="44"/>
+      <c r="J422" s="44"/>
+      <c r="K422" s="44"/>
+    </row>
+    <row r="423" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A423" s="43"/>
+      <c r="B423" s="44"/>
+      <c r="C423" s="43"/>
+      <c r="D423" s="44"/>
+      <c r="E423" s="43"/>
+      <c r="F423" s="44"/>
+      <c r="G423" s="44"/>
+      <c r="H423" s="44"/>
+      <c r="I423" s="44"/>
+      <c r="J423" s="44"/>
+      <c r="K423" s="44"/>
+    </row>
+    <row r="424" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A424" s="43"/>
+      <c r="B424" s="44"/>
+      <c r="C424" s="43"/>
+      <c r="D424" s="44"/>
+      <c r="E424" s="43"/>
+      <c r="F424" s="44"/>
+      <c r="G424" s="44"/>
+      <c r="H424" s="44"/>
+      <c r="I424" s="44"/>
+      <c r="J424" s="44"/>
+      <c r="K424" s="44"/>
+    </row>
+    <row r="425" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A425" s="43"/>
+      <c r="B425" s="44"/>
+      <c r="C425" s="43"/>
+      <c r="D425" s="44"/>
+      <c r="E425" s="43"/>
+      <c r="F425" s="44"/>
+      <c r="G425" s="44"/>
+      <c r="H425" s="44"/>
+      <c r="I425" s="44"/>
+      <c r="J425" s="44"/>
+      <c r="K425" s="44"/>
+    </row>
+    <row r="426" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A426" s="43"/>
+      <c r="B426" s="44"/>
+      <c r="C426" s="43"/>
+      <c r="D426" s="44"/>
+      <c r="E426" s="43"/>
+      <c r="F426" s="44"/>
+      <c r="G426" s="44"/>
+      <c r="H426" s="44"/>
+      <c r="I426" s="44"/>
+      <c r="J426" s="44"/>
+      <c r="K426" s="44"/>
+    </row>
+    <row r="427" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A427" s="43"/>
+      <c r="B427" s="44"/>
+      <c r="C427" s="43"/>
+      <c r="D427" s="44"/>
+      <c r="E427" s="43"/>
+      <c r="F427" s="44"/>
+      <c r="G427" s="44"/>
+      <c r="H427" s="44"/>
+      <c r="I427" s="44"/>
+      <c r="J427" s="44"/>
+      <c r="K427" s="44"/>
+    </row>
+    <row r="428" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A428" s="43"/>
+      <c r="B428" s="44"/>
+      <c r="C428" s="43"/>
+      <c r="D428" s="44"/>
+      <c r="E428" s="43"/>
+      <c r="F428" s="44"/>
+      <c r="G428" s="44"/>
+      <c r="H428" s="44"/>
+      <c r="I428" s="44"/>
+      <c r="J428" s="44"/>
+      <c r="K428" s="44"/>
+    </row>
+    <row r="429" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A429" s="43"/>
+      <c r="B429" s="44"/>
+      <c r="C429" s="43"/>
+      <c r="D429" s="44"/>
+      <c r="E429" s="43"/>
+      <c r="F429" s="44"/>
+      <c r="G429" s="44"/>
+      <c r="H429" s="44"/>
+      <c r="I429" s="44"/>
+      <c r="J429" s="44"/>
+      <c r="K429" s="44"/>
+    </row>
+    <row r="430" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A430" s="43"/>
+      <c r="B430" s="44"/>
+      <c r="C430" s="43"/>
+      <c r="D430" s="44"/>
+      <c r="E430" s="43"/>
+      <c r="F430" s="44"/>
+      <c r="G430" s="44"/>
+      <c r="H430" s="44"/>
+      <c r="I430" s="44"/>
+      <c r="J430" s="44"/>
+      <c r="K430" s="44"/>
+    </row>
+    <row r="431" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A431" s="43"/>
+      <c r="B431" s="44"/>
+      <c r="C431" s="43"/>
+      <c r="D431" s="44"/>
+      <c r="E431" s="43"/>
+      <c r="F431" s="44"/>
+      <c r="G431" s="44"/>
+      <c r="H431" s="44"/>
+      <c r="I431" s="44"/>
+      <c r="J431" s="44"/>
+      <c r="K431" s="44"/>
+    </row>
+    <row r="432" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A432" s="43"/>
+      <c r="B432" s="44"/>
+      <c r="C432" s="43"/>
+      <c r="D432" s="44"/>
+      <c r="E432" s="43"/>
+      <c r="F432" s="44"/>
+      <c r="G432" s="44"/>
+      <c r="H432" s="44"/>
+      <c r="I432" s="44"/>
+      <c r="J432" s="44"/>
+      <c r="K432" s="44"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Images for Markdown files database .xlsx
+++ b/Images for Markdown files database .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trevor\Compac Industries\Compac - General\IT\ChatBot\Markdown-Manuals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1058868D-79DF-42E3-961D-C53D82C68E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA8729C-79CA-4954-82CA-5CE8F68172D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-1320" windowWidth="38640" windowHeight="21120" xr2:uid="{7323B22B-375C-41F7-91CD-F86C900FC6DE}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="726">
   <si>
     <t xml:space="preserve">PCBs </t>
   </si>
@@ -2192,6 +2192,36 @@
   </si>
   <si>
     <t>6.1.5_GPIO_VeederRoot_EMR4_Pulser.png</t>
+  </si>
+  <si>
+    <t>AdBlue</t>
+  </si>
+  <si>
+    <t>19.1.1</t>
+  </si>
+  <si>
+    <t>19.1.1_AdBlue_hyd_module.png</t>
+  </si>
+  <si>
+    <t>19.2.1</t>
+  </si>
+  <si>
+    <t>19.3.1</t>
+  </si>
+  <si>
+    <t>19.4.1</t>
+  </si>
+  <si>
+    <t>19.4.1_AdBlue_ZVA_adblue_nozzle.png</t>
+  </si>
+  <si>
+    <t>19.3.1_AdBlue_solenoid_png</t>
+  </si>
+  <si>
+    <t>19.3.2_Adblue_piston_png</t>
+  </si>
+  <si>
+    <t>19.3.2</t>
   </si>
 </sst>
 </file>
@@ -2355,7 +2385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2464,6 +2494,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7727,10 +7758,18 @@
       <c r="G412" s="5"/>
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A415" s="43"/>
-      <c r="B415" s="44"/>
-      <c r="C415" s="43"/>
-      <c r="D415" s="45"/>
+      <c r="A415" s="43">
+        <v>19</v>
+      </c>
+      <c r="B415" s="50" t="s">
+        <v>716</v>
+      </c>
+      <c r="C415" s="43" t="s">
+        <v>717</v>
+      </c>
+      <c r="D415" s="45" t="s">
+        <v>718</v>
+      </c>
       <c r="E415" s="43"/>
       <c r="F415" s="44"/>
       <c r="G415" s="44"/>
@@ -7768,7 +7807,9 @@
     <row r="418" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A418" s="43"/>
       <c r="B418" s="44"/>
-      <c r="C418" s="43"/>
+      <c r="C418" s="43" t="s">
+        <v>719</v>
+      </c>
       <c r="D418" s="44"/>
       <c r="E418" s="43"/>
       <c r="F418" s="44"/>
@@ -7820,8 +7861,12 @@
     <row r="422" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A422" s="43"/>
       <c r="B422" s="44"/>
-      <c r="C422" s="43"/>
-      <c r="D422" s="44"/>
+      <c r="C422" s="43" t="s">
+        <v>720</v>
+      </c>
+      <c r="D422" s="44" t="s">
+        <v>723</v>
+      </c>
       <c r="E422" s="43"/>
       <c r="F422" s="44"/>
       <c r="G422" s="44"/>
@@ -7833,8 +7878,12 @@
     <row r="423" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A423" s="43"/>
       <c r="B423" s="44"/>
-      <c r="C423" s="43"/>
-      <c r="D423" s="44"/>
+      <c r="C423" s="43" t="s">
+        <v>725</v>
+      </c>
+      <c r="D423" s="44" t="s">
+        <v>724</v>
+      </c>
       <c r="E423" s="43"/>
       <c r="F423" s="44"/>
       <c r="G423" s="44"/>
@@ -7872,8 +7921,12 @@
     <row r="426" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A426" s="43"/>
       <c r="B426" s="44"/>
-      <c r="C426" s="43"/>
-      <c r="D426" s="44"/>
+      <c r="C426" s="43" t="s">
+        <v>721</v>
+      </c>
+      <c r="D426" s="44" t="s">
+        <v>722</v>
+      </c>
       <c r="E426" s="43"/>
       <c r="F426" s="44"/>
       <c r="G426" s="44"/>

--- a/Images for Markdown files database .xlsx
+++ b/Images for Markdown files database .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trevor\Compac Industries\Compac - General\IT\ChatBot\Markdown-Manuals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6811E89-9525-4665-86CB-7AB2B7BC85B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7C4140-385F-4A19-99B1-086C1C443892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-1320" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{7323B22B-375C-41F7-91CD-F86C900FC6DE}"/>
+    <workbookView xWindow="-38520" yWindow="-1320" windowWidth="38640" windowHeight="21120" xr2:uid="{7323B22B-375C-41F7-91CD-F86C900FC6DE}"/>
   </bookViews>
   <sheets>
     <sheet name="images" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="880">
   <si>
     <t xml:space="preserve">PCBs </t>
   </si>
@@ -2625,6 +2625,66 @@
   </si>
   <si>
     <t>MAD0245A-01-A</t>
+  </si>
+  <si>
+    <t>1.6.2</t>
+  </si>
+  <si>
+    <t>1.6.3</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
+    <t>1.6.5</t>
+  </si>
+  <si>
+    <t>1.6.6</t>
+  </si>
+  <si>
+    <t>1.6.7</t>
+  </si>
+  <si>
+    <t>1.6.8</t>
+  </si>
+  <si>
+    <t>1.6.9</t>
+  </si>
+  <si>
+    <t>1.6.10</t>
+  </si>
+  <si>
+    <t>1.6.7_Terminals_</t>
+  </si>
+  <si>
+    <t>1.6.8_Terminals_</t>
+  </si>
+  <si>
+    <t>1.6.9_Terminals_</t>
+  </si>
+  <si>
+    <t>1.6.10_Terminals_</t>
+  </si>
+  <si>
+    <t>1.6.1_Terminals_MR400S,L400S.png</t>
+  </si>
+  <si>
+    <t>ET285</t>
+  </si>
+  <si>
+    <t>1.6.2_Terminals_MMR400S_2x_C5K_MR400S.png</t>
+  </si>
+  <si>
+    <t>1.6.3_Terminals_MMR400-80S.png</t>
+  </si>
+  <si>
+    <t>1.6.4_Terminals_MMR400_160S.png</t>
+  </si>
+  <si>
+    <t>1.6.5_Terminals_MMR400S _ with_Estop.png</t>
+  </si>
+  <si>
+    <t>1.6.6_Terminals_MMR400_160S _ Avi_2x_C5K.png</t>
   </si>
 </sst>
 </file>
@@ -3234,7 +3294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B533B56-556A-40A2-8D3F-E8E5A852019A}">
-  <dimension ref="A1:K449"/>
+  <dimension ref="A1:K460"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="1" customWidth="1"/>
@@ -3500,32 +3560,42 @@
       <c r="C20" s="4" t="s">
         <v>841</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="4"/>
+      <c r="D20" s="16" t="s">
+        <v>873</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>874</v>
+      </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="4"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="4"/>
+      <c r="C21" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>875</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>874</v>
+      </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="4"/>
-      <c r="B22" s="5" t="s">
-        <v>847</v>
-      </c>
+      <c r="B22" s="5"/>
       <c r="C22" s="4" t="s">
-        <v>842</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>851</v>
-      </c>
-      <c r="E22" s="4"/>
+        <v>861</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>876</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>874</v>
+      </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
     </row>
@@ -3533,12 +3603,14 @@
       <c r="A23" s="4"/>
       <c r="B23" s="5"/>
       <c r="C23" s="4" t="s">
-        <v>848</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>852</v>
-      </c>
-      <c r="E23" s="4"/>
+        <v>862</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>877</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>874</v>
+      </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
     </row>
@@ -3546,12 +3618,12 @@
       <c r="A24" s="4"/>
       <c r="B24" s="5"/>
       <c r="C24" s="4" t="s">
-        <v>849</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>853</v>
-      </c>
-      <c r="E24" s="4"/>
+        <v>863</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>878</v>
+      </c>
+      <c r="E24" s="22"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
     </row>
@@ -3559,10 +3631,10 @@
       <c r="A25" s="4"/>
       <c r="B25" s="5"/>
       <c r="C25" s="4" t="s">
-        <v>850</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>854</v>
+        <v>864</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>879</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="5"/>
@@ -3571,8 +3643,12 @@
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="4"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>869</v>
+      </c>
       <c r="E26" s="4"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -3580,8 +3656,12 @@
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="4"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>870</v>
+      </c>
       <c r="E27" s="4"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -3589,8 +3669,12 @@
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="4"/>
       <c r="B28" s="5"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>871</v>
+      </c>
       <c r="E28" s="4"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -3599,9 +3683,11 @@
       <c r="A29" s="4"/>
       <c r="B29" s="5"/>
       <c r="C29" s="4" t="s">
-        <v>843</v>
-      </c>
-      <c r="D29" s="5"/>
+        <v>868</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>872</v>
+      </c>
       <c r="E29" s="4"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -3635,25 +3721,27 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="4"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="5"/>
+      <c r="B33" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>851</v>
+      </c>
       <c r="E33" s="4"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="4">
-        <v>2</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>0</v>
-      </c>
+      <c r="A34" s="4"/>
+      <c r="B34" s="5"/>
       <c r="C34" s="4" t="s">
-        <v>141</v>
+        <v>848</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>147</v>
+        <v>852</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="5"/>
@@ -3663,10 +3751,10 @@
       <c r="A35" s="4"/>
       <c r="B35" s="5"/>
       <c r="C35" s="4" t="s">
-        <v>142</v>
+        <v>849</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>179</v>
+        <v>853</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="5"/>
@@ -3676,10 +3764,10 @@
       <c r="A36" s="4"/>
       <c r="B36" s="5"/>
       <c r="C36" s="4" t="s">
-        <v>143</v>
+        <v>850</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>146</v>
+        <v>854</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="5"/>
@@ -3688,12 +3776,8 @@
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>161</v>
-      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="5"/>
       <c r="E37" s="4"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -3701,12 +3785,8 @@
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
       <c r="B38" s="5"/>
-      <c r="C38" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>171</v>
-      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="5"/>
       <c r="E38" s="4"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -3714,9 +3794,7 @@
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="4" t="s">
-        <v>172</v>
-      </c>
+      <c r="C39" s="4"/>
       <c r="D39" s="5"/>
       <c r="E39" s="4"/>
       <c r="F39" s="5"/>
@@ -3725,25 +3803,19 @@
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4"/>
       <c r="B40" s="5"/>
-      <c r="C40" s="4"/>
+      <c r="C40" s="4" t="s">
+        <v>843</v>
+      </c>
       <c r="D40" s="5"/>
       <c r="E40" s="4"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="4">
-        <v>3</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>127</v>
-      </c>
+      <c r="A41" s="4"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="5"/>
       <c r="E41" s="4"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -3751,12 +3823,8 @@
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4"/>
       <c r="B42" s="5"/>
-      <c r="C42" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>128</v>
-      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="5"/>
       <c r="E42" s="4"/>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -3764,12 +3832,8 @@
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>129</v>
-      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="5"/>
       <c r="E43" s="4"/>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -3777,24 +3841,24 @@
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4"/>
       <c r="B44" s="5"/>
-      <c r="C44" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>130</v>
-      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="5"/>
       <c r="E44" s="4"/>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="4"/>
-      <c r="B45" s="5"/>
+      <c r="A45" s="4">
+        <v>2</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="C45" s="4" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="E45" s="4"/>
       <c r="F45" s="5"/>
@@ -3804,10 +3868,10 @@
       <c r="A46" s="4"/>
       <c r="B46" s="5"/>
       <c r="C46" s="4" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="5"/>
@@ -3817,10 +3881,10 @@
       <c r="A47" s="4"/>
       <c r="B47" s="5"/>
       <c r="C47" s="4" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="5"/>
@@ -3830,10 +3894,10 @@
       <c r="A48" s="4"/>
       <c r="B48" s="5"/>
       <c r="C48" s="4" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="5"/>
@@ -3843,10 +3907,10 @@
       <c r="A49" s="4"/>
       <c r="B49" s="5"/>
       <c r="C49" s="4" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="5"/>
@@ -3856,11 +3920,9 @@
       <c r="A50" s="4"/>
       <c r="B50" s="5"/>
       <c r="C50" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>136</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="D50" s="5"/>
       <c r="E50" s="4"/>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -3868,24 +3930,24 @@
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>137</v>
-      </c>
+      <c r="C51" s="4"/>
+      <c r="D51" s="5"/>
       <c r="E51" s="4"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" s="4"/>
-      <c r="B52" s="5"/>
+      <c r="A52" s="4">
+        <v>3</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="C52" s="4" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="5"/>
@@ -3895,10 +3957,10 @@
       <c r="A53" s="4"/>
       <c r="B53" s="5"/>
       <c r="C53" s="4" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="5"/>
@@ -3908,10 +3970,10 @@
       <c r="A54" s="4"/>
       <c r="B54" s="5"/>
       <c r="C54" s="4" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="E54" s="4"/>
       <c r="F54" s="5"/>
@@ -3920,33 +3982,37 @@
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4"/>
       <c r="B55" s="5"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="5"/>
+      <c r="C55" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>130</v>
+      </c>
       <c r="E55" s="4"/>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" s="6"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="6"/>
+      <c r="A56" s="4"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E56" s="4"/>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57" s="4">
-        <v>4</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>1</v>
-      </c>
+      <c r="A57" s="4"/>
+      <c r="B57" s="5"/>
       <c r="C57" s="4" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="5"/>
@@ -3956,10 +4022,10 @@
       <c r="A58" s="4"/>
       <c r="B58" s="5"/>
       <c r="C58" s="4" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E58" s="4"/>
       <c r="F58" s="5"/>
@@ -3969,10 +4035,10 @@
       <c r="A59" s="4"/>
       <c r="B59" s="5"/>
       <c r="C59" s="4" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="5"/>
@@ -3982,10 +4048,10 @@
       <c r="A60" s="4"/>
       <c r="B60" s="5"/>
       <c r="C60" s="4" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>93</v>
+        <v>135</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="5"/>
@@ -3995,10 +4061,10 @@
       <c r="A61" s="4"/>
       <c r="B61" s="5"/>
       <c r="C61" s="4" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="5"/>
@@ -4008,10 +4074,10 @@
       <c r="A62" s="4"/>
       <c r="B62" s="5"/>
       <c r="C62" s="4" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="5"/>
@@ -4021,10 +4087,10 @@
       <c r="A63" s="4"/>
       <c r="B63" s="5"/>
       <c r="C63" s="4" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="E63" s="4"/>
       <c r="F63" s="5"/>
@@ -4034,301 +4100,253 @@
       <c r="A64" s="4"/>
       <c r="B64" s="5"/>
       <c r="C64" s="4" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4"/>
       <c r="B65" s="5"/>
       <c r="C65" s="4" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4"/>
       <c r="B66" s="5"/>
-      <c r="C66" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>106</v>
-      </c>
+      <c r="C66" s="4"/>
+      <c r="D66" s="5"/>
       <c r="E66" s="4"/>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A67" s="4"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E67" s="4"/>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" s="6"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="6"/>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A68" s="4"/>
-      <c r="B68" s="5"/>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" s="4">
+        <v>4</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>1</v>
+      </c>
       <c r="C68" s="4" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4"/>
       <c r="B69" s="5"/>
       <c r="C69" s="4" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4"/>
       <c r="B70" s="5"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="5"/>
+      <c r="C70" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="E70" s="4"/>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A71" s="26"/>
-      <c r="B71" s="25"/>
-      <c r="C71" s="26"/>
-      <c r="D71" s="25"/>
-      <c r="E71" s="26"/>
-      <c r="F71" s="25"/>
-      <c r="G71" s="25"/>
-      <c r="H71" s="25"/>
-      <c r="I71" s="25"/>
-      <c r="J71" s="25"/>
-      <c r="K71" s="25"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A72" s="28">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" s="4"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" s="4"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" s="4"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" s="4"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" s="4"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76" s="4"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77" s="4"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78" s="4"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79" s="4"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80" s="4"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A81" s="4"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="5"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A82" s="26"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="25"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="25"/>
+      <c r="G82" s="25"/>
+      <c r="H82" s="25"/>
+      <c r="I82" s="25"/>
+      <c r="J82" s="25"/>
+      <c r="K82" s="25"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A83" s="28">
         <v>5</v>
       </c>
-      <c r="B72" s="29" t="s">
+      <c r="B83" s="29" t="s">
         <v>568</v>
       </c>
-      <c r="C72" s="28" t="s">
+      <c r="C83" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D72" s="29" t="s">
+      <c r="D83" s="29" t="s">
         <v>30</v>
-      </c>
-      <c r="E72" s="28"/>
-      <c r="F72" s="29"/>
-      <c r="G72" s="29"/>
-      <c r="H72" s="29"/>
-      <c r="I72" s="29"/>
-      <c r="J72" s="29"/>
-      <c r="K72" s="29"/>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A73" s="28"/>
-      <c r="B73" s="29"/>
-      <c r="C73" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="E73" s="28"/>
-      <c r="F73" s="29"/>
-      <c r="G73" s="29"/>
-      <c r="H73" s="29"/>
-      <c r="I73" s="29"/>
-      <c r="J73" s="29"/>
-      <c r="K73" s="29"/>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A74" s="28"/>
-      <c r="B74" s="29"/>
-      <c r="C74" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D74" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="E74" s="28"/>
-      <c r="F74" s="29"/>
-      <c r="G74" s="29"/>
-      <c r="H74" s="29"/>
-      <c r="I74" s="29"/>
-      <c r="J74" s="29"/>
-      <c r="K74" s="29"/>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A75" s="28"/>
-      <c r="B75" s="29"/>
-      <c r="C75" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="D75" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="E75" s="28"/>
-      <c r="F75" s="29"/>
-      <c r="G75" s="29"/>
-      <c r="H75" s="29"/>
-      <c r="I75" s="29"/>
-      <c r="J75" s="29"/>
-      <c r="K75" s="29"/>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A76" s="28"/>
-      <c r="B76" s="29"/>
-      <c r="C76" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="D76" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="E76" s="28"/>
-      <c r="F76" s="29"/>
-      <c r="G76" s="29"/>
-      <c r="H76" s="29"/>
-      <c r="I76" s="29"/>
-      <c r="J76" s="29"/>
-      <c r="K76" s="29"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A77" s="28"/>
-      <c r="B77" s="29"/>
-      <c r="C77" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D77" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="E77" s="28"/>
-      <c r="F77" s="29"/>
-      <c r="G77" s="29"/>
-      <c r="H77" s="29"/>
-      <c r="I77" s="29"/>
-      <c r="J77" s="29"/>
-      <c r="K77" s="29"/>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A78" s="28"/>
-      <c r="B78" s="29"/>
-      <c r="C78" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="E78" s="28"/>
-      <c r="F78" s="29"/>
-      <c r="G78" s="29"/>
-      <c r="H78" s="29"/>
-      <c r="I78" s="29"/>
-      <c r="J78" s="29"/>
-      <c r="K78" s="29"/>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A79" s="28"/>
-      <c r="B79" s="29"/>
-      <c r="C79" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D79" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="E79" s="28"/>
-      <c r="F79" s="29"/>
-      <c r="G79" s="29"/>
-      <c r="H79" s="29"/>
-      <c r="I79" s="29"/>
-      <c r="J79" s="29"/>
-      <c r="K79" s="29"/>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A80" s="28"/>
-      <c r="B80" s="29"/>
-      <c r="C80" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D80" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="E80" s="28"/>
-      <c r="F80" s="29"/>
-      <c r="G80" s="29"/>
-      <c r="H80" s="29"/>
-      <c r="I80" s="29"/>
-      <c r="J80" s="29"/>
-      <c r="K80" s="29"/>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A81" s="28"/>
-      <c r="B81" s="29"/>
-      <c r="C81" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="D81" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="E81" s="28"/>
-      <c r="F81" s="29"/>
-      <c r="G81" s="29"/>
-      <c r="H81" s="29"/>
-      <c r="I81" s="29"/>
-      <c r="J81" s="29"/>
-      <c r="K81" s="29"/>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A82" s="28"/>
-      <c r="B82" s="29"/>
-      <c r="C82" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D82" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="E82" s="28"/>
-      <c r="F82" s="29"/>
-      <c r="G82" s="29"/>
-      <c r="H82" s="29"/>
-      <c r="I82" s="29"/>
-      <c r="J82" s="29"/>
-      <c r="K82" s="29"/>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A83" s="28"/>
-      <c r="B83" s="29"/>
-      <c r="C83" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="D83" s="29" t="s">
-        <v>39</v>
       </c>
       <c r="E83" s="28"/>
       <c r="F83" s="29"/>
@@ -4342,10 +4360,10 @@
       <c r="A84" s="28"/>
       <c r="B84" s="29"/>
       <c r="C84" s="28" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D84" s="29" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E84" s="28"/>
       <c r="F84" s="29"/>
@@ -4359,10 +4377,10 @@
       <c r="A85" s="28"/>
       <c r="B85" s="29"/>
       <c r="C85" s="28" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D85" s="29" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E85" s="28"/>
       <c r="F85" s="29"/>
@@ -4376,10 +4394,10 @@
       <c r="A86" s="28"/>
       <c r="B86" s="29"/>
       <c r="C86" s="28" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E86" s="28"/>
       <c r="F86" s="29"/>
@@ -4393,10 +4411,10 @@
       <c r="A87" s="28"/>
       <c r="B87" s="29"/>
       <c r="C87" s="28" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D87" s="29" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E87" s="28"/>
       <c r="F87" s="29"/>
@@ -4410,10 +4428,10 @@
       <c r="A88" s="28"/>
       <c r="B88" s="29"/>
       <c r="C88" s="28" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E88" s="28"/>
       <c r="F88" s="29"/>
@@ -4427,10 +4445,10 @@
       <c r="A89" s="28"/>
       <c r="B89" s="29"/>
       <c r="C89" s="28" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="E89" s="28"/>
       <c r="F89" s="29"/>
@@ -4444,10 +4462,10 @@
       <c r="A90" s="28"/>
       <c r="B90" s="29"/>
       <c r="C90" s="28" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D90" s="29" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E90" s="28"/>
       <c r="F90" s="29"/>
@@ -4461,10 +4479,10 @@
       <c r="A91" s="28"/>
       <c r="B91" s="29"/>
       <c r="C91" s="28" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D91" s="29" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E91" s="28"/>
       <c r="F91" s="29"/>
@@ -4478,10 +4496,10 @@
       <c r="A92" s="28"/>
       <c r="B92" s="29"/>
       <c r="C92" s="28" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D92" s="29" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E92" s="28"/>
       <c r="F92" s="29"/>
@@ -4495,10 +4513,10 @@
       <c r="A93" s="28"/>
       <c r="B93" s="29"/>
       <c r="C93" s="28" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D93" s="29" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E93" s="28"/>
       <c r="F93" s="29"/>
@@ -4512,10 +4530,10 @@
       <c r="A94" s="28"/>
       <c r="B94" s="29"/>
       <c r="C94" s="28" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D94" s="29" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E94" s="28"/>
       <c r="F94" s="29"/>
@@ -4526,217 +4544,217 @@
       <c r="K94" s="29"/>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A95" s="26"/>
-      <c r="B95" s="25"/>
-      <c r="C95" s="26"/>
-      <c r="D95" s="25"/>
-      <c r="E95" s="26"/>
-      <c r="F95" s="25"/>
-      <c r="G95" s="25"/>
-      <c r="H95" s="25"/>
-      <c r="I95" s="25"/>
-      <c r="J95" s="25"/>
-      <c r="K95" s="25"/>
+      <c r="A95" s="28"/>
+      <c r="B95" s="29"/>
+      <c r="C95" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="E95" s="28"/>
+      <c r="F95" s="29"/>
+      <c r="G95" s="29"/>
+      <c r="H95" s="29"/>
+      <c r="I95" s="29"/>
+      <c r="J95" s="29"/>
+      <c r="K95" s="29"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A96" s="13">
+      <c r="A96" s="28"/>
+      <c r="B96" s="29"/>
+      <c r="C96" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D96" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="E96" s="28"/>
+      <c r="F96" s="29"/>
+      <c r="G96" s="29"/>
+      <c r="H96" s="29"/>
+      <c r="I96" s="29"/>
+      <c r="J96" s="29"/>
+      <c r="K96" s="29"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A97" s="28"/>
+      <c r="B97" s="29"/>
+      <c r="C97" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E97" s="28"/>
+      <c r="F97" s="29"/>
+      <c r="G97" s="29"/>
+      <c r="H97" s="29"/>
+      <c r="I97" s="29"/>
+      <c r="J97" s="29"/>
+      <c r="K97" s="29"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A98" s="28"/>
+      <c r="B98" s="29"/>
+      <c r="C98" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D98" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="E98" s="28"/>
+      <c r="F98" s="29"/>
+      <c r="G98" s="29"/>
+      <c r="H98" s="29"/>
+      <c r="I98" s="29"/>
+      <c r="J98" s="29"/>
+      <c r="K98" s="29"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A99" s="28"/>
+      <c r="B99" s="29"/>
+      <c r="C99" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D99" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="E99" s="28"/>
+      <c r="F99" s="29"/>
+      <c r="G99" s="29"/>
+      <c r="H99" s="29"/>
+      <c r="I99" s="29"/>
+      <c r="J99" s="29"/>
+      <c r="K99" s="29"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A100" s="28"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D100" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="E100" s="28"/>
+      <c r="F100" s="29"/>
+      <c r="G100" s="29"/>
+      <c r="H100" s="29"/>
+      <c r="I100" s="29"/>
+      <c r="J100" s="29"/>
+      <c r="K100" s="29"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A101" s="28"/>
+      <c r="B101" s="29"/>
+      <c r="C101" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D101" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E101" s="28"/>
+      <c r="F101" s="29"/>
+      <c r="G101" s="29"/>
+      <c r="H101" s="29"/>
+      <c r="I101" s="29"/>
+      <c r="J101" s="29"/>
+      <c r="K101" s="29"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A102" s="28"/>
+      <c r="B102" s="29"/>
+      <c r="C102" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D102" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E102" s="28"/>
+      <c r="F102" s="29"/>
+      <c r="G102" s="29"/>
+      <c r="H102" s="29"/>
+      <c r="I102" s="29"/>
+      <c r="J102" s="29"/>
+      <c r="K102" s="29"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A103" s="28"/>
+      <c r="B103" s="29"/>
+      <c r="C103" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D103" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="E103" s="28"/>
+      <c r="F103" s="29"/>
+      <c r="G103" s="29"/>
+      <c r="H103" s="29"/>
+      <c r="I103" s="29"/>
+      <c r="J103" s="29"/>
+      <c r="K103" s="29"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A104" s="28"/>
+      <c r="B104" s="29"/>
+      <c r="C104" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D104" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="E104" s="28"/>
+      <c r="F104" s="29"/>
+      <c r="G104" s="29"/>
+      <c r="H104" s="29"/>
+      <c r="I104" s="29"/>
+      <c r="J104" s="29"/>
+      <c r="K104" s="29"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A105" s="28"/>
+      <c r="B105" s="29"/>
+      <c r="C105" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D105" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E105" s="28"/>
+      <c r="F105" s="29"/>
+      <c r="G105" s="29"/>
+      <c r="H105" s="29"/>
+      <c r="I105" s="29"/>
+      <c r="J105" s="29"/>
+      <c r="K105" s="29"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A106" s="26"/>
+      <c r="B106" s="25"/>
+      <c r="C106" s="26"/>
+      <c r="D106" s="25"/>
+      <c r="E106" s="26"/>
+      <c r="F106" s="25"/>
+      <c r="G106" s="25"/>
+      <c r="H106" s="25"/>
+      <c r="I106" s="25"/>
+      <c r="J106" s="25"/>
+      <c r="K106" s="25"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A107" s="13">
         <v>6</v>
       </c>
-      <c r="B96" s="27" t="s">
+      <c r="B107" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C107" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="D96" s="12" t="s">
+      <c r="D107" s="12" t="s">
         <v>178</v>
-      </c>
-      <c r="E96" s="13"/>
-      <c r="F96" s="12"/>
-      <c r="G96" s="12"/>
-      <c r="H96" s="12"/>
-      <c r="I96" s="12"/>
-      <c r="J96" s="12"/>
-      <c r="K96" s="12"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A97" s="13"/>
-      <c r="B97" s="12"/>
-      <c r="C97" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E97" s="13"/>
-      <c r="F97" s="12"/>
-      <c r="G97" s="12"/>
-      <c r="H97" s="12"/>
-      <c r="I97" s="12"/>
-      <c r="J97" s="12"/>
-      <c r="K97" s="12"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A98" s="13"/>
-      <c r="B98" s="12"/>
-      <c r="C98" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E98" s="13"/>
-      <c r="F98" s="12"/>
-      <c r="G98" s="12"/>
-      <c r="H98" s="12"/>
-      <c r="I98" s="12"/>
-      <c r="J98" s="12"/>
-      <c r="K98" s="12"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A99" s="13"/>
-      <c r="B99" s="12"/>
-      <c r="C99" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D99" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E99" s="13"/>
-      <c r="F99" s="12"/>
-      <c r="G99" s="12"/>
-      <c r="H99" s="12"/>
-      <c r="I99" s="12"/>
-      <c r="J99" s="12"/>
-      <c r="K99" s="12"/>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A100" s="13"/>
-      <c r="B100" s="12"/>
-      <c r="C100" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D100" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E100" s="13"/>
-      <c r="F100" s="12"/>
-      <c r="G100" s="12"/>
-      <c r="H100" s="12"/>
-      <c r="I100" s="12"/>
-      <c r="J100" s="12"/>
-      <c r="K100" s="12"/>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A101" s="13"/>
-      <c r="B101" s="12"/>
-      <c r="C101" s="13" t="s">
-        <v>714</v>
-      </c>
-      <c r="D101" s="12" t="s">
-        <v>715</v>
-      </c>
-      <c r="E101" s="13"/>
-      <c r="F101" s="12"/>
-      <c r="G101" s="12"/>
-      <c r="H101" s="12"/>
-      <c r="I101" s="12"/>
-      <c r="J101" s="12"/>
-      <c r="K101" s="12"/>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A102" s="13"/>
-      <c r="B102" s="12"/>
-      <c r="C102" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D102" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E102" s="13"/>
-      <c r="F102" s="12"/>
-      <c r="G102" s="12"/>
-      <c r="H102" s="12"/>
-      <c r="I102" s="12"/>
-      <c r="J102" s="12"/>
-      <c r="K102" s="12"/>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A103" s="13"/>
-      <c r="B103" s="12"/>
-      <c r="C103" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D103" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E103" s="13"/>
-      <c r="F103" s="12"/>
-      <c r="G103" s="12"/>
-      <c r="H103" s="12"/>
-      <c r="I103" s="12"/>
-      <c r="J103" s="12"/>
-      <c r="K103" s="12"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A104" s="13"/>
-      <c r="B104" s="12"/>
-      <c r="C104" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="D104" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E104" s="13"/>
-      <c r="F104" s="12"/>
-      <c r="G104" s="12"/>
-      <c r="H104" s="12"/>
-      <c r="I104" s="12"/>
-      <c r="J104" s="12"/>
-      <c r="K104" s="12"/>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A105" s="13"/>
-      <c r="B105" s="12"/>
-      <c r="C105" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D105" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E105" s="13"/>
-      <c r="F105" s="12"/>
-      <c r="G105" s="12"/>
-      <c r="H105" s="12"/>
-      <c r="I105" s="12"/>
-      <c r="J105" s="12"/>
-      <c r="K105" s="12"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A106" s="13"/>
-      <c r="B106" s="12"/>
-      <c r="C106" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="D106" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="E106" s="13"/>
-      <c r="F106" s="12"/>
-      <c r="G106" s="12"/>
-      <c r="H106" s="12"/>
-      <c r="I106" s="12"/>
-      <c r="J106" s="12"/>
-      <c r="K106" s="12"/>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A107" s="13"/>
-      <c r="B107" s="12"/>
-      <c r="C107" s="13" t="s">
-        <v>456</v>
-      </c>
-      <c r="D107" s="19" t="s">
-        <v>460</v>
       </c>
       <c r="E107" s="13"/>
       <c r="F107" s="12"/>
@@ -4750,10 +4768,10 @@
       <c r="A108" s="13"/>
       <c r="B108" s="12"/>
       <c r="C108" s="13" t="s">
-        <v>457</v>
-      </c>
-      <c r="D108" s="19" t="s">
-        <v>461</v>
+        <v>73</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="E108" s="13"/>
       <c r="F108" s="12"/>
@@ -4767,10 +4785,10 @@
       <c r="A109" s="13"/>
       <c r="B109" s="12"/>
       <c r="C109" s="13" t="s">
-        <v>458</v>
-      </c>
-      <c r="D109" s="19" t="s">
-        <v>462</v>
+        <v>75</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="E109" s="13"/>
       <c r="F109" s="12"/>
@@ -4783,8 +4801,12 @@
     <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" s="13"/>
       <c r="B110" s="12"/>
-      <c r="C110" s="13"/>
-      <c r="D110" s="19"/>
+      <c r="C110" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>79</v>
+      </c>
       <c r="E110" s="13"/>
       <c r="F110" s="12"/>
       <c r="G110" s="12"/>
@@ -4794,625 +4816,633 @@
       <c r="K110" s="12"/>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A111" s="26"/>
-      <c r="B111" s="25"/>
-      <c r="C111" s="26"/>
-      <c r="D111" s="25"/>
-      <c r="E111" s="26"/>
-      <c r="F111" s="25"/>
-      <c r="G111" s="25"/>
-      <c r="H111" s="25"/>
-      <c r="I111" s="25"/>
-      <c r="J111" s="25"/>
-      <c r="K111" s="25"/>
+      <c r="A111" s="13"/>
+      <c r="B111" s="12"/>
+      <c r="C111" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E111" s="13"/>
+      <c r="F111" s="12"/>
+      <c r="G111" s="12"/>
+      <c r="H111" s="12"/>
+      <c r="I111" s="12"/>
+      <c r="J111" s="12"/>
+      <c r="K111" s="12"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A112" s="4">
+      <c r="A112" s="13"/>
+      <c r="B112" s="12"/>
+      <c r="C112" s="13" t="s">
+        <v>714</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>715</v>
+      </c>
+      <c r="E112" s="13"/>
+      <c r="F112" s="12"/>
+      <c r="G112" s="12"/>
+      <c r="H112" s="12"/>
+      <c r="I112" s="12"/>
+      <c r="J112" s="12"/>
+      <c r="K112" s="12"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A113" s="13"/>
+      <c r="B113" s="12"/>
+      <c r="C113" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E113" s="13"/>
+      <c r="F113" s="12"/>
+      <c r="G113" s="12"/>
+      <c r="H113" s="12"/>
+      <c r="I113" s="12"/>
+      <c r="J113" s="12"/>
+      <c r="K113" s="12"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A114" s="13"/>
+      <c r="B114" s="12"/>
+      <c r="C114" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E114" s="13"/>
+      <c r="F114" s="12"/>
+      <c r="G114" s="12"/>
+      <c r="H114" s="12"/>
+      <c r="I114" s="12"/>
+      <c r="J114" s="12"/>
+      <c r="K114" s="12"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A115" s="13"/>
+      <c r="B115" s="12"/>
+      <c r="C115" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E115" s="13"/>
+      <c r="F115" s="12"/>
+      <c r="G115" s="12"/>
+      <c r="H115" s="12"/>
+      <c r="I115" s="12"/>
+      <c r="J115" s="12"/>
+      <c r="K115" s="12"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A116" s="13"/>
+      <c r="B116" s="12"/>
+      <c r="C116" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D116" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E116" s="13"/>
+      <c r="F116" s="12"/>
+      <c r="G116" s="12"/>
+      <c r="H116" s="12"/>
+      <c r="I116" s="12"/>
+      <c r="J116" s="12"/>
+      <c r="K116" s="12"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A117" s="13"/>
+      <c r="B117" s="12"/>
+      <c r="C117" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="D117" s="19" t="s">
+        <v>459</v>
+      </c>
+      <c r="E117" s="13"/>
+      <c r="F117" s="12"/>
+      <c r="G117" s="12"/>
+      <c r="H117" s="12"/>
+      <c r="I117" s="12"/>
+      <c r="J117" s="12"/>
+      <c r="K117" s="12"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A118" s="13"/>
+      <c r="B118" s="12"/>
+      <c r="C118" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="D118" s="19" t="s">
+        <v>460</v>
+      </c>
+      <c r="E118" s="13"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="12"/>
+      <c r="H118" s="12"/>
+      <c r="I118" s="12"/>
+      <c r="J118" s="12"/>
+      <c r="K118" s="12"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A119" s="13"/>
+      <c r="B119" s="12"/>
+      <c r="C119" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="D119" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="E119" s="13"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="12"/>
+      <c r="H119" s="12"/>
+      <c r="I119" s="12"/>
+      <c r="J119" s="12"/>
+      <c r="K119" s="12"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A120" s="13"/>
+      <c r="B120" s="12"/>
+      <c r="C120" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="D120" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="E120" s="13"/>
+      <c r="F120" s="12"/>
+      <c r="G120" s="12"/>
+      <c r="H120" s="12"/>
+      <c r="I120" s="12"/>
+      <c r="J120" s="12"/>
+      <c r="K120" s="12"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A121" s="13"/>
+      <c r="B121" s="12"/>
+      <c r="C121" s="13"/>
+      <c r="D121" s="19"/>
+      <c r="E121" s="13"/>
+      <c r="F121" s="12"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="12"/>
+      <c r="I121" s="12"/>
+      <c r="J121" s="12"/>
+      <c r="K121" s="12"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A122" s="26"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="26"/>
+      <c r="D122" s="25"/>
+      <c r="E122" s="26"/>
+      <c r="F122" s="25"/>
+      <c r="G122" s="25"/>
+      <c r="H122" s="25"/>
+      <c r="I122" s="25"/>
+      <c r="J122" s="25"/>
+      <c r="K122" s="25"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A123" s="4">
         <v>7</v>
       </c>
-      <c r="B112" s="5" t="s">
+      <c r="B123" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C123" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D112" s="5" t="s">
+      <c r="D123" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E112" s="4"/>
-      <c r="F112" s="5"/>
-      <c r="G112" s="5"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A113" s="4"/>
-      <c r="B113" s="5"/>
-      <c r="C113" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E113" s="4"/>
-      <c r="F113" s="5"/>
-      <c r="G113" s="5"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A114" s="4"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E114" s="4"/>
-      <c r="F114" s="5"/>
-      <c r="G114" s="5"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A115" s="6"/>
-      <c r="B115" s="7"/>
-      <c r="C115" s="6"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="6"/>
-      <c r="F115" s="5"/>
-      <c r="G115" s="5"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A116" s="4">
-        <v>8</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E116" s="4"/>
-      <c r="F116" s="5"/>
-      <c r="G116" s="5"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A117" s="4"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E117" s="4"/>
-      <c r="F117" s="5"/>
-      <c r="G117" s="5"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A118" s="4"/>
-      <c r="B118" s="5"/>
-      <c r="C118" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E118" s="4"/>
-      <c r="F118" s="5"/>
-      <c r="G118" s="5"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A119" s="4"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E119" s="4"/>
-      <c r="F119" s="5"/>
-      <c r="G119" s="5"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A120" s="4"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D120" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E120" s="4"/>
-      <c r="F120" s="5"/>
-      <c r="G120" s="5"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A121" s="6"/>
-      <c r="B121" s="7"/>
-      <c r="C121" s="6"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="6"/>
-      <c r="F121" s="5"/>
-      <c r="G121" s="5"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A122" s="4">
-        <v>9</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="D122" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="E122" s="4"/>
-      <c r="F122" s="5"/>
-      <c r="G122" s="5"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A123" s="4"/>
-      <c r="B123" s="5"/>
-      <c r="C123" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="D123" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E123" s="17">
-        <v>46098</v>
-      </c>
+      <c r="E123" s="4"/>
       <c r="F123" s="5"/>
       <c r="G123" s="5"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" s="4"/>
       <c r="B124" s="5"/>
       <c r="C124" s="4" t="s">
-        <v>157</v>
+        <v>69</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>162</v>
+        <v>71</v>
       </c>
       <c r="E124" s="4"/>
       <c r="F124" s="5"/>
       <c r="G124" s="5"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" s="4"/>
       <c r="B125" s="5"/>
       <c r="C125" s="4" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="E125" s="4"/>
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A126" s="4"/>
-      <c r="B126" s="5"/>
-      <c r="C126" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="E126" s="4"/>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A126" s="6"/>
+      <c r="B126" s="7"/>
+      <c r="C126" s="6"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="6"/>
       <c r="F126" s="5"/>
       <c r="G126" s="5"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A127" s="4"/>
-      <c r="B127" s="5"/>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A127" s="4">
+        <v>8</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="C127" s="4" t="s">
-        <v>160</v>
+        <v>54</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="E127" s="4"/>
       <c r="F127" s="5"/>
       <c r="G127" s="5"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" s="4"/>
       <c r="B128" s="5"/>
       <c r="C128" s="4" t="s">
-        <v>166</v>
+        <v>55</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>167</v>
+        <v>59</v>
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="5"/>
       <c r="G128" s="5"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4"/>
       <c r="B129" s="5"/>
       <c r="C129" s="4" t="s">
-        <v>175</v>
+        <v>56</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>176</v>
+        <v>60</v>
       </c>
       <c r="E129" s="4"/>
       <c r="F129" s="5"/>
       <c r="G129" s="5"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4"/>
       <c r="B130" s="5"/>
       <c r="C130" s="4" t="s">
-        <v>173</v>
+        <v>57</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>174</v>
+        <v>61</v>
       </c>
       <c r="E130" s="4"/>
       <c r="F130" s="5"/>
       <c r="G130" s="5"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4"/>
       <c r="B131" s="5"/>
-      <c r="C131" s="4"/>
-      <c r="D131" s="5"/>
+      <c r="C131" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="E131" s="4"/>
       <c r="F131" s="5"/>
       <c r="G131" s="5"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A132" s="4"/>
-      <c r="B132" s="5"/>
-      <c r="C132" s="4"/>
-      <c r="D132" s="5"/>
-      <c r="E132" s="4"/>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A132" s="6"/>
+      <c r="B132" s="7"/>
+      <c r="C132" s="6"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="6"/>
       <c r="F132" s="5"/>
       <c r="G132" s="5"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A133" s="30"/>
-      <c r="B133" s="31"/>
-      <c r="C133" s="30"/>
-      <c r="D133" s="31"/>
-      <c r="E133" s="30"/>
-      <c r="F133" s="31"/>
-      <c r="G133" s="31"/>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A134" s="26"/>
-      <c r="B134" s="25"/>
-      <c r="C134" s="26"/>
-      <c r="D134" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="E134" s="26"/>
-      <c r="F134" s="25"/>
-      <c r="G134" s="25"/>
-      <c r="H134" s="25"/>
-      <c r="I134" s="25"/>
-      <c r="J134" s="25"/>
-      <c r="K134" s="25"/>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A135" s="35"/>
-      <c r="B135" s="36" t="s">
-        <v>569</v>
-      </c>
-      <c r="C135" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="D135" s="36" t="s">
-        <v>266</v>
-      </c>
-      <c r="E135" s="37">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A133" s="4">
+        <v>9</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E133" s="4"/>
+      <c r="F133" s="5"/>
+      <c r="G133" s="5"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A134" s="4"/>
+      <c r="B134" s="5"/>
+      <c r="C134" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="E134" s="17">
         <v>46098</v>
       </c>
-      <c r="F135" s="36"/>
-      <c r="G135" s="36"/>
-      <c r="H135" s="36"/>
-      <c r="I135" s="36"/>
-      <c r="J135" s="36"/>
-      <c r="K135" s="36"/>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A136" s="35"/>
-      <c r="B136" s="36"/>
-      <c r="C136" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="D136" s="36" t="s">
-        <v>267</v>
-      </c>
-      <c r="E136" s="37">
-        <v>46098</v>
-      </c>
-      <c r="F136" s="36"/>
-      <c r="G136" s="36"/>
-      <c r="H136" s="36"/>
-      <c r="I136" s="36"/>
-      <c r="J136" s="36"/>
-      <c r="K136" s="36"/>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A137" s="35"/>
-      <c r="B137" s="36"/>
-      <c r="C137" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="D137" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="E137" s="37">
-        <v>46098</v>
-      </c>
-      <c r="F137" s="36"/>
-      <c r="G137" s="36"/>
-      <c r="H137" s="36"/>
-      <c r="I137" s="36"/>
-      <c r="J137" s="36"/>
-      <c r="K137" s="36"/>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A138" s="35"/>
-      <c r="B138" s="36"/>
-      <c r="C138" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="D138" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="E138" s="37">
-        <v>46098</v>
-      </c>
-      <c r="F138" s="36"/>
-      <c r="G138" s="36"/>
-      <c r="H138" s="36"/>
-      <c r="I138" s="36"/>
-      <c r="J138" s="36"/>
-      <c r="K138" s="36"/>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A139" s="35"/>
-      <c r="B139" s="36"/>
-      <c r="C139" s="35"/>
-      <c r="D139" s="36"/>
-      <c r="E139" s="35"/>
-      <c r="F139" s="36"/>
-      <c r="G139" s="36"/>
-      <c r="H139" s="36"/>
-      <c r="I139" s="36"/>
-      <c r="J139" s="36"/>
-      <c r="K139" s="36"/>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A140" s="26"/>
-      <c r="B140" s="25"/>
-      <c r="C140" s="26"/>
-      <c r="D140" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="E140" s="26"/>
-      <c r="F140" s="25"/>
-      <c r="G140" s="25"/>
-      <c r="H140" s="25"/>
-      <c r="I140" s="25"/>
-      <c r="J140" s="25"/>
-      <c r="K140" s="25"/>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A141" s="47" t="s">
-        <v>573</v>
-      </c>
-      <c r="B141" s="48" t="s">
-        <v>572</v>
-      </c>
-      <c r="C141" s="32" t="s">
-        <v>270</v>
-      </c>
-      <c r="D141" s="33" t="s">
-        <v>677</v>
-      </c>
-      <c r="E141" s="34">
-        <v>46099</v>
-      </c>
-      <c r="F141" s="33"/>
-      <c r="G141" s="33"/>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A142" s="13" t="s">
-        <v>574</v>
-      </c>
-      <c r="B142" s="19">
-        <v>11</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="D142" s="5" t="s">
-        <v>678</v>
-      </c>
-      <c r="E142" s="17">
-        <v>46099</v>
-      </c>
+      <c r="F134" s="5"/>
+      <c r="G134" s="5"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A135" s="4"/>
+      <c r="B135" s="5"/>
+      <c r="C135" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="E135" s="4"/>
+      <c r="F135" s="5"/>
+      <c r="G135" s="5"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A136" s="4"/>
+      <c r="B136" s="5"/>
+      <c r="C136" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E136" s="4"/>
+      <c r="F136" s="5"/>
+      <c r="G136" s="5"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A137" s="4"/>
+      <c r="B137" s="5"/>
+      <c r="C137" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E137" s="4"/>
+      <c r="F137" s="5"/>
+      <c r="G137" s="5"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A138" s="4"/>
+      <c r="B138" s="5"/>
+      <c r="C138" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E138" s="4"/>
+      <c r="F138" s="5"/>
+      <c r="G138" s="5"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A139" s="4"/>
+      <c r="B139" s="5"/>
+      <c r="C139" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E139" s="4"/>
+      <c r="F139" s="5"/>
+      <c r="G139" s="5"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A140" s="4"/>
+      <c r="B140" s="5"/>
+      <c r="C140" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E140" s="4"/>
+      <c r="F140" s="5"/>
+      <c r="G140" s="5"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A141" s="4"/>
+      <c r="B141" s="5"/>
+      <c r="C141" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E141" s="4"/>
+      <c r="F141" s="5"/>
+      <c r="G141" s="5"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A142" s="4"/>
+      <c r="B142" s="5"/>
+      <c r="C142" s="4"/>
+      <c r="D142" s="5"/>
+      <c r="E142" s="4"/>
       <c r="F142" s="5"/>
       <c r="G142" s="5"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4"/>
       <c r="B143" s="5"/>
-      <c r="C143" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D143" s="5" t="s">
-        <v>658</v>
-      </c>
-      <c r="E143" s="17">
+      <c r="C143" s="4"/>
+      <c r="D143" s="5"/>
+      <c r="E143" s="4"/>
+      <c r="F143" s="5"/>
+      <c r="G143" s="5"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A144" s="30"/>
+      <c r="B144" s="31"/>
+      <c r="C144" s="30"/>
+      <c r="D144" s="31"/>
+      <c r="E144" s="30"/>
+      <c r="F144" s="31"/>
+      <c r="G144" s="31"/>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A145" s="26"/>
+      <c r="B145" s="25"/>
+      <c r="C145" s="26"/>
+      <c r="D145" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="E145" s="26"/>
+      <c r="F145" s="25"/>
+      <c r="G145" s="25"/>
+      <c r="H145" s="25"/>
+      <c r="I145" s="25"/>
+      <c r="J145" s="25"/>
+      <c r="K145" s="25"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A146" s="35"/>
+      <c r="B146" s="36" t="s">
+        <v>569</v>
+      </c>
+      <c r="C146" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="D146" s="36" t="s">
+        <v>266</v>
+      </c>
+      <c r="E146" s="37">
+        <v>46098</v>
+      </c>
+      <c r="F146" s="36"/>
+      <c r="G146" s="36"/>
+      <c r="H146" s="36"/>
+      <c r="I146" s="36"/>
+      <c r="J146" s="36"/>
+      <c r="K146" s="36"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A147" s="35"/>
+      <c r="B147" s="36"/>
+      <c r="C147" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="D147" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="E147" s="37">
+        <v>46098</v>
+      </c>
+      <c r="F147" s="36"/>
+      <c r="G147" s="36"/>
+      <c r="H147" s="36"/>
+      <c r="I147" s="36"/>
+      <c r="J147" s="36"/>
+      <c r="K147" s="36"/>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A148" s="35"/>
+      <c r="B148" s="36"/>
+      <c r="C148" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="D148" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="E148" s="37">
+        <v>46098</v>
+      </c>
+      <c r="F148" s="36"/>
+      <c r="G148" s="36"/>
+      <c r="H148" s="36"/>
+      <c r="I148" s="36"/>
+      <c r="J148" s="36"/>
+      <c r="K148" s="36"/>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A149" s="35"/>
+      <c r="B149" s="36"/>
+      <c r="C149" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="D149" s="36" t="s">
+        <v>269</v>
+      </c>
+      <c r="E149" s="37">
+        <v>46098</v>
+      </c>
+      <c r="F149" s="36"/>
+      <c r="G149" s="36"/>
+      <c r="H149" s="36"/>
+      <c r="I149" s="36"/>
+      <c r="J149" s="36"/>
+      <c r="K149" s="36"/>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A150" s="35"/>
+      <c r="B150" s="36"/>
+      <c r="C150" s="35"/>
+      <c r="D150" s="36"/>
+      <c r="E150" s="35"/>
+      <c r="F150" s="36"/>
+      <c r="G150" s="36"/>
+      <c r="H150" s="36"/>
+      <c r="I150" s="36"/>
+      <c r="J150" s="36"/>
+      <c r="K150" s="36"/>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A151" s="26"/>
+      <c r="B151" s="25"/>
+      <c r="C151" s="26"/>
+      <c r="D151" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="E151" s="26"/>
+      <c r="F151" s="25"/>
+      <c r="G151" s="25"/>
+      <c r="H151" s="25"/>
+      <c r="I151" s="25"/>
+      <c r="J151" s="25"/>
+      <c r="K151" s="25"/>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A152" s="47" t="s">
+        <v>573</v>
+      </c>
+      <c r="B152" s="48" t="s">
+        <v>572</v>
+      </c>
+      <c r="C152" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="D152" s="33" t="s">
+        <v>677</v>
+      </c>
+      <c r="E152" s="34">
         <v>46099</v>
       </c>
-      <c r="F143" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G143" s="5"/>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A144" s="4"/>
-      <c r="B144" s="5"/>
-      <c r="C144" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>659</v>
-      </c>
-      <c r="E144" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G144" s="5"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A145" s="4"/>
-      <c r="B145" s="5"/>
-      <c r="C145" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="E145" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G145" s="5"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A146" s="4"/>
-      <c r="B146" s="5"/>
-      <c r="C146" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="D146" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="E146" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G146" s="5"/>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A147" s="4"/>
-      <c r="B147" s="5"/>
-      <c r="C147" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="D147" s="5" t="s">
-        <v>662</v>
-      </c>
-      <c r="E147" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G147" s="5"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A148" s="4"/>
-      <c r="B148" s="5"/>
-      <c r="C148" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="E148" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F148" s="5"/>
-      <c r="G148" s="5"/>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A149" s="4"/>
-      <c r="B149" s="5"/>
-      <c r="C149" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="D149" s="5" t="s">
-        <v>664</v>
-      </c>
-      <c r="E149" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F149" s="5"/>
-      <c r="G149" s="5"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A150" s="4"/>
-      <c r="B150" s="5"/>
-      <c r="C150" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="E150" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F150" s="5"/>
-      <c r="G150" s="5"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A151" s="4"/>
-      <c r="B151" s="5"/>
-      <c r="C151" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="D151" s="5" t="s">
-        <v>666</v>
-      </c>
-      <c r="E151" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F151" s="5"/>
-      <c r="G151" s="5"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A152" s="4"/>
-      <c r="B152" s="5"/>
-      <c r="C152" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D152" s="5" t="s">
-        <v>667</v>
-      </c>
-      <c r="E152" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F152" s="5"/>
-      <c r="G152" s="5"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A153" s="4"/>
-      <c r="B153" s="5"/>
+      <c r="F152" s="33"/>
+      <c r="G152" s="33"/>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A153" s="13" t="s">
+        <v>574</v>
+      </c>
+      <c r="B153" s="19">
+        <v>11</v>
+      </c>
       <c r="C153" s="4" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="E153" s="17">
         <v>46099</v>
@@ -5420,89 +5450,99 @@
       <c r="F153" s="5"/>
       <c r="G153" s="5"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
       <c r="C154" s="4" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="E154" s="17">
         <v>46099</v>
       </c>
-      <c r="F154" s="5"/>
+      <c r="F154" s="5" t="s">
+        <v>172</v>
+      </c>
       <c r="G154" s="5"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155" s="4"/>
       <c r="B155" s="5"/>
       <c r="C155" s="4" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="E155" s="17">
         <v>46099</v>
       </c>
-      <c r="F155" s="5"/>
+      <c r="F155" s="5" t="s">
+        <v>172</v>
+      </c>
       <c r="G155" s="5"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156" s="4"/>
       <c r="B156" s="5"/>
       <c r="C156" s="4" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="E156" s="17">
         <v>46099</v>
       </c>
-      <c r="F156" s="5"/>
+      <c r="F156" s="5" t="s">
+        <v>172</v>
+      </c>
       <c r="G156" s="5"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157" s="4"/>
       <c r="B157" s="5"/>
       <c r="C157" s="4" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="E157" s="17">
         <v>46099</v>
       </c>
-      <c r="F157" s="5"/>
+      <c r="F157" s="5" t="s">
+        <v>172</v>
+      </c>
       <c r="G157" s="5"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158" s="4"/>
       <c r="B158" s="5"/>
       <c r="C158" s="4" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="E158" s="17">
         <v>46099</v>
       </c>
-      <c r="F158" s="5"/>
+      <c r="F158" s="5" t="s">
+        <v>172</v>
+      </c>
       <c r="G158" s="5"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" s="4"/>
       <c r="B159" s="5"/>
       <c r="C159" s="4" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="E159" s="17">
         <v>46099</v>
@@ -5510,14 +5550,14 @@
       <c r="F159" s="5"/>
       <c r="G159" s="5"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160" s="4"/>
       <c r="B160" s="5"/>
       <c r="C160" s="4" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="E160" s="17">
         <v>46099</v>
@@ -5529,10 +5569,10 @@
       <c r="A161" s="4"/>
       <c r="B161" s="5"/>
       <c r="C161" s="4" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="E161" s="17">
         <v>46099</v>
@@ -5543,24 +5583,26 @@
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4"/>
       <c r="B162" s="5"/>
-      <c r="C162" s="13">
-        <v>11.2</v>
-      </c>
-      <c r="D162" s="12" t="s">
-        <v>657</v>
-      </c>
-      <c r="E162" s="46"/>
-      <c r="F162" s="12"/>
-      <c r="G162" s="12"/>
+      <c r="C162" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="E162" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F162" s="5"/>
+      <c r="G162" s="5"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4"/>
       <c r="B163" s="5"/>
       <c r="C163" s="4" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="E163" s="17">
         <v>46099</v>
@@ -5572,10 +5614,10 @@
       <c r="A164" s="4"/>
       <c r="B164" s="5"/>
       <c r="C164" s="4" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>655</v>
+        <v>668</v>
       </c>
       <c r="E164" s="17">
         <v>46099</v>
@@ -5587,10 +5629,10 @@
       <c r="A165" s="4"/>
       <c r="B165" s="5"/>
       <c r="C165" s="4" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="E165" s="17">
         <v>46099</v>
@@ -5602,10 +5644,10 @@
       <c r="A166" s="4"/>
       <c r="B166" s="5"/>
       <c r="C166" s="4" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="E166" s="17">
         <v>46099</v>
@@ -5617,232 +5659,192 @@
       <c r="A167" s="4"/>
       <c r="B167" s="5"/>
       <c r="C167" s="4" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>652</v>
+        <v>671</v>
       </c>
       <c r="E167" s="17">
         <v>46099</v>
       </c>
-      <c r="F167" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G167" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="F167" s="5"/>
+      <c r="G167" s="5"/>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4"/>
       <c r="B168" s="5"/>
       <c r="C168" s="4" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>651</v>
+        <v>672</v>
       </c>
       <c r="E168" s="17">
         <v>46099</v>
       </c>
-      <c r="F168" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G168" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="F168" s="5"/>
+      <c r="G168" s="5"/>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4"/>
       <c r="B169" s="5"/>
       <c r="C169" s="4" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>650</v>
+        <v>673</v>
       </c>
       <c r="E169" s="17">
         <v>46099</v>
       </c>
-      <c r="F169" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G169" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="F169" s="5"/>
+      <c r="G169" s="5"/>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4"/>
       <c r="B170" s="5"/>
       <c r="C170" s="4" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>649</v>
+        <v>674</v>
       </c>
       <c r="E170" s="17">
         <v>46099</v>
       </c>
-      <c r="F170" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G170" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="F170" s="5"/>
+      <c r="G170" s="5"/>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4"/>
       <c r="B171" s="5"/>
       <c r="C171" s="4" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>648</v>
+        <v>676</v>
       </c>
       <c r="E171" s="17">
         <v>46099</v>
       </c>
-      <c r="F171" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G171" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="F171" s="5"/>
+      <c r="G171" s="5"/>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4"/>
       <c r="B172" s="5"/>
       <c r="C172" s="4" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>647</v>
+        <v>675</v>
       </c>
       <c r="E172" s="17">
         <v>46099</v>
       </c>
-      <c r="F172" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G172" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="F172" s="5"/>
+      <c r="G172" s="5"/>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4"/>
       <c r="B173" s="5"/>
-      <c r="C173" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D173" s="5" t="s">
-        <v>646</v>
-      </c>
-      <c r="E173" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G173" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="C173" s="13">
+        <v>11.2</v>
+      </c>
+      <c r="D173" s="12" t="s">
+        <v>657</v>
+      </c>
+      <c r="E173" s="46"/>
+      <c r="F173" s="12"/>
+      <c r="G173" s="12"/>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4"/>
       <c r="B174" s="5"/>
       <c r="C174" s="4" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="E174" s="17">
         <v>46099</v>
       </c>
-      <c r="F174" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G174" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="F174" s="5"/>
+      <c r="G174" s="5"/>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4"/>
       <c r="B175" s="5"/>
       <c r="C175" s="4" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="E175" s="17">
         <v>46099</v>
       </c>
-      <c r="F175" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G175" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="F175" s="5"/>
+      <c r="G175" s="5"/>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4"/>
       <c r="B176" s="5"/>
       <c r="C176" s="4" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="E176" s="17">
         <v>46099</v>
       </c>
-      <c r="F176" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G176" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="F176" s="5"/>
+      <c r="G176" s="5"/>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4"/>
       <c r="B177" s="5"/>
       <c r="C177" s="4" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="E177" s="17">
         <v>46099</v>
       </c>
-      <c r="F177" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G177" s="5" t="s">
-        <v>172</v>
-      </c>
+      <c r="F177" s="5"/>
+      <c r="G177" s="5"/>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4"/>
       <c r="B178" s="5"/>
-      <c r="C178" s="13">
-        <v>11.3</v>
-      </c>
-      <c r="D178" s="12" t="s">
-        <v>641</v>
-      </c>
-      <c r="E178" s="46"/>
-      <c r="F178" s="12"/>
-      <c r="G178" s="12"/>
+      <c r="C178" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="E178" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4"/>
       <c r="B179" s="5"/>
       <c r="C179" s="4" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>640</v>
+        <v>651</v>
       </c>
       <c r="E179" s="17">
         <v>46099</v>
@@ -5857,24 +5859,30 @@
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4"/>
       <c r="B180" s="5"/>
-      <c r="C180" s="13">
-        <v>11.4</v>
-      </c>
-      <c r="D180" s="12" t="s">
-        <v>637</v>
-      </c>
-      <c r="E180" s="46"/>
-      <c r="F180" s="12"/>
-      <c r="G180" s="12"/>
+      <c r="C180" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="E180" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F180" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G180" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4"/>
       <c r="B181" s="5"/>
       <c r="C181" s="4" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="E181" s="17">
         <v>46099</v>
@@ -5890,10 +5898,10 @@
       <c r="A182" s="4"/>
       <c r="B182" s="5"/>
       <c r="C182" s="4" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="E182" s="17">
         <v>46099</v>
@@ -5908,24 +5916,30 @@
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4"/>
       <c r="B183" s="5"/>
-      <c r="C183" s="13">
-        <v>11.5</v>
-      </c>
-      <c r="D183" s="12" t="s">
-        <v>627</v>
-      </c>
-      <c r="E183" s="46"/>
-      <c r="F183" s="12"/>
-      <c r="G183" s="12"/>
+      <c r="C183" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="E183" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F183" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G183" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4"/>
       <c r="B184" s="5"/>
       <c r="C184" s="4" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>620</v>
+        <v>646</v>
       </c>
       <c r="E184" s="17">
         <v>46099</v>
@@ -5941,55 +5955,67 @@
       <c r="A185" s="4"/>
       <c r="B185" s="5"/>
       <c r="C185" s="4" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="E185" s="17">
         <v>46099</v>
       </c>
-      <c r="F185" s="5"/>
-      <c r="G185" s="5"/>
+      <c r="F185" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G185" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4"/>
       <c r="B186" s="5"/>
       <c r="C186" s="4" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>622</v>
+        <v>644</v>
       </c>
       <c r="E186" s="17">
         <v>46099</v>
       </c>
-      <c r="F186" s="5"/>
-      <c r="G186" s="5"/>
+      <c r="F186" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G186" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4"/>
       <c r="B187" s="5"/>
       <c r="C187" s="4" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>623</v>
+        <v>643</v>
       </c>
       <c r="E187" s="17">
         <v>46099</v>
       </c>
-      <c r="F187" s="5"/>
-      <c r="G187" s="5"/>
+      <c r="F187" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4"/>
       <c r="B188" s="5"/>
       <c r="C188" s="4" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>628</v>
+        <v>642</v>
       </c>
       <c r="E188" s="17">
         <v>46099</v>
@@ -6004,56 +6030,56 @@
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="4"/>
       <c r="B189" s="5"/>
-      <c r="C189" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="D189" s="5" t="s">
-        <v>624</v>
-      </c>
-      <c r="E189" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F189" s="5"/>
-      <c r="G189" s="5"/>
+      <c r="C189" s="13">
+        <v>11.3</v>
+      </c>
+      <c r="D189" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="E189" s="46"/>
+      <c r="F189" s="12"/>
+      <c r="G189" s="12"/>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="4"/>
       <c r="B190" s="5"/>
       <c r="C190" s="4" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="E190" s="17">
         <v>46099</v>
       </c>
-      <c r="F190" s="5"/>
-      <c r="G190" s="5"/>
+      <c r="F190" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G190" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="4"/>
       <c r="B191" s="5"/>
-      <c r="C191" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="D191" s="5" t="s">
-        <v>626</v>
-      </c>
-      <c r="E191" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F191" s="5"/>
-      <c r="G191" s="5"/>
+      <c r="C191" s="13">
+        <v>11.4</v>
+      </c>
+      <c r="D191" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="E191" s="46"/>
+      <c r="F191" s="12"/>
+      <c r="G191" s="12"/>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="4"/>
       <c r="B192" s="5"/>
       <c r="C192" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="D192" s="49" t="s">
-        <v>630</v>
+        <v>307</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>638</v>
       </c>
       <c r="E192" s="17">
         <v>46099</v>
@@ -6069,55 +6095,61 @@
       <c r="A193" s="4"/>
       <c r="B193" s="5"/>
       <c r="C193" s="4" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="E193" s="17">
         <v>46099</v>
       </c>
-      <c r="F193" s="5"/>
-      <c r="G193" s="5"/>
+      <c r="F193" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G193" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="4"/>
       <c r="B194" s="5"/>
-      <c r="C194" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D194" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="E194" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F194" s="5"/>
-      <c r="G194" s="5"/>
+      <c r="C194" s="13">
+        <v>11.5</v>
+      </c>
+      <c r="D194" s="12" t="s">
+        <v>627</v>
+      </c>
+      <c r="E194" s="46"/>
+      <c r="F194" s="12"/>
+      <c r="G194" s="12"/>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="4"/>
       <c r="B195" s="5"/>
       <c r="C195" s="4" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="E195" s="17">
         <v>46099</v>
       </c>
-      <c r="F195" s="5"/>
-      <c r="G195" s="5"/>
+      <c r="F195" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G195" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="4"/>
       <c r="B196" s="5"/>
       <c r="C196" s="4" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="E196" s="17">
         <v>46099</v>
@@ -6129,10 +6161,10 @@
       <c r="A197" s="4"/>
       <c r="B197" s="5"/>
       <c r="C197" s="4" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="E197" s="17">
         <v>46099</v>
@@ -6144,10 +6176,10 @@
       <c r="A198" s="4"/>
       <c r="B198" s="5"/>
       <c r="C198" s="4" t="s">
-        <v>629</v>
+        <v>312</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="E198" s="17">
         <v>46099</v>
@@ -6158,24 +6190,30 @@
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="4"/>
       <c r="B199" s="5"/>
-      <c r="C199" s="13">
-        <v>11.6</v>
-      </c>
-      <c r="D199" s="12" t="s">
-        <v>613</v>
-      </c>
-      <c r="E199" s="46"/>
-      <c r="F199" s="12"/>
-      <c r="G199" s="12"/>
+      <c r="C199" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="E199" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G199" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="4"/>
       <c r="B200" s="5"/>
       <c r="C200" s="4" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>614</v>
+        <v>624</v>
       </c>
       <c r="E200" s="17">
         <v>46099</v>
@@ -6187,10 +6225,10 @@
       <c r="A201" s="4"/>
       <c r="B201" s="5"/>
       <c r="C201" s="4" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="E201" s="17">
         <v>46099</v>
@@ -6202,10 +6240,10 @@
       <c r="A202" s="4"/>
       <c r="B202" s="5"/>
       <c r="C202" s="4" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="E202" s="17">
         <v>46099</v>
@@ -6217,25 +6255,29 @@
       <c r="A203" s="4"/>
       <c r="B203" s="5"/>
       <c r="C203" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="D203" s="5" t="s">
-        <v>617</v>
+        <v>317</v>
+      </c>
+      <c r="D203" s="49" t="s">
+        <v>630</v>
       </c>
       <c r="E203" s="17">
         <v>46099</v>
       </c>
-      <c r="F203" s="5"/>
-      <c r="G203" s="5"/>
+      <c r="F203" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G203" s="5" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="4"/>
       <c r="B204" s="5"/>
       <c r="C204" s="4" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>618</v>
+        <v>631</v>
       </c>
       <c r="E204" s="17">
         <v>46099</v>
@@ -6247,10 +6289,10 @@
       <c r="A205" s="4"/>
       <c r="B205" s="5"/>
       <c r="C205" s="4" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>619</v>
+        <v>632</v>
       </c>
       <c r="E205" s="17">
         <v>46099</v>
@@ -6261,24 +6303,26 @@
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="4"/>
       <c r="B206" s="5"/>
-      <c r="C206" s="13">
-        <v>11.7</v>
-      </c>
-      <c r="D206" s="12" t="s">
-        <v>611</v>
-      </c>
-      <c r="E206" s="46"/>
-      <c r="F206" s="12"/>
-      <c r="G206" s="12"/>
+      <c r="C206" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D206" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="E206" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F206" s="5"/>
+      <c r="G206" s="5"/>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="4"/>
       <c r="B207" s="5"/>
       <c r="C207" s="4" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>603</v>
+        <v>634</v>
       </c>
       <c r="E207" s="17">
         <v>46099</v>
@@ -6290,10 +6334,10 @@
       <c r="A208" s="4"/>
       <c r="B208" s="5"/>
       <c r="C208" s="4" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="E208" s="17">
         <v>46099</v>
@@ -6305,10 +6349,10 @@
       <c r="A209" s="4"/>
       <c r="B209" s="5"/>
       <c r="C209" s="4" t="s">
-        <v>331</v>
+        <v>629</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>605</v>
+        <v>636</v>
       </c>
       <c r="E209" s="17">
         <v>46099</v>
@@ -6319,26 +6363,24 @@
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="4"/>
       <c r="B210" s="5"/>
-      <c r="C210" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="D210" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="E210" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F210" s="5"/>
-      <c r="G210" s="5"/>
+      <c r="C210" s="13">
+        <v>11.6</v>
+      </c>
+      <c r="D210" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="E210" s="46"/>
+      <c r="F210" s="12"/>
+      <c r="G210" s="12"/>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="4"/>
       <c r="B211" s="5"/>
       <c r="C211" s="4" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="E211" s="17">
         <v>46099</v>
@@ -6350,10 +6392,10 @@
       <c r="A212" s="4"/>
       <c r="B212" s="5"/>
       <c r="C212" s="4" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="E212" s="17">
         <v>46099</v>
@@ -6365,10 +6407,10 @@
       <c r="A213" s="4"/>
       <c r="B213" s="5"/>
       <c r="C213" s="4" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="E213" s="17">
         <v>46099</v>
@@ -6380,10 +6422,10 @@
       <c r="A214" s="4"/>
       <c r="B214" s="5"/>
       <c r="C214" s="4" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="E214" s="17">
         <v>46099</v>
@@ -6394,27 +6436,29 @@
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="4"/>
       <c r="B215" s="5"/>
-      <c r="C215" s="13">
-        <v>11.8</v>
-      </c>
-      <c r="D215" s="12" t="s">
-        <v>612</v>
-      </c>
-      <c r="E215" s="46"/>
-      <c r="F215" s="12"/>
-      <c r="G215" s="12"/>
+      <c r="C215" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D215" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="E215" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F215" s="5"/>
+      <c r="G215" s="5"/>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="4"/>
       <c r="B216" s="5"/>
       <c r="C216" s="4" t="s">
-        <v>575</v>
+        <v>328</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>589</v>
+        <v>619</v>
       </c>
       <c r="E216" s="17">
-        <v>46275</v>
+        <v>46099</v>
       </c>
       <c r="F216" s="5"/>
       <c r="G216" s="5"/>
@@ -6422,29 +6466,27 @@
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="4"/>
       <c r="B217" s="5"/>
-      <c r="C217" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="D217" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="E217" s="17">
-        <v>46275</v>
-      </c>
-      <c r="F217" s="5"/>
-      <c r="G217" s="5"/>
+      <c r="C217" s="13">
+        <v>11.7</v>
+      </c>
+      <c r="D217" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="E217" s="46"/>
+      <c r="F217" s="12"/>
+      <c r="G217" s="12"/>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="4"/>
       <c r="B218" s="5"/>
       <c r="C218" s="4" t="s">
-        <v>577</v>
+        <v>329</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="E218" s="17">
-        <v>46275</v>
+        <v>46099</v>
       </c>
       <c r="F218" s="5"/>
       <c r="G218" s="5"/>
@@ -6453,13 +6495,13 @@
       <c r="A219" s="4"/>
       <c r="B219" s="5"/>
       <c r="C219" s="4" t="s">
-        <v>578</v>
+        <v>330</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="E219" s="17">
-        <v>46275</v>
+        <v>46099</v>
       </c>
       <c r="F219" s="5"/>
       <c r="G219" s="5"/>
@@ -6468,13 +6510,13 @@
       <c r="A220" s="4"/>
       <c r="B220" s="5"/>
       <c r="C220" s="4" t="s">
-        <v>579</v>
+        <v>331</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="E220" s="17">
-        <v>46275</v>
+        <v>46099</v>
       </c>
       <c r="F220" s="5"/>
       <c r="G220" s="5"/>
@@ -6483,13 +6525,13 @@
       <c r="A221" s="4"/>
       <c r="B221" s="5"/>
       <c r="C221" s="4" t="s">
-        <v>580</v>
+        <v>332</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="E221" s="17">
-        <v>46275</v>
+        <v>46099</v>
       </c>
       <c r="F221" s="5"/>
       <c r="G221" s="5"/>
@@ -6498,13 +6540,13 @@
       <c r="A222" s="4"/>
       <c r="B222" s="5"/>
       <c r="C222" s="4" t="s">
-        <v>581</v>
+        <v>333</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="E222" s="17">
-        <v>46275</v>
+        <v>46099</v>
       </c>
       <c r="F222" s="5"/>
       <c r="G222" s="5"/>
@@ -6513,13 +6555,13 @@
       <c r="A223" s="4"/>
       <c r="B223" s="5"/>
       <c r="C223" s="4" t="s">
-        <v>582</v>
+        <v>334</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="E223" s="17">
-        <v>46275</v>
+        <v>46099</v>
       </c>
       <c r="F223" s="5"/>
       <c r="G223" s="5"/>
@@ -6528,13 +6570,13 @@
       <c r="A224" s="4"/>
       <c r="B224" s="5"/>
       <c r="C224" s="4" t="s">
-        <v>583</v>
+        <v>335</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="E224" s="17">
-        <v>46275</v>
+        <v>46099</v>
       </c>
       <c r="F224" s="5"/>
       <c r="G224" s="5"/>
@@ -6543,13 +6585,13 @@
       <c r="A225" s="4"/>
       <c r="B225" s="5"/>
       <c r="C225" s="4" t="s">
-        <v>584</v>
+        <v>336</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="E225" s="17">
-        <v>46275</v>
+        <v>46099</v>
       </c>
       <c r="F225" s="5"/>
       <c r="G225" s="5"/>
@@ -6557,26 +6599,24 @@
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="4"/>
       <c r="B226" s="5"/>
-      <c r="C226" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="D226" s="5" t="s">
-        <v>599</v>
-      </c>
-      <c r="E226" s="17">
-        <v>46275</v>
-      </c>
-      <c r="F226" s="5"/>
-      <c r="G226" s="5"/>
+      <c r="C226" s="13">
+        <v>11.8</v>
+      </c>
+      <c r="D226" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="E226" s="46"/>
+      <c r="F226" s="12"/>
+      <c r="G226" s="12"/>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="4"/>
       <c r="B227" s="5"/>
       <c r="C227" s="4" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="E227" s="17">
         <v>46275</v>
@@ -6588,10 +6628,10 @@
       <c r="A228" s="4"/>
       <c r="B228" s="5"/>
       <c r="C228" s="4" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="E228" s="17">
         <v>46275</v>
@@ -6603,10 +6643,10 @@
       <c r="A229" s="4"/>
       <c r="B229" s="5"/>
       <c r="C229" s="4" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="E229" s="17">
         <v>46275</v>
@@ -6617,112 +6657,178 @@
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="4"/>
       <c r="B230" s="5"/>
-      <c r="C230" s="13">
-        <v>11.9</v>
-      </c>
-      <c r="D230" s="12"/>
-      <c r="E230" s="46"/>
-      <c r="F230" s="12"/>
-      <c r="G230" s="12"/>
+      <c r="C230" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="D230" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="E230" s="17">
+        <v>46275</v>
+      </c>
+      <c r="F230" s="5"/>
+      <c r="G230" s="5"/>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="4"/>
       <c r="B231" s="5"/>
-      <c r="C231" s="4"/>
-      <c r="D231" s="5"/>
-      <c r="E231" s="17"/>
+      <c r="C231" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="E231" s="17">
+        <v>46275</v>
+      </c>
       <c r="F231" s="5"/>
       <c r="G231" s="5"/>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="4"/>
       <c r="B232" s="5"/>
-      <c r="C232" s="4"/>
-      <c r="D232" s="5"/>
-      <c r="E232" s="17"/>
+      <c r="C232" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="D232" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="E232" s="17">
+        <v>46275</v>
+      </c>
       <c r="F232" s="5"/>
       <c r="G232" s="5"/>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="4"/>
       <c r="B233" s="5"/>
-      <c r="C233" s="4"/>
-      <c r="D233" s="5"/>
-      <c r="E233" s="17"/>
+      <c r="C233" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="D233" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="E233" s="17">
+        <v>46275</v>
+      </c>
       <c r="F233" s="5"/>
       <c r="G233" s="5"/>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="4"/>
       <c r="B234" s="5"/>
-      <c r="C234" s="4"/>
-      <c r="D234" s="5"/>
-      <c r="E234" s="17"/>
+      <c r="C234" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="D234" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="E234" s="17">
+        <v>46275</v>
+      </c>
       <c r="F234" s="5"/>
       <c r="G234" s="5"/>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="4"/>
       <c r="B235" s="5"/>
-      <c r="C235" s="4"/>
-      <c r="D235" s="5"/>
-      <c r="E235" s="17"/>
+      <c r="C235" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="D235" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="E235" s="17">
+        <v>46275</v>
+      </c>
       <c r="F235" s="5"/>
       <c r="G235" s="5"/>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="4"/>
       <c r="B236" s="5"/>
-      <c r="C236" s="4"/>
-      <c r="D236" s="5"/>
-      <c r="E236" s="17"/>
+      <c r="C236" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="D236" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="E236" s="17">
+        <v>46275</v>
+      </c>
       <c r="F236" s="5"/>
       <c r="G236" s="5"/>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="4"/>
       <c r="B237" s="5"/>
-      <c r="C237" s="4"/>
-      <c r="D237" s="5"/>
-      <c r="E237" s="17"/>
+      <c r="C237" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="D237" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="E237" s="17">
+        <v>46275</v>
+      </c>
       <c r="F237" s="5"/>
       <c r="G237" s="5"/>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="4"/>
       <c r="B238" s="5"/>
-      <c r="C238" s="4"/>
-      <c r="D238" s="5"/>
-      <c r="E238" s="17"/>
+      <c r="C238" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="D238" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="E238" s="17">
+        <v>46275</v>
+      </c>
       <c r="F238" s="5"/>
       <c r="G238" s="5"/>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="4"/>
       <c r="B239" s="5"/>
-      <c r="C239" s="4"/>
-      <c r="D239" s="5"/>
-      <c r="E239" s="17"/>
+      <c r="C239" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="D239" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="E239" s="17">
+        <v>46275</v>
+      </c>
       <c r="F239" s="5"/>
       <c r="G239" s="5"/>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="4"/>
       <c r="B240" s="5"/>
-      <c r="C240" s="4"/>
-      <c r="D240" s="5"/>
-      <c r="E240" s="17"/>
+      <c r="C240" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="D240" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="E240" s="17">
+        <v>46275</v>
+      </c>
       <c r="F240" s="5"/>
       <c r="G240" s="5"/>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="4"/>
       <c r="B241" s="5"/>
-      <c r="C241" s="4"/>
-      <c r="D241" s="5"/>
-      <c r="E241" s="17"/>
-      <c r="F241" s="5"/>
-      <c r="G241" s="5"/>
+      <c r="C241" s="13">
+        <v>11.9</v>
+      </c>
+      <c r="D241" s="12"/>
+      <c r="E241" s="46"/>
+      <c r="F241" s="12"/>
+      <c r="G241" s="12"/>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="4"/>
@@ -6738,704 +6844,614 @@
       <c r="B243" s="5"/>
       <c r="C243" s="4"/>
       <c r="D243" s="5"/>
-      <c r="E243" s="4"/>
+      <c r="E243" s="17"/>
       <c r="F243" s="5"/>
       <c r="G243" s="5"/>
     </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A244" s="4"/>
+      <c r="B244" s="5"/>
+      <c r="C244" s="4"/>
+      <c r="D244" s="5"/>
+      <c r="E244" s="17"/>
+      <c r="F244" s="5"/>
+      <c r="G244" s="5"/>
+    </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B245" t="s">
+      <c r="A245" s="4"/>
+      <c r="B245" s="5"/>
+      <c r="C245" s="4"/>
+      <c r="D245" s="5"/>
+      <c r="E245" s="17"/>
+      <c r="F245" s="5"/>
+      <c r="G245" s="5"/>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A246" s="4"/>
+      <c r="B246" s="5"/>
+      <c r="C246" s="4"/>
+      <c r="D246" s="5"/>
+      <c r="E246" s="17"/>
+      <c r="F246" s="5"/>
+      <c r="G246" s="5"/>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A247" s="4"/>
+      <c r="B247" s="5"/>
+      <c r="C247" s="4"/>
+      <c r="D247" s="5"/>
+      <c r="E247" s="17"/>
+      <c r="F247" s="5"/>
+      <c r="G247" s="5"/>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A248" s="4"/>
+      <c r="B248" s="5"/>
+      <c r="C248" s="4"/>
+      <c r="D248" s="5"/>
+      <c r="E248" s="17"/>
+      <c r="F248" s="5"/>
+      <c r="G248" s="5"/>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A249" s="4"/>
+      <c r="B249" s="5"/>
+      <c r="C249" s="4"/>
+      <c r="D249" s="5"/>
+      <c r="E249" s="17"/>
+      <c r="F249" s="5"/>
+      <c r="G249" s="5"/>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A250" s="4"/>
+      <c r="B250" s="5"/>
+      <c r="C250" s="4"/>
+      <c r="D250" s="5"/>
+      <c r="E250" s="17"/>
+      <c r="F250" s="5"/>
+      <c r="G250" s="5"/>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A251" s="4"/>
+      <c r="B251" s="5"/>
+      <c r="C251" s="4"/>
+      <c r="D251" s="5"/>
+      <c r="E251" s="17"/>
+      <c r="F251" s="5"/>
+      <c r="G251" s="5"/>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A252" s="4"/>
+      <c r="B252" s="5"/>
+      <c r="C252" s="4"/>
+      <c r="D252" s="5"/>
+      <c r="E252" s="17"/>
+      <c r="F252" s="5"/>
+      <c r="G252" s="5"/>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A253" s="4"/>
+      <c r="B253" s="5"/>
+      <c r="C253" s="4"/>
+      <c r="D253" s="5"/>
+      <c r="E253" s="17"/>
+      <c r="F253" s="5"/>
+      <c r="G253" s="5"/>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A254" s="4"/>
+      <c r="B254" s="5"/>
+      <c r="C254" s="4"/>
+      <c r="D254" s="5"/>
+      <c r="E254" s="4"/>
+      <c r="F254" s="5"/>
+      <c r="G254" s="5"/>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B256" t="s">
         <v>565</v>
       </c>
-      <c r="C245" s="1" t="s">
+      <c r="C256" s="1" t="s">
         <v>463</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C246" s="1" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C247" s="1" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C248" s="1" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C249" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C250" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C251" s="1" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C252" s="1" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C253" s="1" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C254" s="1" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C255" s="1" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C256" s="1" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="257" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C257" s="1" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
     </row>
     <row r="258" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C258" s="1" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
     </row>
     <row r="259" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C259" s="1" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
     </row>
     <row r="260" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C260" s="1" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
     </row>
     <row r="261" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C261" s="1" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
     </row>
     <row r="262" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C262" s="1" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
     </row>
     <row r="263" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C263" s="1" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
     </row>
     <row r="264" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C264" s="1" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
     </row>
     <row r="265" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C265" s="1" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
     </row>
     <row r="266" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C266" s="1" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
     </row>
     <row r="267" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C267" s="1" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
     </row>
     <row r="268" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C268" s="1" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
     </row>
     <row r="269" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C269" s="1" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
     </row>
     <row r="270" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C270" s="1" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
     </row>
     <row r="271" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C271" s="1" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
     </row>
     <row r="272" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C272" s="1" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
     </row>
     <row r="273" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C273" s="1" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
     </row>
     <row r="274" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C274" s="1" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
     </row>
     <row r="275" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C275" s="1" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
     </row>
     <row r="276" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C276" s="1" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
     </row>
     <row r="277" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C277" s="1" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
     </row>
     <row r="278" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C278" s="1" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
     </row>
     <row r="279" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C279" s="1" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
     </row>
     <row r="280" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C280" s="1" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
     </row>
     <row r="281" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C281" s="1" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
     </row>
     <row r="282" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C282" s="1" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
     </row>
     <row r="283" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C283" s="1" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
     </row>
     <row r="284" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C284" s="1" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
     </row>
     <row r="285" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C285" s="1" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
     </row>
     <row r="286" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C286" s="1" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
     </row>
     <row r="287" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C287" s="1" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
     </row>
     <row r="288" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C288" s="1" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
     </row>
     <row r="289" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C289" s="1" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
     </row>
     <row r="290" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C290" s="1" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="291" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C291" s="1" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
     </row>
     <row r="292" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C292" s="1" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
     </row>
     <row r="293" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C293" s="1" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
     </row>
     <row r="294" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C294" s="1" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
     </row>
     <row r="295" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C295" s="1" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
     </row>
     <row r="296" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C296" s="1" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
     </row>
     <row r="297" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C297" s="1" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
     </row>
     <row r="298" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C298" s="1" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
     </row>
     <row r="299" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C299" s="1" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
     </row>
     <row r="300" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C300" s="1" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
     </row>
     <row r="301" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C301" s="1" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
     </row>
     <row r="302" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C302" s="1" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
     </row>
     <row r="303" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C303" s="1" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="304" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C304" s="1" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
     </row>
     <row r="305" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C305" s="1" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
     </row>
     <row r="306" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C306" s="1" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
     </row>
     <row r="307" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C307" s="1" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
     </row>
     <row r="308" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C308" s="1" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
     </row>
     <row r="309" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C309" s="1" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
     </row>
     <row r="310" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C310" s="1" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
     </row>
     <row r="311" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C311" s="1" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
     </row>
     <row r="312" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C312" s="1" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
     </row>
     <row r="313" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C313" s="1" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
     </row>
     <row r="314" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C314" s="1" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
     </row>
     <row r="315" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C315" s="1" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
     </row>
     <row r="316" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C316" s="1" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
     </row>
     <row r="317" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C317" s="1" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
     </row>
     <row r="318" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C318" s="1" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
     </row>
     <row r="319" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C319" s="1" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
     </row>
     <row r="320" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C320" s="1" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
     </row>
     <row r="321" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C321" s="1" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
     </row>
     <row r="322" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C322" s="1" t="s">
-        <v>540</v>
+        <v>529</v>
+      </c>
+    </row>
+    <row r="323" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C323" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="324" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C324" s="1" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="325" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B325" t="s">
-        <v>571</v>
-      </c>
       <c r="C325" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="D325" t="s">
-        <v>712</v>
+        <v>532</v>
       </c>
     </row>
     <row r="326" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C326" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="D326" t="s">
-        <v>713</v>
+        <v>533</v>
       </c>
     </row>
     <row r="327" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C327" s="1" t="s">
-        <v>704</v>
+        <v>534</v>
       </c>
     </row>
     <row r="328" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C328" s="1" t="s">
-        <v>705</v>
+        <v>535</v>
       </c>
     </row>
     <row r="329" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C329" s="1" t="s">
-        <v>706</v>
+        <v>536</v>
       </c>
     </row>
     <row r="330" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C330" s="1" t="s">
-        <v>707</v>
+        <v>537</v>
       </c>
     </row>
     <row r="331" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C331" s="1" t="s">
-        <v>708</v>
+        <v>538</v>
       </c>
     </row>
     <row r="332" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C332" s="1" t="s">
-        <v>709</v>
+        <v>539</v>
       </c>
     </row>
     <row r="333" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C333" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="336" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B336" t="s">
+        <v>571</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="D336" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="337" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C337" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="D337" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="338" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C338" s="1" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="339" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C339" s="1" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="340" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C340" s="1" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="341" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C341" s="1" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="342" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C342" s="1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="343" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C343" s="1" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="344" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C344" s="1" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="335" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B335" t="s">
+    <row r="346" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B346" t="s">
         <v>541</v>
       </c>
-      <c r="C335" s="1" t="s">
+      <c r="C346" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="D335" t="s">
+      <c r="D346" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="336" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="C336" s="1" t="s">
+    <row r="347" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C347" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="D336" t="s">
+      <c r="D347" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C337" s="1" t="s">
+    <row r="348" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C348" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="D337" t="s">
+      <c r="D348" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C338" s="1" t="s">
+    <row r="349" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C349" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="D338" t="s">
+      <c r="D349" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C339" s="1" t="s">
+    <row r="350" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C350" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="D339" t="s">
+      <c r="D350" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C340" s="1" t="s">
+    <row r="351" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C351" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="D340" t="s">
+      <c r="D351" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C341" s="1" t="s">
+    <row r="352" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C352" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="D341" t="s">
+      <c r="D352" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A349" s="20"/>
-      <c r="B349" s="21"/>
-      <c r="C349" s="20"/>
-      <c r="D349" s="21"/>
-      <c r="E349" s="20"/>
-      <c r="F349" s="21"/>
-      <c r="G349" s="21"/>
-      <c r="H349" s="21"/>
-      <c r="I349" s="21"/>
-      <c r="J349" s="21"/>
-      <c r="K349" s="21"/>
-    </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A350" s="22">
-        <v>13</v>
-      </c>
-      <c r="B350" s="23" t="s">
-        <v>546</v>
-      </c>
-      <c r="C350" s="22" t="s">
-        <v>547</v>
-      </c>
-      <c r="D350" s="24" t="s">
-        <v>553</v>
-      </c>
-      <c r="E350" s="22" t="s">
-        <v>565</v>
-      </c>
-      <c r="F350" s="22" t="s">
-        <v>566</v>
-      </c>
-      <c r="G350" s="24" t="s">
-        <v>567</v>
-      </c>
-      <c r="H350" s="24"/>
-      <c r="I350" s="24"/>
-      <c r="J350" s="24"/>
-      <c r="K350" s="24"/>
-    </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A351" s="22"/>
-      <c r="B351" s="24"/>
-      <c r="C351" s="22" t="s">
-        <v>548</v>
-      </c>
-      <c r="D351" s="24" t="s">
-        <v>555</v>
-      </c>
-      <c r="E351" s="22"/>
-      <c r="F351" s="24"/>
-      <c r="G351" s="24"/>
-      <c r="H351" s="24"/>
-      <c r="I351" s="24"/>
-      <c r="J351" s="24"/>
-      <c r="K351" s="24"/>
-    </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A352" s="22"/>
-      <c r="B352" s="24"/>
-      <c r="C352" s="22" t="s">
-        <v>549</v>
-      </c>
-      <c r="D352" s="24" t="s">
-        <v>554</v>
-      </c>
-      <c r="E352" s="22"/>
-      <c r="F352" s="24"/>
-      <c r="G352" s="24"/>
-      <c r="H352" s="24"/>
-      <c r="I352" s="24"/>
-      <c r="J352" s="24"/>
-      <c r="K352" s="24"/>
-    </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A353" s="22"/>
-      <c r="B353" s="24"/>
-      <c r="C353" s="22" t="s">
-        <v>550</v>
-      </c>
-      <c r="D353" s="24" t="s">
-        <v>556</v>
-      </c>
-      <c r="E353" s="22"/>
-      <c r="F353" s="24"/>
-      <c r="G353" s="24"/>
-      <c r="H353" s="24"/>
-      <c r="I353" s="24"/>
-      <c r="J353" s="24"/>
-      <c r="K353" s="24"/>
-    </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A354" s="22"/>
-      <c r="B354" s="24"/>
-      <c r="C354" s="22" t="s">
-        <v>551</v>
-      </c>
-      <c r="D354" s="24" t="s">
-        <v>557</v>
-      </c>
-      <c r="E354" s="22"/>
-      <c r="F354" s="24"/>
-      <c r="G354" s="24"/>
-      <c r="H354" s="24"/>
-      <c r="I354" s="24"/>
-      <c r="J354" s="24"/>
-      <c r="K354" s="24"/>
-    </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A355" s="22"/>
-      <c r="B355" s="24"/>
-      <c r="C355" s="22" t="s">
-        <v>552</v>
-      </c>
-      <c r="D355" s="24" t="s">
-        <v>558</v>
-      </c>
-      <c r="E355" s="22"/>
-      <c r="F355" s="24"/>
-      <c r="G355" s="24"/>
-      <c r="H355" s="24"/>
-      <c r="I355" s="24"/>
-      <c r="J355" s="24"/>
-      <c r="K355" s="24"/>
-    </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A356" s="22"/>
-      <c r="B356" s="24"/>
-      <c r="C356" s="22" t="s">
-        <v>559</v>
-      </c>
-      <c r="D356" s="24" t="s">
-        <v>562</v>
-      </c>
-      <c r="E356" s="22"/>
-      <c r="F356" s="24"/>
-      <c r="G356" s="24"/>
-      <c r="H356" s="24"/>
-      <c r="I356" s="24"/>
-      <c r="J356" s="24"/>
-      <c r="K356" s="24"/>
-    </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A357" s="22"/>
-      <c r="B357" s="24"/>
-      <c r="C357" s="22" t="s">
-        <v>560</v>
-      </c>
-      <c r="D357" s="24" t="s">
-        <v>563</v>
-      </c>
-      <c r="E357" s="22"/>
-      <c r="F357" s="24"/>
-      <c r="G357" s="24"/>
-      <c r="H357" s="24"/>
-      <c r="I357" s="24"/>
-      <c r="J357" s="24"/>
-      <c r="K357" s="24"/>
-    </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A358" s="22"/>
-      <c r="B358" s="24"/>
-      <c r="C358" s="22" t="s">
-        <v>561</v>
-      </c>
-      <c r="D358" s="24" t="s">
-        <v>564</v>
-      </c>
-      <c r="E358" s="22"/>
-      <c r="F358" s="24"/>
-      <c r="G358" s="24"/>
-      <c r="H358" s="24"/>
-      <c r="I358" s="24"/>
-      <c r="J358" s="24"/>
-      <c r="K358" s="24"/>
-    </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A359" s="22"/>
-      <c r="B359" s="24"/>
-      <c r="C359" s="22"/>
-      <c r="D359" s="24"/>
-      <c r="E359" s="22"/>
-      <c r="F359" s="24"/>
-      <c r="G359" s="24"/>
-      <c r="H359" s="24"/>
-      <c r="I359" s="24"/>
-      <c r="J359" s="24"/>
-      <c r="K359" s="24"/>
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A360" s="20"/>
@@ -7450,554 +7466,556 @@
       <c r="J360" s="21"/>
       <c r="K360" s="21"/>
     </row>
+    <row r="361" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A361" s="22">
+        <v>13</v>
+      </c>
+      <c r="B361" s="23" t="s">
+        <v>546</v>
+      </c>
+      <c r="C361" s="22" t="s">
+        <v>547</v>
+      </c>
+      <c r="D361" s="24" t="s">
+        <v>553</v>
+      </c>
+      <c r="E361" s="22" t="s">
+        <v>565</v>
+      </c>
+      <c r="F361" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="G361" s="24" t="s">
+        <v>567</v>
+      </c>
+      <c r="H361" s="24"/>
+      <c r="I361" s="24"/>
+      <c r="J361" s="24"/>
+      <c r="K361" s="24"/>
+    </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A362" s="4">
+      <c r="A362" s="22"/>
+      <c r="B362" s="24"/>
+      <c r="C362" s="22" t="s">
+        <v>548</v>
+      </c>
+      <c r="D362" s="24" t="s">
+        <v>555</v>
+      </c>
+      <c r="E362" s="22"/>
+      <c r="F362" s="24"/>
+      <c r="G362" s="24"/>
+      <c r="H362" s="24"/>
+      <c r="I362" s="24"/>
+      <c r="J362" s="24"/>
+      <c r="K362" s="24"/>
+    </row>
+    <row r="363" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A363" s="22"/>
+      <c r="B363" s="24"/>
+      <c r="C363" s="22" t="s">
+        <v>549</v>
+      </c>
+      <c r="D363" s="24" t="s">
+        <v>554</v>
+      </c>
+      <c r="E363" s="22"/>
+      <c r="F363" s="24"/>
+      <c r="G363" s="24"/>
+      <c r="H363" s="24"/>
+      <c r="I363" s="24"/>
+      <c r="J363" s="24"/>
+      <c r="K363" s="24"/>
+    </row>
+    <row r="364" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A364" s="22"/>
+      <c r="B364" s="24"/>
+      <c r="C364" s="22" t="s">
+        <v>550</v>
+      </c>
+      <c r="D364" s="24" t="s">
+        <v>556</v>
+      </c>
+      <c r="E364" s="22"/>
+      <c r="F364" s="24"/>
+      <c r="G364" s="24"/>
+      <c r="H364" s="24"/>
+      <c r="I364" s="24"/>
+      <c r="J364" s="24"/>
+      <c r="K364" s="24"/>
+    </row>
+    <row r="365" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A365" s="22"/>
+      <c r="B365" s="24"/>
+      <c r="C365" s="22" t="s">
+        <v>551</v>
+      </c>
+      <c r="D365" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="E365" s="22"/>
+      <c r="F365" s="24"/>
+      <c r="G365" s="24"/>
+      <c r="H365" s="24"/>
+      <c r="I365" s="24"/>
+      <c r="J365" s="24"/>
+      <c r="K365" s="24"/>
+    </row>
+    <row r="366" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A366" s="22"/>
+      <c r="B366" s="24"/>
+      <c r="C366" s="22" t="s">
+        <v>552</v>
+      </c>
+      <c r="D366" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="E366" s="22"/>
+      <c r="F366" s="24"/>
+      <c r="G366" s="24"/>
+      <c r="H366" s="24"/>
+      <c r="I366" s="24"/>
+      <c r="J366" s="24"/>
+      <c r="K366" s="24"/>
+    </row>
+    <row r="367" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A367" s="22"/>
+      <c r="B367" s="24"/>
+      <c r="C367" s="22" t="s">
+        <v>559</v>
+      </c>
+      <c r="D367" s="24" t="s">
+        <v>562</v>
+      </c>
+      <c r="E367" s="22"/>
+      <c r="F367" s="24"/>
+      <c r="G367" s="24"/>
+      <c r="H367" s="24"/>
+      <c r="I367" s="24"/>
+      <c r="J367" s="24"/>
+      <c r="K367" s="24"/>
+    </row>
+    <row r="368" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A368" s="22"/>
+      <c r="B368" s="24"/>
+      <c r="C368" s="22" t="s">
+        <v>560</v>
+      </c>
+      <c r="D368" s="24" t="s">
+        <v>563</v>
+      </c>
+      <c r="E368" s="22"/>
+      <c r="F368" s="24"/>
+      <c r="G368" s="24"/>
+      <c r="H368" s="24"/>
+      <c r="I368" s="24"/>
+      <c r="J368" s="24"/>
+      <c r="K368" s="24"/>
+    </row>
+    <row r="369" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A369" s="22"/>
+      <c r="B369" s="24"/>
+      <c r="C369" s="22" t="s">
+        <v>561</v>
+      </c>
+      <c r="D369" s="24" t="s">
+        <v>564</v>
+      </c>
+      <c r="E369" s="22"/>
+      <c r="F369" s="24"/>
+      <c r="G369" s="24"/>
+      <c r="H369" s="24"/>
+      <c r="I369" s="24"/>
+      <c r="J369" s="24"/>
+      <c r="K369" s="24"/>
+    </row>
+    <row r="370" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A370" s="22"/>
+      <c r="B370" s="24"/>
+      <c r="C370" s="22"/>
+      <c r="D370" s="24"/>
+      <c r="E370" s="22"/>
+      <c r="F370" s="24"/>
+      <c r="G370" s="24"/>
+      <c r="H370" s="24"/>
+      <c r="I370" s="24"/>
+      <c r="J370" s="24"/>
+      <c r="K370" s="24"/>
+    </row>
+    <row r="371" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A371" s="20"/>
+      <c r="B371" s="21"/>
+      <c r="C371" s="20"/>
+      <c r="D371" s="21"/>
+      <c r="E371" s="20"/>
+      <c r="F371" s="21"/>
+      <c r="G371" s="21"/>
+      <c r="H371" s="21"/>
+      <c r="I371" s="21"/>
+      <c r="J371" s="21"/>
+      <c r="K371" s="21"/>
+    </row>
+    <row r="373" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A373" s="4">
         <v>14</v>
       </c>
-      <c r="B362" s="3" t="s">
+      <c r="B373" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="C362" s="4" t="s">
+      <c r="C373" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="D362" s="5" t="s">
+      <c r="D373" s="5" t="s">
         <v>691</v>
       </c>
-      <c r="E362" s="4"/>
-      <c r="F362" s="5"/>
-      <c r="G362" s="5"/>
-      <c r="H362" s="5"/>
-      <c r="I362" s="5"/>
-      <c r="J362" s="5"/>
-      <c r="K362" s="5"/>
-    </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A363" s="4"/>
-      <c r="B363" s="5"/>
-      <c r="C363" s="4" t="s">
+      <c r="E373" s="4"/>
+      <c r="F373" s="5"/>
+      <c r="G373" s="5"/>
+      <c r="H373" s="5"/>
+      <c r="I373" s="5"/>
+      <c r="J373" s="5"/>
+      <c r="K373" s="5"/>
+    </row>
+    <row r="374" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A374" s="4"/>
+      <c r="B374" s="5"/>
+      <c r="C374" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="D363" s="5" t="s">
+      <c r="D374" s="5" t="s">
         <v>692</v>
       </c>
-      <c r="E363" s="4"/>
-      <c r="F363" s="5"/>
-      <c r="G363" s="5"/>
-      <c r="H363" s="5"/>
-      <c r="I363" s="5"/>
-      <c r="J363" s="5"/>
-      <c r="K363" s="5"/>
-    </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A364" s="4"/>
-      <c r="B364" s="5"/>
-      <c r="C364" s="4" t="s">
+      <c r="E374" s="4"/>
+      <c r="F374" s="5"/>
+      <c r="G374" s="5"/>
+      <c r="H374" s="5"/>
+      <c r="I374" s="5"/>
+      <c r="J374" s="5"/>
+      <c r="K374" s="5"/>
+    </row>
+    <row r="375" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A375" s="4"/>
+      <c r="B375" s="5"/>
+      <c r="C375" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="D364" s="5" t="s">
+      <c r="D375" s="5" t="s">
         <v>694</v>
       </c>
-      <c r="E364" s="4"/>
-      <c r="F364" s="5"/>
-      <c r="G364" s="5"/>
-      <c r="H364" s="5"/>
-      <c r="I364" s="5"/>
-      <c r="J364" s="5"/>
-      <c r="K364" s="5"/>
-    </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A365" s="4"/>
-      <c r="B365" s="5"/>
-      <c r="C365" s="4" t="s">
+      <c r="E375" s="4"/>
+      <c r="F375" s="5"/>
+      <c r="G375" s="5"/>
+      <c r="H375" s="5"/>
+      <c r="I375" s="5"/>
+      <c r="J375" s="5"/>
+      <c r="K375" s="5"/>
+    </row>
+    <row r="376" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A376" s="4"/>
+      <c r="B376" s="5"/>
+      <c r="C376" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="D365" s="5" t="s">
+      <c r="D376" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="E365" s="4"/>
-      <c r="F365" s="5"/>
-      <c r="G365" s="5"/>
-      <c r="H365" s="5"/>
-      <c r="I365" s="5"/>
-      <c r="J365" s="5"/>
-      <c r="K365" s="5"/>
-    </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A366" s="4"/>
-      <c r="B366" s="5"/>
-      <c r="C366" s="4" t="s">
+      <c r="E376" s="4"/>
+      <c r="F376" s="5"/>
+      <c r="G376" s="5"/>
+      <c r="H376" s="5"/>
+      <c r="I376" s="5"/>
+      <c r="J376" s="5"/>
+      <c r="K376" s="5"/>
+    </row>
+    <row r="377" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A377" s="4"/>
+      <c r="B377" s="5"/>
+      <c r="C377" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="D366" s="5" t="s">
+      <c r="D377" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="E366" s="4"/>
-      <c r="F366" s="5"/>
-      <c r="G366" s="5"/>
-      <c r="H366" s="5"/>
-      <c r="I366" s="5"/>
-      <c r="J366" s="5"/>
-      <c r="K366" s="5"/>
-    </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A367" s="4"/>
-      <c r="B367" s="5"/>
-      <c r="C367" s="4" t="s">
+      <c r="E377" s="4"/>
+      <c r="F377" s="5"/>
+      <c r="G377" s="5"/>
+      <c r="H377" s="5"/>
+      <c r="I377" s="5"/>
+      <c r="J377" s="5"/>
+      <c r="K377" s="5"/>
+    </row>
+    <row r="378" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A378" s="4"/>
+      <c r="B378" s="5"/>
+      <c r="C378" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="D367" s="5" t="s">
+      <c r="D378" s="5" t="s">
         <v>700</v>
       </c>
-      <c r="E367" s="4"/>
-      <c r="F367" s="5"/>
-      <c r="G367" s="5"/>
-      <c r="H367" s="5"/>
-      <c r="I367" s="5"/>
-      <c r="J367" s="5"/>
-      <c r="K367" s="5"/>
-    </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A368" s="4"/>
-      <c r="B368" s="5"/>
-      <c r="C368" s="4" t="s">
+      <c r="E378" s="4"/>
+      <c r="F378" s="5"/>
+      <c r="G378" s="5"/>
+      <c r="H378" s="5"/>
+      <c r="I378" s="5"/>
+      <c r="J378" s="5"/>
+      <c r="K378" s="5"/>
+    </row>
+    <row r="379" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A379" s="4"/>
+      <c r="B379" s="5"/>
+      <c r="C379" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="D368" s="5" t="s">
+      <c r="D379" s="5" t="s">
         <v>702</v>
       </c>
-      <c r="E368" s="4"/>
-      <c r="F368" s="5"/>
-      <c r="G368" s="5"/>
-      <c r="H368" s="5"/>
-      <c r="I368" s="5"/>
-      <c r="J368" s="5"/>
-      <c r="K368" s="5"/>
-    </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A369" s="4"/>
-      <c r="B369" s="5"/>
-      <c r="C369" s="4"/>
-      <c r="D369" s="5"/>
-      <c r="E369" s="4"/>
-      <c r="F369" s="5"/>
-      <c r="G369" s="5"/>
-      <c r="H369" s="5"/>
-      <c r="I369" s="5"/>
-      <c r="J369" s="5"/>
-      <c r="K369" s="5"/>
-    </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A370" s="4"/>
-      <c r="B370" s="5"/>
-      <c r="C370" s="4"/>
-      <c r="D370" s="5"/>
-      <c r="E370" s="4"/>
-      <c r="F370" s="5"/>
-      <c r="G370" s="5"/>
-      <c r="H370" s="5"/>
-      <c r="I370" s="5"/>
-      <c r="J370" s="5"/>
-      <c r="K370" s="5"/>
-    </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A371" s="4"/>
-      <c r="B371" s="5"/>
-      <c r="C371" s="4"/>
-      <c r="D371" s="5"/>
-      <c r="E371" s="4"/>
-      <c r="F371" s="5"/>
-      <c r="G371" s="5"/>
-      <c r="H371" s="5"/>
-      <c r="I371" s="5"/>
-      <c r="J371" s="5"/>
-      <c r="K371" s="5"/>
-    </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A372" s="4"/>
-      <c r="B372" s="5"/>
-      <c r="C372" s="4"/>
-      <c r="D372" s="5"/>
-      <c r="E372" s="4"/>
-      <c r="F372" s="5"/>
-      <c r="G372" s="5"/>
-      <c r="H372" s="5"/>
-      <c r="I372" s="5"/>
-      <c r="J372" s="5"/>
-      <c r="K372" s="5"/>
-    </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C374" s="1" t="s">
+      <c r="E379" s="4"/>
+      <c r="F379" s="5"/>
+      <c r="G379" s="5"/>
+      <c r="H379" s="5"/>
+      <c r="I379" s="5"/>
+      <c r="J379" s="5"/>
+      <c r="K379" s="5"/>
+    </row>
+    <row r="380" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A380" s="4"/>
+      <c r="B380" s="5"/>
+      <c r="C380" s="4"/>
+      <c r="D380" s="5"/>
+      <c r="E380" s="4"/>
+      <c r="F380" s="5"/>
+      <c r="G380" s="5"/>
+      <c r="H380" s="5"/>
+      <c r="I380" s="5"/>
+      <c r="J380" s="5"/>
+      <c r="K380" s="5"/>
+    </row>
+    <row r="381" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A381" s="4"/>
+      <c r="B381" s="5"/>
+      <c r="C381" s="4"/>
+      <c r="D381" s="5"/>
+      <c r="E381" s="4"/>
+      <c r="F381" s="5"/>
+      <c r="G381" s="5"/>
+      <c r="H381" s="5"/>
+      <c r="I381" s="5"/>
+      <c r="J381" s="5"/>
+      <c r="K381" s="5"/>
+    </row>
+    <row r="382" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A382" s="4"/>
+      <c r="B382" s="5"/>
+      <c r="C382" s="4"/>
+      <c r="D382" s="5"/>
+      <c r="E382" s="4"/>
+      <c r="F382" s="5"/>
+      <c r="G382" s="5"/>
+      <c r="H382" s="5"/>
+      <c r="I382" s="5"/>
+      <c r="J382" s="5"/>
+      <c r="K382" s="5"/>
+    </row>
+    <row r="383" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A383" s="4"/>
+      <c r="B383" s="5"/>
+      <c r="C383" s="4"/>
+      <c r="D383" s="5"/>
+      <c r="E383" s="4"/>
+      <c r="F383" s="5"/>
+      <c r="G383" s="5"/>
+      <c r="H383" s="5"/>
+      <c r="I383" s="5"/>
+      <c r="J383" s="5"/>
+      <c r="K383" s="5"/>
+    </row>
+    <row r="385" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C385" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C375" s="1" t="s">
+    <row r="386" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C386" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D375" t="s">
+      <c r="D386" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C376" s="1" t="s">
+    <row r="387" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C387" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="D376" t="s">
+      <c r="D387" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C377" s="1" t="s">
+    <row r="388" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C388" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D377" t="s">
+      <c r="D388" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C378" s="1" t="s">
+    <row r="389" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C389" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D378" t="s">
+      <c r="D389" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C379" s="1" t="s">
+    <row r="390" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C390" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D379" t="s">
+      <c r="D390" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C380" s="1" t="s">
+    <row r="391" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C391" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="D380" t="s">
+      <c r="D391" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C381" s="1" t="s">
+    <row r="392" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C392" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="D381" t="s">
+      <c r="D392" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C382" s="1" t="s">
+    <row r="393" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C393" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="D382" t="s">
+      <c r="D393" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C383" s="1" t="s">
+    <row r="394" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C394" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="D383" t="s">
+      <c r="D394" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C384" s="1" t="s">
+    <row r="395" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C395" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D384" t="s">
+      <c r="D395" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C385" s="1" t="s">
+    <row r="396" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C396" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="D385" t="s">
+      <c r="D396" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C386" s="1" t="s">
+    <row r="397" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C397" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="D386" t="s">
+      <c r="D397" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C387" s="1" t="s">
+    <row r="398" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C398" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D387" t="s">
+      <c r="D398" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C388" s="1" t="s">
+    <row r="399" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C399" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="D388" t="s">
+      <c r="D399" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C389" s="1" t="s">
+    <row r="400" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C400" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D389" t="s">
+      <c r="D400" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C390" s="1" t="s">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C401" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="D390" t="s">
+      <c r="D401" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C391" s="1" t="s">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C402" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="D391" t="s">
+      <c r="D402" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C392" s="1" t="s">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C403" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="D392" t="s">
+      <c r="D403" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="D393" t="s">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D404" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A394" s="26"/>
-      <c r="B394" s="25"/>
-      <c r="C394" s="26"/>
-      <c r="D394" s="25"/>
-      <c r="E394" s="26"/>
-      <c r="F394" s="25"/>
-      <c r="G394" s="25"/>
-      <c r="H394" s="25"/>
-      <c r="I394" s="25"/>
-      <c r="J394" s="25"/>
-      <c r="K394" s="25"/>
-    </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A395" s="39">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A405" s="26"/>
+      <c r="B405" s="25"/>
+      <c r="C405" s="26"/>
+      <c r="D405" s="25"/>
+      <c r="E405" s="26"/>
+      <c r="F405" s="25"/>
+      <c r="G405" s="25"/>
+      <c r="H405" s="25"/>
+      <c r="I405" s="25"/>
+      <c r="J405" s="25"/>
+      <c r="K405" s="25"/>
+    </row>
+    <row r="406" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A406" s="39">
         <v>16</v>
       </c>
-      <c r="B395" s="40" t="s">
+      <c r="B406" s="40" t="s">
         <v>385</v>
       </c>
-      <c r="C395" s="41" t="s">
+      <c r="C406" s="41" t="s">
         <v>337</v>
       </c>
-      <c r="D395" s="42" t="s">
+      <c r="D406" s="42" t="s">
         <v>349</v>
       </c>
-      <c r="E395" s="39" t="s">
+      <c r="E406" s="39" t="s">
         <v>565</v>
       </c>
-      <c r="F395" s="42" t="s">
+      <c r="F406" s="42" t="s">
         <v>385</v>
       </c>
-      <c r="G395" s="42"/>
-      <c r="H395" s="42"/>
-      <c r="I395" s="42"/>
-      <c r="J395" s="42"/>
-      <c r="K395" s="42"/>
-    </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A396" s="39"/>
-      <c r="B396" s="42"/>
-      <c r="C396" s="41" t="s">
-        <v>338</v>
-      </c>
-      <c r="D396" s="42" t="s">
-        <v>350</v>
-      </c>
-      <c r="E396" s="39"/>
-      <c r="F396" s="42"/>
-      <c r="G396" s="42"/>
-      <c r="H396" s="42"/>
-      <c r="I396" s="42"/>
-      <c r="J396" s="42"/>
-      <c r="K396" s="42"/>
-    </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A397" s="39"/>
-      <c r="B397" s="42"/>
-      <c r="C397" s="41" t="s">
-        <v>339</v>
-      </c>
-      <c r="D397" s="42" t="s">
-        <v>351</v>
-      </c>
-      <c r="E397" s="39"/>
-      <c r="F397" s="42"/>
-      <c r="G397" s="42"/>
-      <c r="H397" s="42"/>
-      <c r="I397" s="42"/>
-      <c r="J397" s="42"/>
-      <c r="K397" s="42"/>
-    </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A398" s="39"/>
-      <c r="B398" s="42"/>
-      <c r="C398" s="41" t="s">
-        <v>340</v>
-      </c>
-      <c r="D398" s="42" t="s">
-        <v>352</v>
-      </c>
-      <c r="E398" s="39"/>
-      <c r="F398" s="42"/>
-      <c r="G398" s="42"/>
-      <c r="H398" s="42"/>
-      <c r="I398" s="42"/>
-      <c r="J398" s="42"/>
-      <c r="K398" s="42"/>
-    </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A399" s="39"/>
-      <c r="B399" s="42"/>
-      <c r="C399" s="41" t="s">
-        <v>341</v>
-      </c>
-      <c r="D399" s="42" t="s">
-        <v>353</v>
-      </c>
-      <c r="E399" s="39"/>
-      <c r="F399" s="42"/>
-      <c r="G399" s="42"/>
-      <c r="H399" s="42"/>
-      <c r="I399" s="42"/>
-      <c r="J399" s="42"/>
-      <c r="K399" s="42"/>
-    </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A400" s="39"/>
-      <c r="B400" s="42"/>
-      <c r="C400" s="41" t="s">
-        <v>342</v>
-      </c>
-      <c r="D400" s="42" t="s">
-        <v>354</v>
-      </c>
-      <c r="E400" s="39"/>
-      <c r="F400" s="42"/>
-      <c r="G400" s="42"/>
-      <c r="H400" s="42"/>
-      <c r="I400" s="42"/>
-      <c r="J400" s="42"/>
-      <c r="K400" s="42"/>
-    </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A401" s="39"/>
-      <c r="B401" s="42"/>
-      <c r="C401" s="41" t="s">
-        <v>343</v>
-      </c>
-      <c r="D401" s="42" t="s">
-        <v>355</v>
-      </c>
-      <c r="E401" s="39"/>
-      <c r="F401" s="42"/>
-      <c r="G401" s="42"/>
-      <c r="H401" s="42"/>
-      <c r="I401" s="42"/>
-      <c r="J401" s="42"/>
-      <c r="K401" s="42"/>
-    </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A402" s="39"/>
-      <c r="B402" s="42"/>
-      <c r="C402" s="41" t="s">
-        <v>344</v>
-      </c>
-      <c r="D402" s="42" t="s">
-        <v>356</v>
-      </c>
-      <c r="E402" s="39"/>
-      <c r="F402" s="42"/>
-      <c r="G402" s="42"/>
-      <c r="H402" s="42"/>
-      <c r="I402" s="42"/>
-      <c r="J402" s="42"/>
-      <c r="K402" s="42"/>
-    </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A403" s="39"/>
-      <c r="B403" s="42"/>
-      <c r="C403" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="D403" s="42" t="s">
-        <v>357</v>
-      </c>
-      <c r="E403" s="39"/>
-      <c r="F403" s="42"/>
-      <c r="G403" s="42"/>
-      <c r="H403" s="42"/>
-      <c r="I403" s="42"/>
-      <c r="J403" s="42"/>
-      <c r="K403" s="42"/>
-    </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A404" s="39"/>
-      <c r="B404" s="42"/>
-      <c r="C404" s="41" t="s">
-        <v>346</v>
-      </c>
-      <c r="D404" s="42" t="s">
-        <v>359</v>
-      </c>
-      <c r="E404" s="39"/>
-      <c r="F404" s="42"/>
-      <c r="G404" s="42"/>
-      <c r="H404" s="42"/>
-      <c r="I404" s="42"/>
-      <c r="J404" s="42"/>
-      <c r="K404" s="42"/>
-    </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A405" s="39"/>
-      <c r="B405" s="42"/>
-      <c r="C405" s="41" t="s">
-        <v>347</v>
-      </c>
-      <c r="D405" s="42" t="s">
-        <v>358</v>
-      </c>
-      <c r="E405" s="39"/>
-      <c r="F405" s="42"/>
-      <c r="G405" s="42"/>
-      <c r="H405" s="42"/>
-      <c r="I405" s="42"/>
-      <c r="J405" s="42"/>
-      <c r="K405" s="42"/>
-    </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A406" s="39"/>
-      <c r="B406" s="42"/>
-      <c r="C406" s="41" t="s">
-        <v>348</v>
-      </c>
-      <c r="D406" s="42" t="s">
-        <v>360</v>
-      </c>
-      <c r="E406" s="39"/>
-      <c r="F406" s="42"/>
       <c r="G406" s="42"/>
       <c r="H406" s="42"/>
       <c r="I406" s="42"/>
@@ -8008,10 +8026,10 @@
       <c r="A407" s="39"/>
       <c r="B407" s="42"/>
       <c r="C407" s="41" t="s">
-        <v>372</v>
+        <v>338</v>
       </c>
       <c r="D407" s="42" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="E407" s="39"/>
       <c r="F407" s="42"/>
@@ -8025,10 +8043,10 @@
       <c r="A408" s="39"/>
       <c r="B408" s="42"/>
       <c r="C408" s="41" t="s">
-        <v>373</v>
+        <v>339</v>
       </c>
       <c r="D408" s="42" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="E408" s="39"/>
       <c r="F408" s="42"/>
@@ -8042,10 +8060,10 @@
       <c r="A409" s="39"/>
       <c r="B409" s="42"/>
       <c r="C409" s="41" t="s">
-        <v>374</v>
+        <v>340</v>
       </c>
       <c r="D409" s="42" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="E409" s="39"/>
       <c r="F409" s="42"/>
@@ -8059,10 +8077,10 @@
       <c r="A410" s="39"/>
       <c r="B410" s="42"/>
       <c r="C410" s="41" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="D410" s="42" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="E410" s="39"/>
       <c r="F410" s="42"/>
@@ -8076,10 +8094,10 @@
       <c r="A411" s="39"/>
       <c r="B411" s="42"/>
       <c r="C411" s="41" t="s">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="D411" s="42" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="E411" s="39"/>
       <c r="F411" s="42"/>
@@ -8093,10 +8111,10 @@
       <c r="A412" s="39"/>
       <c r="B412" s="42"/>
       <c r="C412" s="41" t="s">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="D412" s="42" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="E412" s="39"/>
       <c r="F412" s="42"/>
@@ -8110,10 +8128,10 @@
       <c r="A413" s="39"/>
       <c r="B413" s="42"/>
       <c r="C413" s="41" t="s">
-        <v>378</v>
+        <v>344</v>
       </c>
       <c r="D413" s="42" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="E413" s="39"/>
       <c r="F413" s="42"/>
@@ -8127,10 +8145,10 @@
       <c r="A414" s="39"/>
       <c r="B414" s="42"/>
       <c r="C414" s="41" t="s">
-        <v>379</v>
+        <v>345</v>
       </c>
       <c r="D414" s="42" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="E414" s="39"/>
       <c r="F414" s="42"/>
@@ -8144,10 +8162,10 @@
       <c r="A415" s="39"/>
       <c r="B415" s="42"/>
       <c r="C415" s="41" t="s">
-        <v>380</v>
+        <v>346</v>
       </c>
       <c r="D415" s="42" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="E415" s="39"/>
       <c r="F415" s="42"/>
@@ -8161,10 +8179,10 @@
       <c r="A416" s="39"/>
       <c r="B416" s="42"/>
       <c r="C416" s="41" t="s">
-        <v>381</v>
+        <v>347</v>
       </c>
       <c r="D416" s="42" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="E416" s="39"/>
       <c r="F416" s="42"/>
@@ -8178,10 +8196,10 @@
       <c r="A417" s="39"/>
       <c r="B417" s="42"/>
       <c r="C417" s="41" t="s">
-        <v>382</v>
+        <v>348</v>
       </c>
       <c r="D417" s="42" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="E417" s="39"/>
       <c r="F417" s="42"/>
@@ -8195,10 +8213,10 @@
       <c r="A418" s="39"/>
       <c r="B418" s="42"/>
       <c r="C418" s="41" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="D418" s="42" t="s">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="E418" s="39"/>
       <c r="F418" s="42"/>
@@ -8209,406 +8227,593 @@
       <c r="K418" s="42"/>
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A419" s="26"/>
-      <c r="B419" s="25"/>
-      <c r="C419" s="26"/>
-      <c r="D419" s="25"/>
-      <c r="E419" s="26"/>
-      <c r="F419" s="25"/>
-      <c r="G419" s="25"/>
-      <c r="H419" s="25"/>
-      <c r="I419" s="25"/>
-      <c r="J419" s="25"/>
-      <c r="K419" s="25"/>
+      <c r="A419" s="39"/>
+      <c r="B419" s="42"/>
+      <c r="C419" s="41" t="s">
+        <v>373</v>
+      </c>
+      <c r="D419" s="42" t="s">
+        <v>362</v>
+      </c>
+      <c r="E419" s="39"/>
+      <c r="F419" s="42"/>
+      <c r="G419" s="42"/>
+      <c r="H419" s="42"/>
+      <c r="I419" s="42"/>
+      <c r="J419" s="42"/>
+      <c r="K419" s="42"/>
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A420" s="32"/>
-      <c r="B420" s="33" t="s">
+      <c r="A420" s="39"/>
+      <c r="B420" s="42"/>
+      <c r="C420" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="D420" s="42" t="s">
+        <v>363</v>
+      </c>
+      <c r="E420" s="39"/>
+      <c r="F420" s="42"/>
+      <c r="G420" s="42"/>
+      <c r="H420" s="42"/>
+      <c r="I420" s="42"/>
+      <c r="J420" s="42"/>
+      <c r="K420" s="42"/>
+    </row>
+    <row r="421" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A421" s="39"/>
+      <c r="B421" s="42"/>
+      <c r="C421" s="41" t="s">
+        <v>375</v>
+      </c>
+      <c r="D421" s="42" t="s">
+        <v>364</v>
+      </c>
+      <c r="E421" s="39"/>
+      <c r="F421" s="42"/>
+      <c r="G421" s="42"/>
+      <c r="H421" s="42"/>
+      <c r="I421" s="42"/>
+      <c r="J421" s="42"/>
+      <c r="K421" s="42"/>
+    </row>
+    <row r="422" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A422" s="39"/>
+      <c r="B422" s="42"/>
+      <c r="C422" s="41" t="s">
+        <v>376</v>
+      </c>
+      <c r="D422" s="42" t="s">
+        <v>365</v>
+      </c>
+      <c r="E422" s="39"/>
+      <c r="F422" s="42"/>
+      <c r="G422" s="42"/>
+      <c r="H422" s="42"/>
+      <c r="I422" s="42"/>
+      <c r="J422" s="42"/>
+      <c r="K422" s="42"/>
+    </row>
+    <row r="423" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A423" s="39"/>
+      <c r="B423" s="42"/>
+      <c r="C423" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="D423" s="42" t="s">
+        <v>366</v>
+      </c>
+      <c r="E423" s="39"/>
+      <c r="F423" s="42"/>
+      <c r="G423" s="42"/>
+      <c r="H423" s="42"/>
+      <c r="I423" s="42"/>
+      <c r="J423" s="42"/>
+      <c r="K423" s="42"/>
+    </row>
+    <row r="424" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A424" s="39"/>
+      <c r="B424" s="42"/>
+      <c r="C424" s="41" t="s">
+        <v>378</v>
+      </c>
+      <c r="D424" s="42" t="s">
+        <v>367</v>
+      </c>
+      <c r="E424" s="39"/>
+      <c r="F424" s="42"/>
+      <c r="G424" s="42"/>
+      <c r="H424" s="42"/>
+      <c r="I424" s="42"/>
+      <c r="J424" s="42"/>
+      <c r="K424" s="42"/>
+    </row>
+    <row r="425" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A425" s="39"/>
+      <c r="B425" s="42"/>
+      <c r="C425" s="41" t="s">
+        <v>379</v>
+      </c>
+      <c r="D425" s="42" t="s">
+        <v>368</v>
+      </c>
+      <c r="E425" s="39"/>
+      <c r="F425" s="42"/>
+      <c r="G425" s="42"/>
+      <c r="H425" s="42"/>
+      <c r="I425" s="42"/>
+      <c r="J425" s="42"/>
+      <c r="K425" s="42"/>
+    </row>
+    <row r="426" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A426" s="39"/>
+      <c r="B426" s="42"/>
+      <c r="C426" s="41" t="s">
+        <v>380</v>
+      </c>
+      <c r="D426" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="E426" s="39"/>
+      <c r="F426" s="42"/>
+      <c r="G426" s="42"/>
+      <c r="H426" s="42"/>
+      <c r="I426" s="42"/>
+      <c r="J426" s="42"/>
+      <c r="K426" s="42"/>
+    </row>
+    <row r="427" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A427" s="39"/>
+      <c r="B427" s="42"/>
+      <c r="C427" s="41" t="s">
+        <v>381</v>
+      </c>
+      <c r="D427" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="E427" s="39"/>
+      <c r="F427" s="42"/>
+      <c r="G427" s="42"/>
+      <c r="H427" s="42"/>
+      <c r="I427" s="42"/>
+      <c r="J427" s="42"/>
+      <c r="K427" s="42"/>
+    </row>
+    <row r="428" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A428" s="39"/>
+      <c r="B428" s="42"/>
+      <c r="C428" s="41" t="s">
+        <v>382</v>
+      </c>
+      <c r="D428" s="42" t="s">
+        <v>371</v>
+      </c>
+      <c r="E428" s="39"/>
+      <c r="F428" s="42"/>
+      <c r="G428" s="42"/>
+      <c r="H428" s="42"/>
+      <c r="I428" s="42"/>
+      <c r="J428" s="42"/>
+      <c r="K428" s="42"/>
+    </row>
+    <row r="429" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A429" s="39"/>
+      <c r="B429" s="42"/>
+      <c r="C429" s="41" t="s">
+        <v>383</v>
+      </c>
+      <c r="D429" s="42" t="s">
+        <v>384</v>
+      </c>
+      <c r="E429" s="39"/>
+      <c r="F429" s="42"/>
+      <c r="G429" s="42"/>
+      <c r="H429" s="42"/>
+      <c r="I429" s="42"/>
+      <c r="J429" s="42"/>
+      <c r="K429" s="42"/>
+    </row>
+    <row r="430" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A430" s="26"/>
+      <c r="B430" s="25"/>
+      <c r="C430" s="26"/>
+      <c r="D430" s="25"/>
+      <c r="E430" s="26"/>
+      <c r="F430" s="25"/>
+      <c r="G430" s="25"/>
+      <c r="H430" s="25"/>
+      <c r="I430" s="25"/>
+      <c r="J430" s="25"/>
+      <c r="K430" s="25"/>
+    </row>
+    <row r="431" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A431" s="32"/>
+      <c r="B431" s="33" t="s">
         <v>424</v>
       </c>
-      <c r="C420" s="32" t="s">
+      <c r="C431" s="32" t="s">
         <v>425</v>
       </c>
-      <c r="D420" s="38" t="s">
+      <c r="D431" s="38" t="s">
         <v>426</v>
       </c>
-      <c r="E420" s="32"/>
-      <c r="F420" s="33"/>
-      <c r="G420" s="33"/>
-    </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A421" s="4"/>
-      <c r="B421" s="5"/>
-      <c r="C421" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="D421" s="18" t="s">
-        <v>428</v>
-      </c>
-      <c r="E421" s="4"/>
-      <c r="F421" s="5"/>
-      <c r="G421" s="5"/>
-    </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A423" s="4"/>
-      <c r="B423" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="C423" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="D423" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="E423" s="4"/>
-      <c r="F423" s="5"/>
-      <c r="G423" s="5"/>
-    </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A424" s="4"/>
-      <c r="B424" s="5"/>
-      <c r="C424" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="D424" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="E424" s="4"/>
-      <c r="F424" s="5"/>
-      <c r="G424" s="5"/>
-    </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A425" s="4"/>
-      <c r="B425" s="5"/>
-      <c r="C425" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="D425" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="E425" s="4"/>
-      <c r="F425" s="5"/>
-      <c r="G425" s="5"/>
-    </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A426" s="4"/>
-      <c r="B426" s="5"/>
-      <c r="C426" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="D426" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="E426" s="4"/>
-      <c r="F426" s="5"/>
-      <c r="G426" s="5"/>
-    </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A427" s="4"/>
-      <c r="B427" s="5"/>
-      <c r="C427" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="D427" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="E427" s="4"/>
-      <c r="F427" s="5"/>
-      <c r="G427" s="5"/>
-    </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A428" s="4"/>
-      <c r="B428" s="5"/>
-      <c r="C428" s="4"/>
-      <c r="D428" s="5"/>
-      <c r="E428" s="4"/>
-      <c r="F428" s="5"/>
-      <c r="G428" s="5"/>
-    </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A429" s="4"/>
-      <c r="B429" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="C429" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="D429" s="16" t="s">
-        <v>450</v>
-      </c>
-      <c r="E429" s="4"/>
-      <c r="F429" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="G429" s="5"/>
-    </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A430" s="4"/>
-      <c r="B430" s="5"/>
-      <c r="C430" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="D430" s="16" t="s">
-        <v>451</v>
-      </c>
-      <c r="E430" s="4"/>
-      <c r="F430" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="G430" s="5"/>
-    </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A431" s="4"/>
-      <c r="B431" s="5"/>
-      <c r="C431" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="D431" s="16" t="s">
-        <v>452</v>
-      </c>
-      <c r="E431" s="4"/>
-      <c r="F431" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="G431" s="5"/>
+      <c r="E431" s="32"/>
+      <c r="F431" s="33"/>
+      <c r="G431" s="33"/>
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A432" s="4"/>
       <c r="B432" s="5"/>
       <c r="C432" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D432" s="16" t="s">
-        <v>454</v>
+        <v>427</v>
+      </c>
+      <c r="D432" s="18" t="s">
+        <v>428</v>
       </c>
       <c r="E432" s="4"/>
-      <c r="F432" s="5" t="s">
-        <v>453</v>
-      </c>
+      <c r="F432" s="5"/>
       <c r="G432" s="5"/>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A433" s="4"/>
-      <c r="B433" s="5"/>
-      <c r="C433" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="D433" s="16" t="s">
-        <v>440</v>
-      </c>
-      <c r="E433" s="4"/>
-      <c r="F433" s="5"/>
-      <c r="G433" s="5"/>
-    </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A434" s="4"/>
-      <c r="B434" s="5"/>
-      <c r="C434" s="4"/>
-      <c r="D434" s="5"/>
+      <c r="B434" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="C434" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D434" s="16" t="s">
+        <v>429</v>
+      </c>
       <c r="E434" s="4"/>
       <c r="F434" s="5"/>
       <c r="G434" s="5"/>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A435" s="4"/>
-      <c r="B435" s="5" t="s">
-        <v>441</v>
-      </c>
+      <c r="B435" s="5"/>
       <c r="C435" s="4" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="D435" s="16" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="E435" s="4"/>
       <c r="F435" s="5"/>
       <c r="G435" s="5"/>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A436" s="4"/>
       <c r="B436" s="5"/>
       <c r="C436" s="4" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="D436" s="16" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="E436" s="4"/>
       <c r="F436" s="5"/>
       <c r="G436" s="5"/>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A437" s="4"/>
       <c r="B437" s="5"/>
       <c r="C437" s="4" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="D437" s="16" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="E437" s="4"/>
       <c r="F437" s="5"/>
       <c r="G437" s="5"/>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A438" s="4"/>
       <c r="B438" s="5"/>
       <c r="C438" s="4" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="D438" s="16" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="E438" s="4"/>
       <c r="F438" s="5"/>
       <c r="G438" s="5"/>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A439" s="4"/>
       <c r="B439" s="5"/>
-      <c r="C439" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="D439" s="16" t="s">
-        <v>446</v>
-      </c>
+      <c r="C439" s="4"/>
+      <c r="D439" s="5"/>
       <c r="E439" s="4"/>
       <c r="F439" s="5"/>
       <c r="G439" s="5"/>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A442" s="43">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A440" s="4"/>
+      <c r="B440" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C440" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="D440" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="E440" s="4"/>
+      <c r="F440" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="G440" s="5"/>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A441" s="4"/>
+      <c r="B441" s="5"/>
+      <c r="C441" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="D441" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="E441" s="4"/>
+      <c r="F441" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="G441" s="5"/>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A442" s="4"/>
+      <c r="B442" s="5"/>
+      <c r="C442" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D442" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="E442" s="4"/>
+      <c r="F442" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="G442" s="5"/>
+    </row>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A443" s="4"/>
+      <c r="B443" s="5"/>
+      <c r="C443" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D443" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="E443" s="4"/>
+      <c r="F443" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="G443" s="5"/>
+    </row>
+    <row r="444" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A444" s="4"/>
+      <c r="B444" s="5"/>
+      <c r="C444" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="D444" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="E444" s="4"/>
+      <c r="F444" s="5"/>
+      <c r="G444" s="5"/>
+    </row>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A445" s="4"/>
+      <c r="B445" s="5"/>
+      <c r="C445" s="4"/>
+      <c r="D445" s="5"/>
+      <c r="E445" s="4"/>
+      <c r="F445" s="5"/>
+      <c r="G445" s="5"/>
+    </row>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A446" s="4"/>
+      <c r="B446" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="C446" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="D446" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="E446" s="4"/>
+      <c r="F446" s="5"/>
+      <c r="G446" s="5"/>
+    </row>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A447" s="4"/>
+      <c r="B447" s="5"/>
+      <c r="C447" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="D447" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="E447" s="4"/>
+      <c r="F447" s="5"/>
+      <c r="G447" s="5"/>
+    </row>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A448" s="4"/>
+      <c r="B448" s="5"/>
+      <c r="C448" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="D448" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="E448" s="4"/>
+      <c r="F448" s="5"/>
+      <c r="G448" s="5"/>
+    </row>
+    <row r="449" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A449" s="4"/>
+      <c r="B449" s="5"/>
+      <c r="C449" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="D449" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="E449" s="4"/>
+      <c r="F449" s="5"/>
+      <c r="G449" s="5"/>
+    </row>
+    <row r="450" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A450" s="4"/>
+      <c r="B450" s="5"/>
+      <c r="C450" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D450" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="E450" s="4"/>
+      <c r="F450" s="5"/>
+      <c r="G450" s="5"/>
+    </row>
+    <row r="453" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A453" s="43">
         <v>19</v>
       </c>
-      <c r="B442" s="50" t="s">
+      <c r="B453" s="50" t="s">
         <v>716</v>
       </c>
-      <c r="C442" s="43" t="s">
+      <c r="C453" s="43" t="s">
         <v>726</v>
       </c>
-      <c r="D442" s="44" t="s">
+      <c r="D453" s="44" t="s">
         <v>727</v>
       </c>
-      <c r="E442" s="43"/>
-      <c r="F442" s="44"/>
-      <c r="G442" s="44"/>
-      <c r="H442" s="44"/>
-      <c r="I442" s="44"/>
-      <c r="J442" s="44"/>
-      <c r="K442" s="44"/>
-    </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A443" s="43"/>
-      <c r="B443" s="44"/>
-      <c r="C443" s="43" t="s">
+      <c r="E453" s="43"/>
+      <c r="F453" s="44"/>
+      <c r="G453" s="44"/>
+      <c r="H453" s="44"/>
+      <c r="I453" s="44"/>
+      <c r="J453" s="44"/>
+      <c r="K453" s="44"/>
+    </row>
+    <row r="454" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A454" s="43"/>
+      <c r="B454" s="44"/>
+      <c r="C454" s="43" t="s">
         <v>717</v>
       </c>
-      <c r="D443" s="45" t="s">
+      <c r="D454" s="45" t="s">
         <v>718</v>
       </c>
-      <c r="E443" s="43"/>
-      <c r="F443" s="44"/>
-      <c r="G443" s="44"/>
-      <c r="H443" s="44"/>
-      <c r="I443" s="44"/>
-      <c r="J443" s="44"/>
-      <c r="K443" s="44"/>
-    </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A444" s="43"/>
-      <c r="B444" s="44"/>
-      <c r="C444" s="43" t="s">
+      <c r="E454" s="43"/>
+      <c r="F454" s="44"/>
+      <c r="G454" s="44"/>
+      <c r="H454" s="44"/>
+      <c r="I454" s="44"/>
+      <c r="J454" s="44"/>
+      <c r="K454" s="44"/>
+    </row>
+    <row r="455" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A455" s="43"/>
+      <c r="B455" s="44"/>
+      <c r="C455" s="43" t="s">
         <v>728</v>
       </c>
-      <c r="D444" s="44" t="s">
+      <c r="D455" s="44" t="s">
         <v>729</v>
       </c>
-      <c r="E444" s="43"/>
-      <c r="F444" s="44"/>
-      <c r="G444" s="44"/>
-      <c r="H444" s="44"/>
-      <c r="I444" s="44"/>
-      <c r="J444" s="44"/>
-      <c r="K444" s="44"/>
-    </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A445" s="43"/>
-      <c r="B445" s="44"/>
-      <c r="C445" s="43" t="s">
+      <c r="E455" s="43"/>
+      <c r="F455" s="44"/>
+      <c r="G455" s="44"/>
+      <c r="H455" s="44"/>
+      <c r="I455" s="44"/>
+      <c r="J455" s="44"/>
+      <c r="K455" s="44"/>
+    </row>
+    <row r="456" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A456" s="43"/>
+      <c r="B456" s="44"/>
+      <c r="C456" s="43" t="s">
         <v>719</v>
       </c>
-      <c r="D445" s="44"/>
-      <c r="E445" s="43"/>
-      <c r="F445" s="44"/>
-      <c r="G445" s="44"/>
-      <c r="H445" s="44"/>
-      <c r="I445" s="44"/>
-      <c r="J445" s="44"/>
-      <c r="K445" s="44"/>
-    </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A446" s="43"/>
-      <c r="B446" s="44"/>
-      <c r="C446" s="43" t="s">
+      <c r="D456" s="44"/>
+      <c r="E456" s="43"/>
+      <c r="F456" s="44"/>
+      <c r="G456" s="44"/>
+      <c r="H456" s="44"/>
+      <c r="I456" s="44"/>
+      <c r="J456" s="44"/>
+      <c r="K456" s="44"/>
+    </row>
+    <row r="457" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A457" s="43"/>
+      <c r="B457" s="44"/>
+      <c r="C457" s="43" t="s">
         <v>720</v>
       </c>
-      <c r="D446" s="44" t="s">
+      <c r="D457" s="44" t="s">
         <v>723</v>
       </c>
-      <c r="E446" s="43"/>
-      <c r="F446" s="44"/>
-      <c r="G446" s="44"/>
-      <c r="H446" s="44"/>
-      <c r="I446" s="44"/>
-      <c r="J446" s="44"/>
-      <c r="K446" s="44"/>
-    </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A447" s="43"/>
-      <c r="B447" s="44"/>
-      <c r="C447" s="43" t="s">
+      <c r="E457" s="43"/>
+      <c r="F457" s="44"/>
+      <c r="G457" s="44"/>
+      <c r="H457" s="44"/>
+      <c r="I457" s="44"/>
+      <c r="J457" s="44"/>
+      <c r="K457" s="44"/>
+    </row>
+    <row r="458" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A458" s="43"/>
+      <c r="B458" s="44"/>
+      <c r="C458" s="43" t="s">
         <v>725</v>
       </c>
-      <c r="D447" s="44" t="s">
+      <c r="D458" s="44" t="s">
         <v>724</v>
       </c>
-      <c r="E447" s="43"/>
-      <c r="F447" s="44"/>
-      <c r="G447" s="44"/>
-      <c r="H447" s="44"/>
-      <c r="I447" s="44"/>
-      <c r="J447" s="44"/>
-      <c r="K447" s="44"/>
-    </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A448" s="43"/>
-      <c r="B448" s="44"/>
-      <c r="C448" s="43" t="s">
+      <c r="E458" s="43"/>
+      <c r="F458" s="44"/>
+      <c r="G458" s="44"/>
+      <c r="H458" s="44"/>
+      <c r="I458" s="44"/>
+      <c r="J458" s="44"/>
+      <c r="K458" s="44"/>
+    </row>
+    <row r="459" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A459" s="43"/>
+      <c r="B459" s="44"/>
+      <c r="C459" s="43" t="s">
         <v>721</v>
       </c>
-      <c r="D448" s="44" t="s">
+      <c r="D459" s="44" t="s">
         <v>722</v>
       </c>
-      <c r="E448" s="43"/>
-      <c r="F448" s="44"/>
-      <c r="G448" s="44"/>
-      <c r="H448" s="44"/>
-      <c r="I448" s="44"/>
-      <c r="J448" s="44"/>
-      <c r="K448" s="44"/>
-    </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A449" s="43"/>
-      <c r="B449" s="44"/>
-      <c r="C449" s="43"/>
-      <c r="D449" s="44"/>
-      <c r="E449" s="43"/>
-      <c r="F449" s="44"/>
-      <c r="G449" s="44"/>
-      <c r="H449" s="44"/>
-      <c r="I449" s="44"/>
-      <c r="J449" s="44"/>
-      <c r="K449" s="44"/>
+      <c r="E459" s="43"/>
+      <c r="F459" s="44"/>
+      <c r="G459" s="44"/>
+      <c r="H459" s="44"/>
+      <c r="I459" s="44"/>
+      <c r="J459" s="44"/>
+      <c r="K459" s="44"/>
+    </row>
+    <row r="460" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A460" s="43"/>
+      <c r="B460" s="44"/>
+      <c r="C460" s="43"/>
+      <c r="D460" s="44"/>
+      <c r="E460" s="43"/>
+      <c r="F460" s="44"/>
+      <c r="G460" s="44"/>
+      <c r="H460" s="44"/>
+      <c r="I460" s="44"/>
+      <c r="J460" s="44"/>
+      <c r="K460" s="44"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Images for Markdown files database .xlsx
+++ b/Images for Markdown files database .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trevor\Compac Industries\Compac - General\IT\ChatBot\Markdown-Manuals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7C4140-385F-4A19-99B1-086C1C443892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EF3970-6AE4-4608-95C7-86A6CCF26CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-1320" windowWidth="38640" windowHeight="21120" xr2:uid="{7323B22B-375C-41F7-91CD-F86C900FC6DE}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="892">
   <si>
     <t xml:space="preserve">PCBs </t>
   </si>
@@ -2685,6 +2685,42 @@
   </si>
   <si>
     <t>1.6.6_Terminals_MMR400_160S _ Avi_2x_C5K.png</t>
+  </si>
+  <si>
+    <t>12.16.5_ComfillV2_modem_LEDs.png</t>
+  </si>
+  <si>
+    <t>12.16.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.16.6_Teltonika_router_LEDs.png </t>
+  </si>
+  <si>
+    <t>Gateway Lite</t>
+  </si>
+  <si>
+    <t>14.5.1</t>
+  </si>
+  <si>
+    <t>14.5.2</t>
+  </si>
+  <si>
+    <t>14.5.3</t>
+  </si>
+  <si>
+    <t>14.5.4</t>
+  </si>
+  <si>
+    <t>14.5.1_GW_Lite_dimensions.png</t>
+  </si>
+  <si>
+    <t>14.5.2_GW_Lite_mounting.png</t>
+  </si>
+  <si>
+    <t>15.5.3_GW_Lite_glands.png</t>
+  </si>
+  <si>
+    <t>14.5.4_GW_Lite_module.png</t>
   </si>
 </sst>
 </file>
@@ -3294,7 +3330,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B533B56-556A-40A2-8D3F-E8E5A852019A}">
-  <dimension ref="A1:K460"/>
+  <dimension ref="A1:K465"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="1" customWidth="1"/>
@@ -7339,6 +7375,17 @@
       <c r="C333" s="1" t="s">
         <v>540</v>
       </c>
+      <c r="D333" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="334" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C334" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="D334" t="s">
+        <v>882</v>
+      </c>
     </row>
     <row r="336" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B336" t="s">
@@ -7793,9 +7840,15 @@
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A381" s="4"/>
-      <c r="B381" s="5"/>
-      <c r="C381" s="4"/>
-      <c r="D381" s="5"/>
+      <c r="B381" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="C381" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="D381" s="5" t="s">
+        <v>888</v>
+      </c>
       <c r="E381" s="4"/>
       <c r="F381" s="5"/>
       <c r="G381" s="5"/>
@@ -7807,8 +7860,12 @@
     <row r="382" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A382" s="4"/>
       <c r="B382" s="5"/>
-      <c r="C382" s="4"/>
-      <c r="D382" s="5"/>
+      <c r="C382" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="D382" s="5" t="s">
+        <v>889</v>
+      </c>
       <c r="E382" s="4"/>
       <c r="F382" s="5"/>
       <c r="G382" s="5"/>
@@ -7820,8 +7877,12 @@
     <row r="383" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A383" s="4"/>
       <c r="B383" s="5"/>
-      <c r="C383" s="4"/>
-      <c r="D383" s="5"/>
+      <c r="C383" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="D383" s="5" t="s">
+        <v>890</v>
+      </c>
       <c r="E383" s="4"/>
       <c r="F383" s="5"/>
       <c r="G383" s="5"/>
@@ -7830,277 +7891,261 @@
       <c r="J383" s="5"/>
       <c r="K383" s="5"/>
     </row>
-    <row r="385" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C385" s="1" t="s">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A384" s="4"/>
+      <c r="B384" s="5"/>
+      <c r="C384" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D384" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="E384" s="4"/>
+      <c r="F384" s="5"/>
+      <c r="G384" s="5"/>
+      <c r="H384" s="5"/>
+      <c r="I384" s="5"/>
+      <c r="J384" s="5"/>
+      <c r="K384" s="5"/>
+    </row>
+    <row r="385" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A385" s="4"/>
+      <c r="B385" s="5"/>
+      <c r="C385" s="4"/>
+      <c r="D385" s="5"/>
+      <c r="E385" s="4"/>
+      <c r="F385" s="5"/>
+      <c r="G385" s="5"/>
+      <c r="H385" s="5"/>
+      <c r="I385" s="5"/>
+      <c r="J385" s="5"/>
+      <c r="K385" s="5"/>
+    </row>
+    <row r="386" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A386" s="4"/>
+      <c r="B386" s="5"/>
+      <c r="C386" s="4"/>
+      <c r="D386" s="5"/>
+      <c r="E386" s="4"/>
+      <c r="F386" s="5"/>
+      <c r="G386" s="5"/>
+      <c r="H386" s="5"/>
+      <c r="I386" s="5"/>
+      <c r="J386" s="5"/>
+      <c r="K386" s="5"/>
+    </row>
+    <row r="387" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A387" s="4"/>
+      <c r="B387" s="5"/>
+      <c r="C387" s="4"/>
+      <c r="D387" s="5"/>
+      <c r="E387" s="4"/>
+      <c r="F387" s="5"/>
+      <c r="G387" s="5"/>
+      <c r="H387" s="5"/>
+      <c r="I387" s="5"/>
+      <c r="J387" s="5"/>
+      <c r="K387" s="5"/>
+    </row>
+    <row r="388" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A388" s="4"/>
+      <c r="B388" s="5"/>
+      <c r="C388" s="4"/>
+      <c r="D388" s="5"/>
+      <c r="E388" s="4"/>
+      <c r="F388" s="5"/>
+      <c r="G388" s="5"/>
+      <c r="H388" s="5"/>
+      <c r="I388" s="5"/>
+      <c r="J388" s="5"/>
+      <c r="K388" s="5"/>
+    </row>
+    <row r="390" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C390" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="386" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C386" s="1" t="s">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C391" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D386" t="s">
+      <c r="D391" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="387" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C387" s="1" t="s">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C392" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="D387" t="s">
+      <c r="D392" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="388" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C388" s="1" t="s">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C393" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D388" t="s">
+      <c r="D393" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="389" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C389" s="1" t="s">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C394" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D389" t="s">
+      <c r="D394" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="390" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C390" s="1" t="s">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C395" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D390" t="s">
+      <c r="D395" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="391" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C391" s="1" t="s">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C396" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="D391" t="s">
+      <c r="D396" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="392" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C392" s="1" t="s">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C397" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="D392" t="s">
+      <c r="D397" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="393" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C393" s="1" t="s">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C398" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="D393" t="s">
+      <c r="D398" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="394" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C394" s="1" t="s">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C399" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="D394" t="s">
+      <c r="D399" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="395" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C395" s="1" t="s">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C400" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D395" t="s">
+      <c r="D400" t="s">
         <v>404</v>
-      </c>
-    </row>
-    <row r="396" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C396" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="D396" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="397" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C397" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="D397" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="398" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C398" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="D398" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="399" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C399" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="D399" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="400" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C400" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="D400" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C401" s="1" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="D401" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C402" s="1" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D402" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C403" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D403" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="404" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C404" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D404" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="405" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C405" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D405" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="406" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C406" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D406" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="407" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C407" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D407" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="408" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C408" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="D403" t="s">
+      <c r="D408" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="D404" t="s">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D409" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A405" s="26"/>
-      <c r="B405" s="25"/>
-      <c r="C405" s="26"/>
-      <c r="D405" s="25"/>
-      <c r="E405" s="26"/>
-      <c r="F405" s="25"/>
-      <c r="G405" s="25"/>
-      <c r="H405" s="25"/>
-      <c r="I405" s="25"/>
-      <c r="J405" s="25"/>
-      <c r="K405" s="25"/>
-    </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A406" s="39">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A410" s="26"/>
+      <c r="B410" s="25"/>
+      <c r="C410" s="26"/>
+      <c r="D410" s="25"/>
+      <c r="E410" s="26"/>
+      <c r="F410" s="25"/>
+      <c r="G410" s="25"/>
+      <c r="H410" s="25"/>
+      <c r="I410" s="25"/>
+      <c r="J410" s="25"/>
+      <c r="K410" s="25"/>
+    </row>
+    <row r="411" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A411" s="39">
         <v>16</v>
       </c>
-      <c r="B406" s="40" t="s">
+      <c r="B411" s="40" t="s">
         <v>385</v>
       </c>
-      <c r="C406" s="41" t="s">
+      <c r="C411" s="41" t="s">
         <v>337</v>
       </c>
-      <c r="D406" s="42" t="s">
+      <c r="D411" s="42" t="s">
         <v>349</v>
       </c>
-      <c r="E406" s="39" t="s">
+      <c r="E411" s="39" t="s">
         <v>565</v>
       </c>
-      <c r="F406" s="42" t="s">
+      <c r="F411" s="42" t="s">
         <v>385</v>
       </c>
-      <c r="G406" s="42"/>
-      <c r="H406" s="42"/>
-      <c r="I406" s="42"/>
-      <c r="J406" s="42"/>
-      <c r="K406" s="42"/>
-    </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A407" s="39"/>
-      <c r="B407" s="42"/>
-      <c r="C407" s="41" t="s">
-        <v>338</v>
-      </c>
-      <c r="D407" s="42" t="s">
-        <v>350</v>
-      </c>
-      <c r="E407" s="39"/>
-      <c r="F407" s="42"/>
-      <c r="G407" s="42"/>
-      <c r="H407" s="42"/>
-      <c r="I407" s="42"/>
-      <c r="J407" s="42"/>
-      <c r="K407" s="42"/>
-    </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A408" s="39"/>
-      <c r="B408" s="42"/>
-      <c r="C408" s="41" t="s">
-        <v>339</v>
-      </c>
-      <c r="D408" s="42" t="s">
-        <v>351</v>
-      </c>
-      <c r="E408" s="39"/>
-      <c r="F408" s="42"/>
-      <c r="G408" s="42"/>
-      <c r="H408" s="42"/>
-      <c r="I408" s="42"/>
-      <c r="J408" s="42"/>
-      <c r="K408" s="42"/>
-    </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A409" s="39"/>
-      <c r="B409" s="42"/>
-      <c r="C409" s="41" t="s">
-        <v>340</v>
-      </c>
-      <c r="D409" s="42" t="s">
-        <v>352</v>
-      </c>
-      <c r="E409" s="39"/>
-      <c r="F409" s="42"/>
-      <c r="G409" s="42"/>
-      <c r="H409" s="42"/>
-      <c r="I409" s="42"/>
-      <c r="J409" s="42"/>
-      <c r="K409" s="42"/>
-    </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A410" s="39"/>
-      <c r="B410" s="42"/>
-      <c r="C410" s="41" t="s">
-        <v>341</v>
-      </c>
-      <c r="D410" s="42" t="s">
-        <v>353</v>
-      </c>
-      <c r="E410" s="39"/>
-      <c r="F410" s="42"/>
-      <c r="G410" s="42"/>
-      <c r="H410" s="42"/>
-      <c r="I410" s="42"/>
-      <c r="J410" s="42"/>
-      <c r="K410" s="42"/>
-    </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A411" s="39"/>
-      <c r="B411" s="42"/>
-      <c r="C411" s="41" t="s">
-        <v>342</v>
-      </c>
-      <c r="D411" s="42" t="s">
-        <v>354</v>
-      </c>
-      <c r="E411" s="39"/>
-      <c r="F411" s="42"/>
       <c r="G411" s="42"/>
       <c r="H411" s="42"/>
       <c r="I411" s="42"/>
@@ -8111,10 +8156,10 @@
       <c r="A412" s="39"/>
       <c r="B412" s="42"/>
       <c r="C412" s="41" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D412" s="42" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E412" s="39"/>
       <c r="F412" s="42"/>
@@ -8128,10 +8173,10 @@
       <c r="A413" s="39"/>
       <c r="B413" s="42"/>
       <c r="C413" s="41" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D413" s="42" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="E413" s="39"/>
       <c r="F413" s="42"/>
@@ -8145,10 +8190,10 @@
       <c r="A414" s="39"/>
       <c r="B414" s="42"/>
       <c r="C414" s="41" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D414" s="42" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E414" s="39"/>
       <c r="F414" s="42"/>
@@ -8162,10 +8207,10 @@
       <c r="A415" s="39"/>
       <c r="B415" s="42"/>
       <c r="C415" s="41" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D415" s="42" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E415" s="39"/>
       <c r="F415" s="42"/>
@@ -8179,10 +8224,10 @@
       <c r="A416" s="39"/>
       <c r="B416" s="42"/>
       <c r="C416" s="41" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D416" s="42" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E416" s="39"/>
       <c r="F416" s="42"/>
@@ -8196,10 +8241,10 @@
       <c r="A417" s="39"/>
       <c r="B417" s="42"/>
       <c r="C417" s="41" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D417" s="42" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E417" s="39"/>
       <c r="F417" s="42"/>
@@ -8213,10 +8258,10 @@
       <c r="A418" s="39"/>
       <c r="B418" s="42"/>
       <c r="C418" s="41" t="s">
-        <v>372</v>
+        <v>344</v>
       </c>
       <c r="D418" s="42" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E418" s="39"/>
       <c r="F418" s="42"/>
@@ -8230,10 +8275,10 @@
       <c r="A419" s="39"/>
       <c r="B419" s="42"/>
       <c r="C419" s="41" t="s">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="D419" s="42" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="E419" s="39"/>
       <c r="F419" s="42"/>
@@ -8247,10 +8292,10 @@
       <c r="A420" s="39"/>
       <c r="B420" s="42"/>
       <c r="C420" s="41" t="s">
-        <v>374</v>
+        <v>346</v>
       </c>
       <c r="D420" s="42" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E420" s="39"/>
       <c r="F420" s="42"/>
@@ -8264,10 +8309,10 @@
       <c r="A421" s="39"/>
       <c r="B421" s="42"/>
       <c r="C421" s="41" t="s">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="D421" s="42" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="E421" s="39"/>
       <c r="F421" s="42"/>
@@ -8281,10 +8326,10 @@
       <c r="A422" s="39"/>
       <c r="B422" s="42"/>
       <c r="C422" s="41" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
       <c r="D422" s="42" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E422" s="39"/>
       <c r="F422" s="42"/>
@@ -8298,10 +8343,10 @@
       <c r="A423" s="39"/>
       <c r="B423" s="42"/>
       <c r="C423" s="41" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D423" s="42" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="E423" s="39"/>
       <c r="F423" s="42"/>
@@ -8315,10 +8360,10 @@
       <c r="A424" s="39"/>
       <c r="B424" s="42"/>
       <c r="C424" s="41" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D424" s="42" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E424" s="39"/>
       <c r="F424" s="42"/>
@@ -8332,10 +8377,10 @@
       <c r="A425" s="39"/>
       <c r="B425" s="42"/>
       <c r="C425" s="41" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D425" s="42" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E425" s="39"/>
       <c r="F425" s="42"/>
@@ -8349,10 +8394,10 @@
       <c r="A426" s="39"/>
       <c r="B426" s="42"/>
       <c r="C426" s="41" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D426" s="42" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E426" s="39"/>
       <c r="F426" s="42"/>
@@ -8366,10 +8411,10 @@
       <c r="A427" s="39"/>
       <c r="B427" s="42"/>
       <c r="C427" s="41" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="D427" s="42" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E427" s="39"/>
       <c r="F427" s="42"/>
@@ -8383,10 +8428,10 @@
       <c r="A428" s="39"/>
       <c r="B428" s="42"/>
       <c r="C428" s="41" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D428" s="42" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E428" s="39"/>
       <c r="F428" s="42"/>
@@ -8400,10 +8445,10 @@
       <c r="A429" s="39"/>
       <c r="B429" s="42"/>
       <c r="C429" s="41" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D429" s="42" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="E429" s="39"/>
       <c r="F429" s="42"/>
@@ -8414,255 +8459,277 @@
       <c r="K429" s="42"/>
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A430" s="26"/>
-      <c r="B430" s="25"/>
-      <c r="C430" s="26"/>
-      <c r="D430" s="25"/>
-      <c r="E430" s="26"/>
-      <c r="F430" s="25"/>
-      <c r="G430" s="25"/>
-      <c r="H430" s="25"/>
-      <c r="I430" s="25"/>
-      <c r="J430" s="25"/>
-      <c r="K430" s="25"/>
+      <c r="A430" s="39"/>
+      <c r="B430" s="42"/>
+      <c r="C430" s="41" t="s">
+        <v>379</v>
+      </c>
+      <c r="D430" s="42" t="s">
+        <v>368</v>
+      </c>
+      <c r="E430" s="39"/>
+      <c r="F430" s="42"/>
+      <c r="G430" s="42"/>
+      <c r="H430" s="42"/>
+      <c r="I430" s="42"/>
+      <c r="J430" s="42"/>
+      <c r="K430" s="42"/>
     </row>
     <row r="431" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A431" s="32"/>
-      <c r="B431" s="33" t="s">
+      <c r="A431" s="39"/>
+      <c r="B431" s="42"/>
+      <c r="C431" s="41" t="s">
+        <v>380</v>
+      </c>
+      <c r="D431" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="E431" s="39"/>
+      <c r="F431" s="42"/>
+      <c r="G431" s="42"/>
+      <c r="H431" s="42"/>
+      <c r="I431" s="42"/>
+      <c r="J431" s="42"/>
+      <c r="K431" s="42"/>
+    </row>
+    <row r="432" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A432" s="39"/>
+      <c r="B432" s="42"/>
+      <c r="C432" s="41" t="s">
+        <v>381</v>
+      </c>
+      <c r="D432" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="E432" s="39"/>
+      <c r="F432" s="42"/>
+      <c r="G432" s="42"/>
+      <c r="H432" s="42"/>
+      <c r="I432" s="42"/>
+      <c r="J432" s="42"/>
+      <c r="K432" s="42"/>
+    </row>
+    <row r="433" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A433" s="39"/>
+      <c r="B433" s="42"/>
+      <c r="C433" s="41" t="s">
+        <v>382</v>
+      </c>
+      <c r="D433" s="42" t="s">
+        <v>371</v>
+      </c>
+      <c r="E433" s="39"/>
+      <c r="F433" s="42"/>
+      <c r="G433" s="42"/>
+      <c r="H433" s="42"/>
+      <c r="I433" s="42"/>
+      <c r="J433" s="42"/>
+      <c r="K433" s="42"/>
+    </row>
+    <row r="434" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A434" s="39"/>
+      <c r="B434" s="42"/>
+      <c r="C434" s="41" t="s">
+        <v>383</v>
+      </c>
+      <c r="D434" s="42" t="s">
+        <v>384</v>
+      </c>
+      <c r="E434" s="39"/>
+      <c r="F434" s="42"/>
+      <c r="G434" s="42"/>
+      <c r="H434" s="42"/>
+      <c r="I434" s="42"/>
+      <c r="J434" s="42"/>
+      <c r="K434" s="42"/>
+    </row>
+    <row r="435" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A435" s="26"/>
+      <c r="B435" s="25"/>
+      <c r="C435" s="26"/>
+      <c r="D435" s="25"/>
+      <c r="E435" s="26"/>
+      <c r="F435" s="25"/>
+      <c r="G435" s="25"/>
+      <c r="H435" s="25"/>
+      <c r="I435" s="25"/>
+      <c r="J435" s="25"/>
+      <c r="K435" s="25"/>
+    </row>
+    <row r="436" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A436" s="32"/>
+      <c r="B436" s="33" t="s">
         <v>424</v>
       </c>
-      <c r="C431" s="32" t="s">
+      <c r="C436" s="32" t="s">
         <v>425</v>
       </c>
-      <c r="D431" s="38" t="s">
+      <c r="D436" s="38" t="s">
         <v>426</v>
       </c>
-      <c r="E431" s="32"/>
-      <c r="F431" s="33"/>
-      <c r="G431" s="33"/>
-    </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A432" s="4"/>
-      <c r="B432" s="5"/>
-      <c r="C432" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="D432" s="18" t="s">
-        <v>428</v>
-      </c>
-      <c r="E432" s="4"/>
-      <c r="F432" s="5"/>
-      <c r="G432" s="5"/>
-    </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A434" s="4"/>
-      <c r="B434" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="C434" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="D434" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="E434" s="4"/>
-      <c r="F434" s="5"/>
-      <c r="G434" s="5"/>
-    </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A435" s="4"/>
-      <c r="B435" s="5"/>
-      <c r="C435" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="D435" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="E435" s="4"/>
-      <c r="F435" s="5"/>
-      <c r="G435" s="5"/>
-    </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A436" s="4"/>
-      <c r="B436" s="5"/>
-      <c r="C436" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="D436" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="E436" s="4"/>
-      <c r="F436" s="5"/>
-      <c r="G436" s="5"/>
-    </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E436" s="32"/>
+      <c r="F436" s="33"/>
+      <c r="G436" s="33"/>
+    </row>
+    <row r="437" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A437" s="4"/>
       <c r="B437" s="5"/>
       <c r="C437" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="D437" s="16" t="s">
-        <v>432</v>
+        <v>427</v>
+      </c>
+      <c r="D437" s="18" t="s">
+        <v>428</v>
       </c>
       <c r="E437" s="4"/>
       <c r="F437" s="5"/>
       <c r="G437" s="5"/>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A438" s="4"/>
-      <c r="B438" s="5"/>
-      <c r="C438" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="D438" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="E438" s="4"/>
-      <c r="F438" s="5"/>
-      <c r="G438" s="5"/>
-    </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A439" s="4"/>
-      <c r="B439" s="5"/>
-      <c r="C439" s="4"/>
-      <c r="D439" s="5"/>
+      <c r="B439" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="C439" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D439" s="16" t="s">
+        <v>429</v>
+      </c>
       <c r="E439" s="4"/>
       <c r="F439" s="5"/>
       <c r="G439" s="5"/>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A440" s="4"/>
-      <c r="B440" s="5" t="s">
-        <v>436</v>
-      </c>
+      <c r="B440" s="5"/>
       <c r="C440" s="4" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="D440" s="16" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="E440" s="4"/>
-      <c r="F440" s="5" t="s">
-        <v>447</v>
-      </c>
+      <c r="F440" s="5"/>
       <c r="G440" s="5"/>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A441" s="4"/>
       <c r="B441" s="5"/>
       <c r="C441" s="4" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="D441" s="16" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="E441" s="4"/>
-      <c r="F441" s="5" t="s">
-        <v>448</v>
-      </c>
+      <c r="F441" s="5"/>
       <c r="G441" s="5"/>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A442" s="4"/>
       <c r="B442" s="5"/>
       <c r="C442" s="4" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D442" s="16" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="E442" s="4"/>
-      <c r="F442" s="5" t="s">
-        <v>449</v>
-      </c>
+      <c r="F442" s="5"/>
       <c r="G442" s="5"/>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A443" s="4"/>
       <c r="B443" s="5"/>
       <c r="C443" s="4" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="D443" s="16" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="E443" s="4"/>
-      <c r="F443" s="5" t="s">
-        <v>453</v>
-      </c>
+      <c r="F443" s="5"/>
       <c r="G443" s="5"/>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A444" s="4"/>
       <c r="B444" s="5"/>
-      <c r="C444" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="D444" s="16" t="s">
-        <v>440</v>
-      </c>
+      <c r="C444" s="4"/>
+      <c r="D444" s="5"/>
       <c r="E444" s="4"/>
       <c r="F444" s="5"/>
       <c r="G444" s="5"/>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A445" s="4"/>
-      <c r="B445" s="5"/>
-      <c r="C445" s="4"/>
-      <c r="D445" s="5"/>
+      <c r="B445" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C445" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="D445" s="16" t="s">
+        <v>450</v>
+      </c>
       <c r="E445" s="4"/>
-      <c r="F445" s="5"/>
+      <c r="F445" s="5" t="s">
+        <v>447</v>
+      </c>
       <c r="G445" s="5"/>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A446" s="4"/>
-      <c r="B446" s="5" t="s">
-        <v>441</v>
-      </c>
+      <c r="B446" s="5"/>
       <c r="C446" s="4" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D446" s="16" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="E446" s="4"/>
-      <c r="F446" s="5"/>
+      <c r="F446" s="5" t="s">
+        <v>448</v>
+      </c>
       <c r="G446" s="5"/>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A447" s="4"/>
       <c r="B447" s="5"/>
       <c r="C447" s="4" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D447" s="16" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="E447" s="4"/>
-      <c r="F447" s="5"/>
+      <c r="F447" s="5" t="s">
+        <v>449</v>
+      </c>
       <c r="G447" s="5"/>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A448" s="4"/>
       <c r="B448" s="5"/>
       <c r="C448" s="4" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="D448" s="16" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="E448" s="4"/>
-      <c r="F448" s="5"/>
+      <c r="F448" s="5" t="s">
+        <v>453</v>
+      </c>
       <c r="G448" s="5"/>
     </row>
     <row r="449" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A449" s="4"/>
       <c r="B449" s="5"/>
       <c r="C449" s="4" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D449" s="16" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="E449" s="4"/>
       <c r="F449" s="5"/>
@@ -8671,111 +8738,91 @@
     <row r="450" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A450" s="4"/>
       <c r="B450" s="5"/>
-      <c r="C450" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="D450" s="16" t="s">
-        <v>446</v>
-      </c>
+      <c r="C450" s="4"/>
+      <c r="D450" s="5"/>
       <c r="E450" s="4"/>
       <c r="F450" s="5"/>
       <c r="G450" s="5"/>
     </row>
+    <row r="451" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A451" s="4"/>
+      <c r="B451" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="C451" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="D451" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="E451" s="4"/>
+      <c r="F451" s="5"/>
+      <c r="G451" s="5"/>
+    </row>
+    <row r="452" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A452" s="4"/>
+      <c r="B452" s="5"/>
+      <c r="C452" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="D452" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="E452" s="4"/>
+      <c r="F452" s="5"/>
+      <c r="G452" s="5"/>
+    </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A453" s="43">
+      <c r="A453" s="4"/>
+      <c r="B453" s="5"/>
+      <c r="C453" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="D453" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="E453" s="4"/>
+      <c r="F453" s="5"/>
+      <c r="G453" s="5"/>
+    </row>
+    <row r="454" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A454" s="4"/>
+      <c r="B454" s="5"/>
+      <c r="C454" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="D454" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="E454" s="4"/>
+      <c r="F454" s="5"/>
+      <c r="G454" s="5"/>
+    </row>
+    <row r="455" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A455" s="4"/>
+      <c r="B455" s="5"/>
+      <c r="C455" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D455" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="E455" s="4"/>
+      <c r="F455" s="5"/>
+      <c r="G455" s="5"/>
+    </row>
+    <row r="458" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A458" s="43">
         <v>19</v>
       </c>
-      <c r="B453" s="50" t="s">
+      <c r="B458" s="50" t="s">
         <v>716</v>
       </c>
-      <c r="C453" s="43" t="s">
+      <c r="C458" s="43" t="s">
         <v>726</v>
       </c>
-      <c r="D453" s="44" t="s">
+      <c r="D458" s="44" t="s">
         <v>727</v>
-      </c>
-      <c r="E453" s="43"/>
-      <c r="F453" s="44"/>
-      <c r="G453" s="44"/>
-      <c r="H453" s="44"/>
-      <c r="I453" s="44"/>
-      <c r="J453" s="44"/>
-      <c r="K453" s="44"/>
-    </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A454" s="43"/>
-      <c r="B454" s="44"/>
-      <c r="C454" s="43" t="s">
-        <v>717</v>
-      </c>
-      <c r="D454" s="45" t="s">
-        <v>718</v>
-      </c>
-      <c r="E454" s="43"/>
-      <c r="F454" s="44"/>
-      <c r="G454" s="44"/>
-      <c r="H454" s="44"/>
-      <c r="I454" s="44"/>
-      <c r="J454" s="44"/>
-      <c r="K454" s="44"/>
-    </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A455" s="43"/>
-      <c r="B455" s="44"/>
-      <c r="C455" s="43" t="s">
-        <v>728</v>
-      </c>
-      <c r="D455" s="44" t="s">
-        <v>729</v>
-      </c>
-      <c r="E455" s="43"/>
-      <c r="F455" s="44"/>
-      <c r="G455" s="44"/>
-      <c r="H455" s="44"/>
-      <c r="I455" s="44"/>
-      <c r="J455" s="44"/>
-      <c r="K455" s="44"/>
-    </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A456" s="43"/>
-      <c r="B456" s="44"/>
-      <c r="C456" s="43" t="s">
-        <v>719</v>
-      </c>
-      <c r="D456" s="44"/>
-      <c r="E456" s="43"/>
-      <c r="F456" s="44"/>
-      <c r="G456" s="44"/>
-      <c r="H456" s="44"/>
-      <c r="I456" s="44"/>
-      <c r="J456" s="44"/>
-      <c r="K456" s="44"/>
-    </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A457" s="43"/>
-      <c r="B457" s="44"/>
-      <c r="C457" s="43" t="s">
-        <v>720</v>
-      </c>
-      <c r="D457" s="44" t="s">
-        <v>723</v>
-      </c>
-      <c r="E457" s="43"/>
-      <c r="F457" s="44"/>
-      <c r="G457" s="44"/>
-      <c r="H457" s="44"/>
-      <c r="I457" s="44"/>
-      <c r="J457" s="44"/>
-      <c r="K457" s="44"/>
-    </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A458" s="43"/>
-      <c r="B458" s="44"/>
-      <c r="C458" s="43" t="s">
-        <v>725</v>
-      </c>
-      <c r="D458" s="44" t="s">
-        <v>724</v>
       </c>
       <c r="E458" s="43"/>
       <c r="F458" s="44"/>
@@ -8789,10 +8836,10 @@
       <c r="A459" s="43"/>
       <c r="B459" s="44"/>
       <c r="C459" s="43" t="s">
-        <v>721</v>
-      </c>
-      <c r="D459" s="44" t="s">
-        <v>722</v>
+        <v>717</v>
+      </c>
+      <c r="D459" s="45" t="s">
+        <v>718</v>
       </c>
       <c r="E459" s="43"/>
       <c r="F459" s="44"/>
@@ -8805,8 +8852,12 @@
     <row r="460" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A460" s="43"/>
       <c r="B460" s="44"/>
-      <c r="C460" s="43"/>
-      <c r="D460" s="44"/>
+      <c r="C460" s="43" t="s">
+        <v>728</v>
+      </c>
+      <c r="D460" s="44" t="s">
+        <v>729</v>
+      </c>
       <c r="E460" s="43"/>
       <c r="F460" s="44"/>
       <c r="G460" s="44"/>
@@ -8814,6 +8865,85 @@
       <c r="I460" s="44"/>
       <c r="J460" s="44"/>
       <c r="K460" s="44"/>
+    </row>
+    <row r="461" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A461" s="43"/>
+      <c r="B461" s="44"/>
+      <c r="C461" s="43" t="s">
+        <v>719</v>
+      </c>
+      <c r="D461" s="44"/>
+      <c r="E461" s="43"/>
+      <c r="F461" s="44"/>
+      <c r="G461" s="44"/>
+      <c r="H461" s="44"/>
+      <c r="I461" s="44"/>
+      <c r="J461" s="44"/>
+      <c r="K461" s="44"/>
+    </row>
+    <row r="462" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A462" s="43"/>
+      <c r="B462" s="44"/>
+      <c r="C462" s="43" t="s">
+        <v>720</v>
+      </c>
+      <c r="D462" s="44" t="s">
+        <v>723</v>
+      </c>
+      <c r="E462" s="43"/>
+      <c r="F462" s="44"/>
+      <c r="G462" s="44"/>
+      <c r="H462" s="44"/>
+      <c r="I462" s="44"/>
+      <c r="J462" s="44"/>
+      <c r="K462" s="44"/>
+    </row>
+    <row r="463" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A463" s="43"/>
+      <c r="B463" s="44"/>
+      <c r="C463" s="43" t="s">
+        <v>725</v>
+      </c>
+      <c r="D463" s="44" t="s">
+        <v>724</v>
+      </c>
+      <c r="E463" s="43"/>
+      <c r="F463" s="44"/>
+      <c r="G463" s="44"/>
+      <c r="H463" s="44"/>
+      <c r="I463" s="44"/>
+      <c r="J463" s="44"/>
+      <c r="K463" s="44"/>
+    </row>
+    <row r="464" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A464" s="43"/>
+      <c r="B464" s="44"/>
+      <c r="C464" s="43" t="s">
+        <v>721</v>
+      </c>
+      <c r="D464" s="44" t="s">
+        <v>722</v>
+      </c>
+      <c r="E464" s="43"/>
+      <c r="F464" s="44"/>
+      <c r="G464" s="44"/>
+      <c r="H464" s="44"/>
+      <c r="I464" s="44"/>
+      <c r="J464" s="44"/>
+      <c r="K464" s="44"/>
+    </row>
+    <row r="465" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A465" s="43"/>
+      <c r="B465" s="44"/>
+      <c r="C465" s="43"/>
+      <c r="D465" s="44"/>
+      <c r="E465" s="43"/>
+      <c r="F465" s="44"/>
+      <c r="G465" s="44"/>
+      <c r="H465" s="44"/>
+      <c r="I465" s="44"/>
+      <c r="J465" s="44"/>
+      <c r="K465" s="44"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
